--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_England_Pr" displayName="AveragesTable_England_Pr" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="H7" t="n">
-        <v>78</v>
+        <v>74.83</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>32</v>
+        <v>31.83</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.8</v>
-      </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.8</v>
+        <v>6.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="AB7" t="n">
         <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.8</v>
+        <v>16.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.27</v>
+        <v>9.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.52</v>
+        <v>6.61</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="CC7" t="n">
         <v>7.57</v>
@@ -3637,124 +3637,124 @@
         <v>7.81</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS7" t="n">
         <v>2.81</v>
       </c>
-      <c r="CN7" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>2.82</v>
-      </c>
       <c r="CT7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CU7" t="n">
         <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DH7" t="n">
-        <v>78.73</v>
+        <v>77.08</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.82</v>
+        <v>32.66</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.91</v>
+        <v>10.17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.18</v>
+        <v>10.34</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.82</v>
+        <v>10.66</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>38.37</v>
+        <v>38.84</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="DY7" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.73</v>
+        <v>15.92</v>
       </c>
       <c r="EB7" t="n">
         <v>0.98</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>106.2</v>
+        <v>98.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.6</v>
+        <v>5.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.6</v>
+        <v>16.33</v>
       </c>
       <c r="BE8" t="n">
         <v>1.61</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.8</v>
@@ -4028,16 +4028,16 @@
         <v>1.9</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4052,61 +4052,61 @@
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
         <v>1.39</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
         <v>3.29</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CW8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CY8" t="n">
         <v>1.7</v>
       </c>
-      <c r="CX8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>1.68</v>
-      </c>
       <c r="CZ8" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DB8" t="n">
         <v>1.26</v>
@@ -4115,82 +4115,82 @@
         <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="DH8" t="n">
-        <v>108</v>
+        <v>104.08</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.45</v>
+        <v>6.66</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.73</v>
+        <v>56.66</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.55</v>
+        <v>11.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.64</v>
+        <v>13.58</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.73</v>
+        <v>59.42</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.36</v>
+        <v>14.42</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.37</v>
+        <v>16.75</v>
       </c>
       <c r="EB8" t="n">
         <v>1.72</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="9">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>111.4</v>
+        <v>111.83</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>53.4</v>
+        <v>61.33</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="R2" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.4</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.4</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>9.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.4</v>
+        <v>5.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.36</v>
+        <v>10.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>2.08</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>2.16</v>
       </c>
       <c r="CA2" t="n">
         <v>3.75</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC2" t="n">
         <v>4.58</v>
@@ -1625,7 +1625,7 @@
         <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
         <v>3.23</v>
@@ -1640,10 +1640,10 @@
         <v>1.67</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM2" t="n">
         <v>3.04</v>
@@ -1652,13 +1652,13 @@
         <v>2.24</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1667,7 +1667,7 @@
         <v>2.62</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CU2" t="n">
         <v>1.54</v>
@@ -1682,97 +1682,97 @@
         <v>1.53</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.46</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.18000000000001</v>
+        <v>98.58</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.64</v>
+        <v>53.92</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.09</v>
+        <v>12.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.46</v>
+        <v>10.34</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.36</v>
+        <v>6.92</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.64</v>
+        <v>52.75</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>12</v>
+        <v>13.34</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.55</v>
+        <v>8.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.45</v>
+        <v>4.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.46</v>
+        <v>20.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="H3" t="n">
-        <v>106.8</v>
+        <v>110.67</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>64</v>
+        <v>63.5</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.4</v>
+        <v>12.17</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63.4</v>
+        <v>62.33</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.4</v>
+        <v>15.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.91</v>
+        <v>9.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.91</v>
+        <v>4.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BZ3" t="n">
         <v>1.48</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="CC3" t="n">
         <v>1.84</v>
@@ -2028,151 +2028,151 @@
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX3" t="n">
         <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.53</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="DH3" t="n">
-        <v>97.64</v>
+        <v>100.34</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ3" t="n">
         <v>1</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.37</v>
+        <v>61.34</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11</v>
+        <v>11.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.91</v>
+        <v>58.75</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.73</v>
+        <v>14.92</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.18</v>
+        <v>18.16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="EC3" t="n">
         <v>1</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.59999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.4</v>
+        <v>50.83</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.8</v>
+        <v>16.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,73 +2332,73 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>58.6</v>
+        <v>57.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.8</v>
+        <v>11.33</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.8</v>
+        <v>17.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.73</v>
+        <v>10.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="BR4" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY4" t="n">
         <v>2.45</v>
@@ -2416,91 +2416,91 @@
         <v>2.51</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="CE4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK4" t="n">
         <v>1.36</v>
       </c>
-      <c r="CF4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CL4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY4" t="n">
         <v>1.75</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.72</v>
-      </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD4" t="n">
         <v>3.16</v>
@@ -2509,43 +2509,43 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.27</v>
+        <v>90.42</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.36</v>
+        <v>5.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.37</v>
+        <v>44.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.550000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.18</v>
+        <v>16.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.630000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.91</v>
+        <v>53.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.27</v>
+        <v>7.58</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.82</v>
+        <v>15.75</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2681,43 +2681,43 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.59999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.2</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>8.17</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
@@ -2726,91 +2726,91 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.8</v>
+        <v>49.17</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>3.83</v>
@@ -2819,34 +2819,34 @@
         <v>3.91</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI5" t="n">
         <v>2.14</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
         <v>1.36</v>
@@ -2855,10 +2855,10 @@
         <v>1.68</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.24</v>
@@ -2867,7 +2867,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2876,112 +2876,112 @@
         <v>2.62</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CU5" t="n">
         <v>1.51</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX5" t="n">
         <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="EB5" t="n">
         <v>1.3</v>
       </c>
-      <c r="DC5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>83</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>41.36</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="EC5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="6">
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="H6" t="n">
-        <v>76.8</v>
+        <v>88</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>44.2</v>
+        <v>52.17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>12.2</v>
+        <v>11.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="R6" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -3048,37 +3048,37 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.6</v>
+        <v>47</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.8</v>
+        <v>7.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>3.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.09</v>
+        <v>9.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="CA6" t="n">
         <v>3.53</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC6" t="n">
         <v>2.9</v>
@@ -3237,49 +3237,49 @@
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH6" t="n">
         <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.84</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS6" t="n">
         <v>2.57</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU6" t="n">
         <v>1.53</v>
@@ -3294,13 +3294,13 @@
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.35</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
@@ -3312,79 +3312,79 @@
         <v>2.86</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.36</v>
+        <v>91.16</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.36</v>
+        <v>52</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.36</v>
+        <v>12.16</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>10.84</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.82</v>
+        <v>50.08</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.09</v>
+        <v>12.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="7">
@@ -3622,13 +3622,13 @@
         <v>5.92</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.61</v>
+        <v>6.37</v>
       </c>
       <c r="CA7" t="n">
         <v>4.29</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="CC7" t="n">
         <v>7.57</v>
@@ -3679,40 +3679,40 @@
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB7" t="n">
         <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -4031,13 +4031,13 @@
         <v>3.98</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC8" t="n">
         <v>1.96</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4082,40 +4082,40 @@
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB8" t="n">
         <v>1.26</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4293,70 +4293,70 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="n">
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>35.6</v>
+        <v>37.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.4</v>
+        <v>10.83</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.6</v>
+        <v>42.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
@@ -4368,61 +4368,61 @@
         <v>1.26</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.73</v>
+        <v>9.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR9" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS9" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY9" t="n">
         <v>2.42</v>
@@ -4431,16 +4431,16 @@
         <v>2.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.26</v>
+        <v>3.85</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.47</v>
+        <v>4.03</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
@@ -4449,34 +4449,34 @@
         <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.79</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.29</v>
@@ -4494,106 +4494,106 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.09</v>
+        <v>76.25</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.18</v>
+        <v>41.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.36</v>
+        <v>10.25</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="DR9" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.73</v>
+        <v>42.58</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.18</v>
+        <v>18</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="10">
@@ -5006,61 +5006,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>87.17</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>46.6</v>
+        <v>50.17</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.2</v>
+        <v>12.33</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.8</v>
+        <v>52.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>22</v>
+        <v>21.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5177,49 +5177,49 @@
         <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC11" t="n">
         <v>4.01</v>
@@ -5252,10 +5252,10 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CH11" t="n">
         <v>1.4</v>
@@ -5270,31 +5270,31 @@
         <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
@@ -5309,64 +5309,64 @@
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD11" t="n">
         <v>3.36</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.27</v>
+        <v>85.17</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM11" t="n">
-        <v>46</v>
+        <v>47.84</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.54</v>
+        <v>12.58</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.91</v>
+        <v>7.84</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.18</v>
+        <v>50.75</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11</v>
+        <v>12.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.55</v>
+        <v>8.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.73</v>
+        <v>20.67</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>88.40000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>40.8</v>
+        <v>42.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>11.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="R12" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.2</v>
+        <v>47.33</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD12" t="n">
         <v>1.59</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BQ12" t="n">
         <v>4</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>3.99</v>
@@ -5652,19 +5652,19 @@
         <v>4.44</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH12" t="n">
         <v>1.4</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.82</v>
@@ -5673,13 +5673,13 @@
         <v>1.45</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO12" t="n">
         <v>1.32</v>
@@ -5688,7 +5688,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5709,16 +5709,16 @@
         <v>1.91</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
@@ -5730,79 +5730,79 @@
         <v>3.37</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.91</v>
+        <v>82.33</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.27</v>
+        <v>4.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.45</v>
+        <v>43.16</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>10</v>
+        <v>10.66</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.18</v>
+        <v>12.66</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.27</v>
+        <v>48.25</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.18</v>
+        <v>16.66</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="H13" t="n">
-        <v>99.2</v>
+        <v>100.33</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>49.4</v>
+        <v>57</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="P13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.8</v>
+        <v>11.17</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>57.6</v>
+        <v>60.5</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.8</v>
+        <v>15.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.6</v>
+        <v>10.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.4</v>
+        <v>23.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.27</v>
+        <v>10.58</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN13" t="n">
         <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="CC13" t="n">
         <v>2.1</v>
@@ -6067,31 +6067,31 @@
         <v>1.64</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CK13" t="n">
         <v>1.35</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN13" t="n">
         <v>2.22</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP13" t="n">
         <v>1.53</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
@@ -6106,106 +6106,106 @@
         <v>1.67</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DB13" t="n">
         <v>1.25</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.18</v>
+        <v>106.16</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.18</v>
+        <v>5.42</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.82</v>
+        <v>58.16</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.45</v>
+        <v>7</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.64</v>
+        <v>61.84</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.82</v>
+        <v>15.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.64</v>
+        <v>11.16</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.55</v>
+        <v>20.92</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,52 +6305,52 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>102.83</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP14" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>52</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>12.83</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>9.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH14" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.52</v>
@@ -6446,34 +6446,34 @@
         <v>1.52</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CE14" t="n">
         <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CK14" t="n">
         <v>1.41</v>
@@ -6482,19 +6482,19 @@
         <v>1.75</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO14" t="n">
         <v>1.17</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
@@ -6509,16 +6509,16 @@
         <v>1.62</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.42</v>
@@ -6536,46 +6536,46 @@
         <v>2.55</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.36</v>
+        <v>98.92</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="DM14" t="n">
-        <v>55.91</v>
+        <v>56.84</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.63</v>
+        <v>13.75</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.46</v>
+        <v>57.34</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.82</v>
+        <v>14.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.630000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.18</v>
+        <v>19.92</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -7033,79 +7033,79 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H16" t="n">
-        <v>94.59999999999999</v>
+        <v>90.17</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>57.2</v>
+        <v>53.17</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="P16" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>14.17</v>
       </c>
       <c r="R16" t="n">
-        <v>5.8</v>
+        <v>6.67</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>46.8</v>
+        <v>44.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>13.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -7192,70 +7192,70 @@
         <v>1.33</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.45</v>
+        <v>10.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="BR16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="CA16" t="n">
         <v>3.71</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC16" t="n">
         <v>2.41</v>
@@ -7264,43 +7264,43 @@
         <v>2.46</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CG16" t="n">
         <v>3.13</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CQ16" t="n">
         <v>2.95</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>2.98</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,106 +7315,106 @@
         <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>102.18</v>
+        <v>99.34</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DM16" t="n">
-        <v>61.91</v>
+        <v>59.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.73</v>
+        <v>11.84</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.55</v>
+        <v>12.34</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.82</v>
+        <v>6.25</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.18</v>
+        <v>49.66</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.91</v>
+        <v>11.67</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.64</v>
+        <v>20.75</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7514,52 +7514,52 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.8</v>
+        <v>87.33</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>45.8</v>
+        <v>45.17</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.8</v>
+        <v>13.33</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.4</v>
+        <v>9.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,73 +7571,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.8</v>
+        <v>48.17</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.2</v>
+        <v>5.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.82</v>
+        <v>5.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY17" t="n">
         <v>2.34</v>
@@ -7655,55 +7655,55 @@
         <v>2.36</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.67</v>
+        <v>5.08</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI17" t="n">
         <v>1.99</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7718,106 +7718,106 @@
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.39</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>99</v>
+        <v>95.75</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.73</v>
+        <v>55.5</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.91</v>
+        <v>10.66</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.91</v>
+        <v>11.83</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.09</v>
+        <v>7.66</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.54</v>
+        <v>50.25</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.91</v>
+        <v>12.16</v>
       </c>
       <c r="DY17" t="n">
         <v>8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="EA17" t="n">
-        <v>19</v>
+        <v>18.84</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
-        <v>95.2</v>
+        <v>92.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>37.8</v>
+        <v>38.17</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>8.83</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.8</v>
+        <v>43.67</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>5.83</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.8</v>
+        <v>16.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.64</v>
+        <v>7.92</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY18" t="n">
         <v>3.62</v>
@@ -8058,37 +8058,37 @@
         <v>4.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.37</v>
+        <v>5.06</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.37</v>
+        <v>5.14</v>
       </c>
       <c r="CE18" t="n">
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH18" t="n">
         <v>1.38</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL18" t="n">
         <v>1.85</v>
@@ -8112,34 +8112,34 @@
         <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT18" t="n">
         <v>2.84</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA18" t="n">
         <v>1.98</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
         <v>2.14</v>
@@ -8151,76 +8151,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG18" t="n">
         <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>91.81999999999999</v>
+        <v>90.75</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.09</v>
+        <v>39.17</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.550000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.27</v>
+        <v>43.25</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.09</v>
+        <v>9.58</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.36</v>
+        <v>6.92</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.18</v>
+        <v>17.16</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0.33</v>
@@ -8323,49 +8323,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>73</v>
+        <v>71.83</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
-        <v>6.8</v>
+        <v>5.83</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>40.4</v>
+        <v>36.83</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.4</v>
+        <v>11.17</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>9.83</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.2</v>
+        <v>49.83</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.6</v>
+        <v>9.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>5.67</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.6</v>
+        <v>18.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="BF19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.55</v>
+        <v>11</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BP19" t="n">
-        <v>6.18</v>
+        <v>5.75</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.05</v>
@@ -8461,34 +8461,34 @@
         <v>2.27</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.26</v>
+        <v>3.93</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.5</v>
+        <v>4.19</v>
       </c>
       <c r="CE19" t="n">
         <v>1.32</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH19" t="n">
         <v>1.49</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CK19" t="n">
         <v>1.3</v>
@@ -8497,7 +8497,7 @@
         <v>1.62</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CN19" t="n">
         <v>2.34</v>
@@ -8506,87 +8506,87 @@
         <v>1.22</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="inlineStr"/>
       <c r="CY19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CZ19" t="inlineStr"/>
       <c r="DA19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.09</v>
+        <v>84.42</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.09</v>
+        <v>5.66</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.91</v>
+        <v>45.5</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO19" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.55</v>
+        <v>11.84</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.36</v>
+        <v>10.66</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.73</v>
+        <v>8.67</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.73</v>
+        <v>52.83</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.73</v>
+        <v>9.17</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.27</v>
+        <v>5.84</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="EA19" t="n">
-        <v>20</v>
+        <v>20.16</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>0.17</v>
@@ -8722,115 +8722,115 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>98</v>
+        <v>92.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK20" t="n">
         <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.2</v>
+        <v>4.67</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.6</v>
+        <v>37.17</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.8</v>
+        <v>9.67</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>48.8</v>
+        <v>44.67</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.2</v>
+        <v>9.33</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="BD20" t="n">
-        <v>20.4</v>
+        <v>18.67</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BF20" t="n">
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BH20" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,19 +8839,19 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX20" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY20" t="n">
         <v>3.61</v>
@@ -8860,70 +8860,70 @@
         <v>3.54</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CB20" t="n">
         <v>4.1</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.42</v>
+        <v>6.12</v>
       </c>
       <c r="CD20" t="n">
-        <v>7.05</v>
+        <v>6.72</v>
       </c>
       <c r="CE20" t="n">
         <v>1.36</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CO20" t="n">
         <v>1.26</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW20" t="n">
         <v>1.8</v>
@@ -8932,97 +8932,97 @@
         <v>1.5</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.54</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="DH20" t="n">
-        <v>90.09</v>
+        <v>88.08</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="DM20" t="n">
-        <v>43.27</v>
+        <v>40.92</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.64</v>
+        <v>10.58</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.27</v>
+        <v>9.17</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>45.64</v>
+        <v>43.84</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.46</v>
+        <v>10</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.37</v>
+        <v>6.08</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="EA20" t="n">
-        <v>20.27</v>
+        <v>19.42</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="21">
@@ -9032,94 +9032,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H21" t="n">
-        <v>106.6</v>
+        <v>99.67</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="P21" t="n">
-        <v>12.8</v>
+        <v>12.83</v>
       </c>
       <c r="Q21" t="n">
         <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>51.2</v>
+        <v>50.67</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
         <v>7</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AC21" t="n">
-        <v>22.4</v>
+        <v>21.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,70 +9203,70 @@
         <v>2.33</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC21" t="n">
         <v>5.62</v>
@@ -9275,16 +9275,16 @@
         <v>6.28</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF21" t="n">
         <v>2.86</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI21" t="n">
         <v>1.89</v>
@@ -9293,25 +9293,25 @@
         <v>1.85</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CN21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CO21" t="n">
         <v>1.31</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CR21" t="n">
         <v>1.43</v>
@@ -9332,100 +9332,100 @@
         <v>1.93</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DH21" t="n">
-        <v>97</v>
+        <v>94.34</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ21" t="n">
         <v>2</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM21" t="n">
-        <v>42.82</v>
+        <v>42</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.45</v>
+        <v>13.42</v>
       </c>
       <c r="DQ21" t="n">
-        <v>9.91</v>
+        <v>9.83</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.18</v>
+        <v>7.16</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.37</v>
+        <v>47.42</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.539999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="EA21" t="n">
-        <v>21</v>
+        <v>20.83</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,16 +4693,16 @@
         <v>2.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.40000000000001</v>
+        <v>85.33</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -4711,31 +4711,31 @@
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>39.4</v>
+        <v>37.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.8</v>
+        <v>11.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>5.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY10" t="n">
         <v>2.36</v>
@@ -4834,34 +4834,34 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.72</v>
+        <v>4.61</v>
       </c>
       <c r="CE10" t="n">
         <v>1.4</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.41</v>
@@ -4870,133 +4870,133 @@
         <v>1.74</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.47</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
         <v>1.98</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.27</v>
+        <v>93.42</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.64</v>
+        <v>48.92</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.46</v>
+        <v>13.42</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>8.08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>44.91</v>
+        <v>43.66</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.09</v>
+        <v>10.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.91</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.63</v>
+        <v>20.42</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="11">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="H15" t="n">
-        <v>106.6</v>
+        <v>113.83</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M15" t="n">
-        <v>51.8</v>
+        <v>58.33</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="P15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.2</v>
+        <v>13.67</v>
       </c>
       <c r="R15" t="n">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.6</v>
+        <v>54.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.4</v>
+        <v>18.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>12.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.6</v>
+        <v>20.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6789,70 +6789,70 @@
         <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC15" t="n">
         <v>2.96</v>
@@ -6861,157 +6861,157 @@
         <v>3.09</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.6</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CT15" t="n">
         <v>3.3</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX15" t="n">
         <v>1.5</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.36</v>
+        <v>106.33</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.73</v>
+        <v>49.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.359999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.63</v>
+        <v>12.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.63</v>
+        <v>52.25</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.36</v>
+        <v>15.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.27</v>
+        <v>10.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.36</v>
+        <v>19.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,52 +1469,52 @@
         <v>2.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.33</v>
+        <v>88.14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.5</v>
+        <v>46.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.17</v>
+        <v>10.71</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.33</v>
+        <v>7.71</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.5</v>
+        <v>48.86</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.67</v>
+        <v>12.57</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.17</v>
+        <v>7.86</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.17</v>
+        <v>17.29</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.42</v>
+        <v>10.31</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU2" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
         <v>1.98</v>
@@ -1610,169 +1610,169 @@
         <v>2.08</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.58</v>
+        <v>4.25</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.03</v>
+        <v>4.64</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.67</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DA2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CW2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>2.28</v>
-      </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.58</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.08</v>
+        <v>5.84</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.92</v>
+        <v>53.15</v>
       </c>
       <c r="DN2" t="n">
         <v>1.08</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.75</v>
+        <v>12.77</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.34</v>
+        <v>10.61</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.92</v>
+        <v>7.15</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.75</v>
+        <v>53.08</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.34</v>
+        <v>13.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.08</v>
+        <v>19.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL3" t="n">
-        <v>7</v>
+        <v>6.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>59.17</v>
+        <v>58.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC3" t="n">
         <v>5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.17</v>
-      </c>
       <c r="BD3" t="n">
-        <v>17.83</v>
+        <v>17.43</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.5</v>
+        <v>9.23</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL3" t="n">
         <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY3" t="n">
         <v>1.46</v>
@@ -2013,55 +2013,55 @@
         <v>1.48</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.74</v>
+        <v>4.62</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2076,106 +2076,106 @@
         <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.34</v>
+        <v>99.77</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.58</v>
+        <v>6.31</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.34</v>
+        <v>60.85</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.42</v>
+        <v>11.54</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.75</v>
+        <v>59</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.92</v>
+        <v>14.39</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.92</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.16</v>
+        <v>17.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="EC3" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>89.17</v>
+        <v>91.86</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="K4" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>38.67</v>
+        <v>42.43</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="P4" t="n">
-        <v>9.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.5</v>
+        <v>17.43</v>
       </c>
       <c r="R4" t="n">
-        <v>7.33</v>
+        <v>6.57</v>
       </c>
       <c r="S4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50</v>
+        <v>50.29</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.83</v>
+        <v>11.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>6.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>1.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.33</v>
+        <v>10.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP4" t="n">
         <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="CC4" t="n">
         <v>3.08</v>
@@ -2431,19 +2431,19 @@
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
         <v>1.36</v>
@@ -2455,34 +2455,34 @@
         <v>2.85</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.55</v>
@@ -2500,52 +2500,52 @@
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.42</v>
+        <v>91.77</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.16</v>
+        <v>5.31</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.75</v>
+        <v>46.31</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.08</v>
+        <v>10.31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.66</v>
+        <v>17.15</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.42</v>
+        <v>7.92</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.75</v>
+        <v>53.62</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.08</v>
+        <v>11.46</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.58</v>
+        <v>7.77</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.75</v>
+        <v>15.54</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H5" t="n">
+        <v>89</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H5" t="n">
-        <v>85</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.33</v>
-      </c>
       <c r="K5" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="L5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>41.5</v>
+        <v>42.86</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="P5" t="n">
-        <v>10.83</v>
+        <v>10.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5</v>
+        <v>5.71</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.42</v>
+        <v>5.23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.17</v>
+        <v>4.46</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.91</v>
+        <v>3.57</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="CC5" t="n">
         <v>3.36</v>
@@ -2834,7 +2834,7 @@
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG5" t="n">
         <v>3.16</v>
@@ -2843,61 +2843,61 @@
         <v>1.48</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL5" t="n">
         <v>1.68</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU5" t="n">
         <v>1.51</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CX5" t="n">
         <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DB5" t="n">
         <v>1.29</v>
@@ -2912,76 +2912,76 @@
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DH5" t="n">
-        <v>84.16</v>
+        <v>86.38</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.75</v>
+        <v>43.39</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.25</v>
+        <v>10.93</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10</v>
+        <v>9.69</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.34</v>
+        <v>6.85</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.5</v>
+        <v>43.23</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.58</v>
+        <v>10.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.17</v>
+        <v>6.47</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.84</v>
+        <v>19.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>94.33</v>
+        <v>92.14</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN6" t="n">
-        <v>51.83</v>
+        <v>50.86</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.17</v>
+        <v>6.71</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>53.17</v>
+        <v>52.43</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12</v>
+        <v>12.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.83</v>
+        <v>19.29</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BO6" t="n">
         <v>1.08</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY6" t="n">
         <v>2.33</v>
@@ -3222,31 +3222,31 @@
         <v>2.46</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.62</v>
@@ -3255,40 +3255,40 @@
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="DE6" t="n">
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.16</v>
+        <v>90.23</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM6" t="n">
-        <v>52</v>
+        <v>51.46</v>
       </c>
       <c r="DN6" t="n">
         <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.16</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.84</v>
+        <v>10.92</v>
       </c>
       <c r="DR6" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="DY6" t="n">
         <v>7.92</v>
       </c>
-      <c r="DS6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>50.08</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>7.67</v>
-      </c>
       <c r="DZ6" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.08</v>
+        <v>17</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.33</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.5</v>
+        <v>34.14</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>10.29</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>11.14</v>
       </c>
       <c r="AT7" t="n">
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>41.17</v>
+        <v>42.14</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.67</v>
+        <v>16.43</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.33</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.77</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY7" t="n">
         <v>5.92</v>
@@ -3625,25 +3625,25 @@
         <v>6.37</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="CB7" t="n">
         <v>4.55</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.57</v>
+        <v>7.44</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.81</v>
+        <v>7.7</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH7" t="n">
         <v>1.47</v>
@@ -3658,10 +3658,10 @@
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN7" t="n">
         <v>2.11</v>
@@ -3670,19 +3670,19 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU7" t="n">
         <v>1.49</v>
@@ -3691,13 +3691,13 @@
         <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX7" t="n">
         <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.4</v>
@@ -3712,7 +3712,7 @@
         <v>1.94</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3721,73 +3721,73 @@
         <v>1.16</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="DH7" t="n">
-        <v>77.08</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.66</v>
+        <v>33.07</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DO7" t="n">
         <v>1.08</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.17</v>
+        <v>9.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.66</v>
+        <v>11</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>38.84</v>
+        <v>39.54</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.92</v>
+        <v>16.31</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="H8" t="n">
-        <v>109.5</v>
+        <v>105.86</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>7.29</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>62.83</v>
+        <v>59.43</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>4.17</v>
+        <v>3.57</v>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.5</v>
+        <v>13.86</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.83</v>
+        <v>58.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.5</v>
+        <v>14.86</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.5</v>
+        <v>5.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.17</v>
+        <v>16.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.5</v>
+        <v>10.15</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="CC8" t="n">
         <v>1.96</v>
@@ -4040,43 +4040,43 @@
         <v>2.09</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CP8" t="n">
         <v>1.73</v>
       </c>
-      <c r="CM8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>1.69</v>
-      </c>
       <c r="CQ8" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4091,73 +4091,73 @@
         <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW8" t="n">
         <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.08</v>
+        <v>102.54</v>
       </c>
       <c r="DI8" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.66</v>
+        <v>6.39</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.66</v>
+        <v>55.31</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.42</v>
+        <v>57.77</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.42</v>
+        <v>14.15</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.58</v>
+        <v>5.47</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.75</v>
+        <v>16.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>76</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M9" t="n">
-        <v>45.83</v>
+        <v>44.43</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.67</v>
+        <v>42.86</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>13.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>20</v>
+        <v>19.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,67 +4371,67 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.33</v>
+        <v>9.23</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="BR9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
         <v>3.65</v>
@@ -4446,7 +4446,7 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG9" t="n">
         <v>2.95</v>
@@ -4455,10 +4455,10 @@
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
         <v>1.43</v>
@@ -4470,130 +4470,130 @@
         <v>2.63</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="DE9" t="n">
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.25</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.66</v>
+        <v>41.23</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.25</v>
+        <v>10.54</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.75</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.58</v>
+        <v>42.69</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.08</v>
+        <v>12.23</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.67</v>
+        <v>7.92</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="EA9" t="n">
-        <v>18</v>
+        <v>17.69</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="H10" t="n">
-        <v>101.5</v>
+        <v>104</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>10.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.67</v>
+        <v>14.29</v>
       </c>
       <c r="R10" t="n">
-        <v>5.17</v>
+        <v>4.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.33</v>
+        <v>49.29</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.83</v>
+        <v>13.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.33</v>
+        <v>20.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4774,70 +4774,70 @@
         <v>1.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.25</v>
+        <v>9.69</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU10" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC10" t="n">
         <v>4.25</v>
@@ -4858,10 +4858,10 @@
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
         <v>1.41</v>
@@ -4882,88 +4882,88 @@
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.42</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.42</v>
+        <v>95.38</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.83</v>
+        <v>4.16</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.92</v>
+        <v>51.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.58</v>
+        <v>10.07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.42</v>
+        <v>12.85</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.08</v>
+        <v>7.69</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.66</v>
+        <v>44.08</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.42</v>
+        <v>10.39</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.42</v>
+        <v>19.93</v>
       </c>
       <c r="EB10" t="n">
         <v>1.23</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5096,130 +5096,130 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.17</v>
       </c>
-      <c r="AH11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>83.17</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL11" t="n">
         <v>1.23</v>
       </c>
-      <c r="BF11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BM11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BP11" t="n">
         <v>5.08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY11" t="n">
         <v>3.02</v>
@@ -5237,16 +5237,16 @@
         <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.47</v>
+        <v>4.27</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5255,28 +5255,28 @@
         <v>2.83</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH11" t="n">
         <v>1.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL11" t="n">
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
@@ -5285,58 +5285,58 @@
         <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DH11" t="n">
-        <v>85.17</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
@@ -5345,28 +5345,28 @@
         <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
         <v>0.08</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.84</v>
+        <v>45.61</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.25</v>
+        <v>12.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.84</v>
+        <v>8</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.75</v>
+        <v>49.69</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.08</v>
+        <v>11.69</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.42</v>
+        <v>8.07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.67</v>
+        <v>20.85</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.83</v>
+        <v>73.14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.83</v>
+        <v>43.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.83</v>
+        <v>12.43</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.17</v>
+        <v>47.57</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.33</v>
+        <v>16.29</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.42</v>
+        <v>7.54</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
         <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY12" t="n">
         <v>2.69</v>
@@ -5640,34 +5640,34 @@
         <v>2.86</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.49</v>
+        <v>3.72</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.99</v>
+        <v>4.85</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.44</v>
+        <v>5.67</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK12" t="n">
         <v>1.45</v>
@@ -5676,31 +5676,31 @@
         <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN12" t="n">
         <v>2.03</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="CT12" t="n">
         <v>2.89</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="CV12" t="n">
         <v>1.97</v>
@@ -5709,67 +5709,67 @@
         <v>1.91</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.33</v>
+        <v>81.77</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.16</v>
+        <v>3.92</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.16</v>
+        <v>43</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.66</v>
+        <v>10.69</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.66</v>
+        <v>12.92</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.25</v>
+        <v>47.46</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.16</v>
+        <v>11.92</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.58</v>
+        <v>8.31</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.66</v>
+        <v>16.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AI13" t="n">
-        <v>112</v>
+        <v>109.14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>59.33</v>
+        <v>56.14</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.83</v>
+        <v>11.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>63.17</v>
+        <v>62.14</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.83</v>
+        <v>14</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>10.43</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.17</v>
+        <v>18.86</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.58</v>
+        <v>10.46</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BN13" t="n">
         <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY13" t="n">
         <v>1.59</v>
@@ -6043,16 +6043,16 @@
         <v>1.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="CE13" t="n">
         <v>1.25</v>
@@ -6061,7 +6061,7 @@
         <v>2.23</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CH13" t="n">
         <v>1.64</v>
@@ -6070,7 +6070,7 @@
         <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK13" t="n">
         <v>1.35</v>
@@ -6079,13 +6079,13 @@
         <v>1.61</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP13" t="n">
         <v>1.53</v>
@@ -6097,7 +6097,7 @@
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CT13" t="n">
         <v>3.33</v>
@@ -6115,64 +6115,64 @@
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DB13" t="n">
         <v>1.25</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.16</v>
+        <v>105.07</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.42</v>
+        <v>5.15</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM13" t="n">
-        <v>58.16</v>
+        <v>56.54</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.17</v>
+        <v>10.46</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.67</v>
+        <v>11.85</v>
       </c>
       <c r="DR13" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.84</v>
+        <v>61.38</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.33</v>
+        <v>14.84</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.16</v>
+        <v>10.61</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.16</v>
+        <v>4.23</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.92</v>
+        <v>21.08</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="H14" t="n">
-        <v>95</v>
+        <v>95.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="K14" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="L14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M14" t="n">
-        <v>59.17</v>
+        <v>60.71</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O14" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>8.33</v>
+        <v>9.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>57.17</v>
+        <v>57.86</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.33</v>
+        <v>15.71</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.5</v>
+        <v>6.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.33</v>
+        <v>20.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
         <v>0.33</v>
@@ -6386,70 +6386,70 @@
         <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.33</v>
+        <v>10.23</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.51</v>
+        <v>4.73</v>
       </c>
       <c r="CC14" t="n">
         <v>2.04</v>
@@ -6461,67 +6461,67 @@
         <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL14" t="n">
         <v>1.75</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO14" t="n">
         <v>1.17</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY14" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
         <v>2.08</v>
@@ -6530,52 +6530,52 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.92</v>
+        <v>99.08</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.92</v>
+        <v>6.08</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.84</v>
+        <v>57.84</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.25</v>
+        <v>9.85</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.34</v>
+        <v>57.69</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.08</v>
+        <v>14.38</v>
       </c>
       <c r="DY14" t="n">
         <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.08</v>
+        <v>5.39</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.92</v>
+        <v>19.08</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6708,52 +6708,52 @@
         <v>1.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AI15" t="n">
-        <v>98.83</v>
+        <v>101.71</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.67</v>
+        <v>40.57</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.5</v>
+        <v>10.14</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.83</v>
+        <v>50.71</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.33</v>
+        <v>19</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BH15" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY15" t="n">
         <v>2.22</v>
@@ -6849,25 +6849,25 @@
         <v>2.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CB15" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CH15" t="n">
         <v>1.54</v>
@@ -6885,28 +6885,28 @@
         <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU15" t="n">
         <v>1.59</v>
@@ -6918,16 +6918,16 @@
         <v>1.62</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
@@ -6936,49 +6936,49 @@
         <v>1.66</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>106.33</v>
+        <v>107.3</v>
       </c>
       <c r="DI15" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.5</v>
+        <v>48.77</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.58</v>
+        <v>9.92</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.5</v>
+        <v>12.77</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.58</v>
+        <v>7.62</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.25</v>
+        <v>52.54</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.25</v>
+        <v>15.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.33</v>
+        <v>19.61</v>
       </c>
       <c r="EB15" t="n">
         <v>1.68</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,53 +7111,53 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>109.29</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU16" t="n">
         <v>1</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>65.83</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV16" t="n">
         <v>0</v>
       </c>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.83</v>
+        <v>54.29</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.17</v>
+        <v>10.57</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.5</v>
+        <v>20.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.75</v>
+        <v>11.08</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.67</v>
+        <v>5.92</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BR16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY16" t="n">
         <v>2.5</v>
@@ -7252,28 +7252,28 @@
         <v>2.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI16" t="n">
         <v>2.12</v>
@@ -7288,34 +7288,34 @@
         <v>1.66</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW16" t="n">
         <v>1.74</v>
@@ -7324,64 +7324,64 @@
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DH16" t="n">
-        <v>99.34</v>
+        <v>100.47</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="DM16" t="n">
-        <v>59.5</v>
+        <v>58.16</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.84</v>
+        <v>11.39</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.34</v>
+        <v>11.69</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.25</v>
+        <v>6.23</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.66</v>
+        <v>49.77</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.92</v>
+        <v>7.69</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.75</v>
+        <v>20.54</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G17" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="H17" t="n">
-        <v>104.17</v>
+        <v>105.43</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="K17" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M17" t="n">
-        <v>65.83</v>
+        <v>66.86</v>
       </c>
       <c r="N17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.33</v>
+        <v>10.29</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>6.71</v>
       </c>
       <c r="S17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>52.33</v>
+        <v>52.29</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.5</v>
+        <v>15.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.33</v>
+        <v>11.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.17</v>
+        <v>18.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7595,49 +7595,49 @@
         <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM17" t="n">
         <v>0.92</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
         <v>5.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="CA17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="CB17" t="n">
         <v>3.8</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>3.84</v>
       </c>
       <c r="CC17" t="n">
         <v>4.92</v>
@@ -7670,7 +7670,7 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG17" t="n">
         <v>3.08</v>
@@ -7679,22 +7679,22 @@
         <v>1.45</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.78</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL17" t="n">
         <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO17" t="n">
         <v>1.26</v>
@@ -7718,10 +7718,10 @@
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7742,49 +7742,49 @@
         <v>1.92</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.75</v>
+        <v>97.08</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.17</v>
+        <v>5.46</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.5</v>
+        <v>56.85</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.66</v>
+        <v>10.69</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.83</v>
+        <v>11.69</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.66</v>
+        <v>7.92</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.25</v>
+        <v>50.39</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.16</v>
+        <v>12.69</v>
       </c>
       <c r="DY17" t="n">
-        <v>8</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.84</v>
+        <v>18.46</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>89</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M18" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>11</v>
-      </c>
-      <c r="R18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>42.83</v>
+        <v>42.86</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.5</v>
+        <v>16.71</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU18" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BZ18" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC18" t="n">
         <v>5.06</v>
@@ -8073,7 +8073,7 @@
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
         <v>2.74</v>
@@ -8082,49 +8082,49 @@
         <v>1.38</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK18" t="n">
         <v>1.45</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN18" t="n">
         <v>2</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX18" t="n">
         <v>1.58</v>
@@ -8133,94 +8133,94 @@
         <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="DG18" t="n">
         <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.75</v>
+        <v>89.92</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.17</v>
+        <v>39.23</v>
       </c>
       <c r="DN18" t="n">
         <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.83</v>
+        <v>10.15</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.5</v>
+        <v>10.61</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.25</v>
+        <v>43.23</v>
       </c>
       <c r="DW18" t="n">
         <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.58</v>
+        <v>9.77</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.92</v>
+        <v>6.84</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.16</v>
+        <v>16.77</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>99.86</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="L19" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>54.17</v>
+        <v>56.86</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="R19" t="n">
-        <v>7.17</v>
+        <v>6.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>55.83</v>
+        <v>56.86</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>6</v>
+        <v>6.86</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>22.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH19" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC19" t="n">
         <v>3.93</v>
@@ -8473,22 +8473,22 @@
         <v>4.19</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
         <v>1.3</v>
@@ -8497,28 +8497,28 @@
         <v>1.62</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CN19" t="n">
         <v>2.34</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CU19" t="n">
         <v>1.48</v>
@@ -8541,52 +8541,52 @@
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE19" t="n">
         <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="DH19" t="n">
-        <v>84.42</v>
+        <v>86.92</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.66</v>
+        <v>5.85</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.5</v>
+        <v>47.62</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO19" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.84</v>
+        <v>11.77</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.66</v>
+        <v>10.69</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.67</v>
+        <v>8.16</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.83</v>
+        <v>53.62</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.17</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY19" t="n">
-        <v>5.84</v>
+        <v>6.31</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.16</v>
+        <v>20.61</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="20">
@@ -8629,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="H20" t="n">
-        <v>83.5</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="K20" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="L20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M20" t="n">
-        <v>44.67</v>
+        <v>45</v>
       </c>
       <c r="N20" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.5</v>
+        <v>11.14</v>
       </c>
       <c r="R20" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="T20" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,28 +8695,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>43</v>
+        <v>43.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.67</v>
+        <v>10.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AC20" t="n">
-        <v>20.17</v>
+        <v>19.29</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8800,37 +8800,37 @@
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BH20" t="n">
-        <v>12.33</v>
+        <v>12.08</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BN20" t="n">
         <v>1.92</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,31 +8839,31 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU20" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV20" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.61</v>
+        <v>3.83</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="CC20" t="n">
         <v>6.12</v>
@@ -8872,124 +8872,124 @@
         <v>6.72</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CK20" t="n">
         <v>1.36</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="CT20" t="n">
         <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CX20" t="n">
         <v>1.5</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.54</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.08</v>
+        <v>88.92</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM20" t="n">
-        <v>40.92</v>
+        <v>41.39</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.58</v>
+        <v>10.7</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.58</v>
+        <v>10.92</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.17</v>
+        <v>8.93</v>
       </c>
       <c r="DS20" t="n">
         <v>0.08</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.84</v>
+        <v>43.85</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DX20" t="n">
-        <v>10</v>
+        <v>9.77</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.08</v>
+        <v>6.16</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.42</v>
+        <v>19</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="21">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0.17</v>
@@ -9125,49 +9125,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" t="n">
-        <v>89</v>
+        <v>90.14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.5</v>
+        <v>40.29</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9179,82 +9179,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.17</v>
+        <v>44.71</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="BC21" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>19.83</v>
+        <v>18.43</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BH21" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP21" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU21" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV21" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY21" t="n">
         <v>3.58</v>
@@ -9263,28 +9263,28 @@
         <v>3.84</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.62</v>
+        <v>5.81</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.28</v>
+        <v>6.42</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI21" t="n">
         <v>1.89</v>
@@ -9293,34 +9293,34 @@
         <v>1.85</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN21" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO21" t="n">
         <v>1.31</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU21" t="n">
         <v>1.44</v>
@@ -9347,7 +9347,7 @@
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DD21" t="n">
         <v>3.03</v>
@@ -9356,43 +9356,43 @@
         <v>0.08</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DH21" t="n">
-        <v>94.34</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI21" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DK21" t="n">
         <v>3.08</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM21" t="n">
-        <v>42</v>
+        <v>41.77</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.42</v>
+        <v>14</v>
       </c>
       <c r="DQ21" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.16</v>
+        <v>7.23</v>
       </c>
       <c r="DS21" t="n">
         <v>0.08</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.42</v>
+        <v>47.46</v>
       </c>
       <c r="DW21" t="n">
         <v>0.16</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.42</v>
+        <v>6.31</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="EB21" t="n">
         <v>1.12</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="H2" t="n">
-        <v>111.83</v>
+        <v>109</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>5.29</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>61.33</v>
+        <v>58.43</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="P2" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.5</v>
+        <v>11.14</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>57.57</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>13.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>23</v>
+        <v>22.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF2" t="n">
         <v>0.43</v>
@@ -1550,70 +1550,70 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.31</v>
+        <v>10.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC2" t="n">
         <v>4.25</v>
@@ -1625,28 +1625,28 @@
         <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI2" t="n">
         <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK2" t="n">
         <v>1.34</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CN2" t="n">
         <v>2.22</v>
@@ -1655,10 +1655,10 @@
         <v>1.24</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1700,79 +1700,79 @@
         <v>2.91</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.06999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.84</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.15</v>
+        <v>52.28</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.77</v>
+        <v>12.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.61</v>
+        <v>10.92</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.08</v>
+        <v>53.22</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.69</v>
+        <v>13.07</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="EA2" t="n">
         <v>19.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="3">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,49 +4693,49 @@
         <v>2.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.33</v>
+        <v>86.86</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.83</v>
+        <v>42.43</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>10.14</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>7.86</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.17</v>
+        <v>5.86</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>20.29</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY10" t="n">
         <v>2.4</v>
@@ -4834,16 +4834,16 @@
         <v>2.49</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
         <v>3.56</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="CE10" t="n">
         <v>1.4</v>
@@ -4852,25 +4852,25 @@
         <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH10" t="n">
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK10" t="n">
         <v>1.41</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN10" t="n">
         <v>2.03</v>
@@ -4879,10 +4879,10 @@
         <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4897,10 +4897,10 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
         <v>1.56</v>
@@ -4924,79 +4924,79 @@
         <v>3.23</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="DG10" t="n">
         <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.38</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.16</v>
+        <v>4.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.38</v>
+        <v>52.72</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.07</v>
+        <v>10.36</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.85</v>
+        <v>12.93</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>44.08</v>
+        <v>44.14</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.39</v>
+        <v>10.58</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.46</v>
+        <v>7.64</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.93</v>
+        <v>20.29</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="11">
@@ -5006,61 +5006,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="H11" t="n">
-        <v>87.17</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="K11" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>50.17</v>
+        <v>51</v>
       </c>
       <c r="N11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.33</v>
+        <v>11.71</v>
       </c>
       <c r="R11" t="n">
-        <v>7.17</v>
+        <v>6.71</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.67</v>
+        <v>53.29</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.67</v>
+        <v>21.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
         <v>0.43</v>
@@ -5177,70 +5177,70 @@
         <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.31</v>
+        <v>10.21</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.18</v>
+        <v>3.49</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CC11" t="n">
         <v>3.88</v>
@@ -5252,40 +5252,40 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL11" t="n">
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,10 +5300,10 @@
         <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5327,46 +5327,46 @@
         <v>3.34</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="DH11" t="n">
-        <v>84.15000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.61</v>
+        <v>46.36</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.69</v>
+        <v>12.36</v>
       </c>
       <c r="DR11" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.69</v>
+        <v>50.22</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.69</v>
+        <v>11.71</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.07</v>
+        <v>7.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.85</v>
+        <v>20.64</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="12">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6305,52 +6305,52 @@
         <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" t="n">
-        <v>102.83</v>
+        <v>100.29</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.5</v>
+        <v>52.14</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.5</v>
+        <v>55.43</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.23</v>
+        <v>10.14</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BP14" t="n">
         <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>1.48</v>
@@ -6446,31 +6446,31 @@
         <v>1.48</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="CE14" t="n">
         <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.69</v>
@@ -6509,10 +6509,10 @@
         <v>1.63</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6536,46 +6536,46 @@
         <v>2.51</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.08</v>
+        <v>98.08</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.08</v>
+        <v>5.78</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>57.84</v>
+        <v>56.42</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.54</v>
+        <v>13.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.69</v>
+        <v>56.64</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.38</v>
+        <v>14.14</v>
       </c>
       <c r="DY14" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.08</v>
+        <v>19</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="15">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="H16" t="n">
-        <v>90.17</v>
+        <v>91</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="K16" t="n">
-        <v>6.67</v>
+        <v>7.29</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="M16" t="n">
-        <v>53.17</v>
+        <v>53.14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O16" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P16" t="n">
-        <v>12.5</v>
+        <v>11.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="R16" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>44.5</v>
+        <v>45.71</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>8.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AF16" t="n">
         <v>0.29</v>
@@ -7192,64 +7192,64 @@
         <v>1.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.08</v>
+        <v>11.64</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.92</v>
+        <v>5.43</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="BR16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="CA16" t="n">
         <v>3.66</v>
@@ -7279,28 +7279,28 @@
         <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP16" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7318,19 +7318,19 @@
         <v>2.23</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7342,79 +7342,79 @@
         <v>2.97</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="DH16" t="n">
-        <v>100.47</v>
+        <v>100.15</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.54</v>
+        <v>5.93</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="DM16" t="n">
-        <v>58.16</v>
+        <v>57.78</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO16" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.39</v>
+        <v>10.93</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.69</v>
+        <v>11.72</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.23</v>
+        <v>6.14</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.77</v>
+        <v>50</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.77</v>
+        <v>12.28</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.69</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.54</v>
+        <v>20.07</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.29</v>
@@ -8323,49 +8323,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.67</v>
+        <v>2.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>71.83</v>
+        <v>72.86</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.83</v>
+        <v>6.14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>36.83</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.83</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.83</v>
+        <v>49.43</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.92</v>
+        <v>11.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.69</v>
+        <v>5.21</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.23</v>
+        <v>4.79</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
         <v>2.08</v>
@@ -8461,16 +8461,16 @@
         <v>2.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB19" t="n">
         <v>3.82</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="CE19" t="n">
         <v>1.33</v>
@@ -8488,19 +8488,19 @@
         <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK19" t="n">
         <v>1.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CO19" t="n">
         <v>1.23</v>
@@ -8509,7 +8509,7 @@
         <v>1.78</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
@@ -8524,10 +8524,10 @@
         <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="inlineStr"/>
       <c r="CY19" t="n">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="CZ19" t="inlineStr"/>
       <c r="DA19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
@@ -8547,46 +8547,46 @@
         <v>2.99</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.92</v>
+        <v>86.36</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.62</v>
+        <v>47.43</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.69</v>
+        <v>10.36</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.16</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.62</v>
+        <v>53.14</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.529999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.61</v>
+        <v>20.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G3" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="H3" t="n">
-        <v>110.67</v>
+        <v>112.29</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="K3" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>63.5</v>
+        <v>63.14</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P3" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="R3" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="S3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="T3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62.33</v>
+        <v>62.29</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.67</v>
+        <v>15.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.5</v>
+        <v>18.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,67 +1953,67 @@
         <v>2.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.23</v>
+        <v>9.43</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO3" t="n">
         <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY3" t="n">
         <v>1.46</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="CB3" t="n">
         <v>4.62</v>
@@ -2025,19 +2025,19 @@
         <v>2.02</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
         <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.97</v>
@@ -2049,10 +2049,10 @@
         <v>1.78</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2067,16 +2067,16 @@
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
         <v>2.02</v>
@@ -2085,7 +2085,7 @@
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.51</v>
@@ -2097,85 +2097,85 @@
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.77</v>
+        <v>101.36</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.31</v>
+        <v>6.14</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.85</v>
+        <v>60.86</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.69</v>
+        <v>10.43</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.54</v>
+        <v>11.36</v>
       </c>
       <c r="DR3" t="n">
         <v>5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59</v>
+        <v>59.22</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.39</v>
+        <v>14.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.92</v>
+        <v>17.86</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,49 +2278,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.67</v>
+        <v>87</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>50.83</v>
+        <v>47</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>10.71</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.83</v>
+        <v>16.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>57.5</v>
+        <v>55.57</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.33</v>
+        <v>11.71</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.17</v>
+        <v>8.43</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.17</v>
+        <v>3.29</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.33</v>
+        <v>17.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.31</v>
+        <v>10.36</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>2.31</v>
@@ -2416,22 +2416,22 @@
         <v>2.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CE4" t="n">
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2440,31 +2440,31 @@
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2476,13 +2476,13 @@
         <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
         <v>1.55</v>
@@ -2509,43 +2509,43 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.77</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>46.31</v>
+        <v>44.72</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.31</v>
+        <v>10.21</v>
       </c>
       <c r="DQ4" t="n">
-        <v>17.15</v>
+        <v>16.93</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.92</v>
+        <v>8.07</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.62</v>
+        <v>52.93</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.77</v>
+        <v>7.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.54</v>
+        <v>15.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.29</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AI5" t="n">
-        <v>83.33</v>
+        <v>80.86</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>41.43</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.67</v>
+        <v>11.29</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.17</v>
+        <v>47.57</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.5</v>
+        <v>17.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.85</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY5" t="n">
         <v>3.5</v>
@@ -2819,34 +2819,34 @@
         <v>3.57</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
         <v>1.37</v>
@@ -2855,133 +2855,133 @@
         <v>1.68</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN5" t="n">
         <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
         <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB5" t="n">
         <v>1.29</v>
       </c>
       <c r="DC5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>84.93000000000001</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ5" t="n">
         <v>1.86</v>
       </c>
-      <c r="DD5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>86.38</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DK5" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>43.39</v>
+        <v>42.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.93</v>
+        <v>10.79</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.23</v>
+        <v>42.86</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.84</v>
+        <v>10.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.47</v>
+        <v>6.36</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.15</v>
+        <v>18.78</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>88</v>
+        <v>93.14</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>52.17</v>
+        <v>51.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P6" t="n">
-        <v>11.83</v>
+        <v>11.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>9.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47</v>
+        <v>48.29</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.17</v>
+        <v>7.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.33</v>
+        <v>13.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>3.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.380000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.31</v>
+        <v>4.43</v>
       </c>
       <c r="BQ6" t="n">
         <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BX6" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CA6" t="n">
         <v>3.51</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC6" t="n">
         <v>2.85</v>
@@ -3240,13 +3240,13 @@
         <v>2.55</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.62</v>
@@ -3255,13 +3255,13 @@
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
@@ -3270,22 +3270,22 @@
         <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW6" t="n">
         <v>1.63</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>90.23</v>
+        <v>92.64</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
         <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.46</v>
+        <v>51.36</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.92</v>
+        <v>10.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.92</v>
+        <v>50.36</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.61</v>
+        <v>12.86</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>17</v>
+        <v>16.58</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H7" t="n">
-        <v>74.83</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M7" t="n">
-        <v>31.83</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.83</v>
-      </c>
       <c r="P7" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>36.5</v>
+        <v>39.57</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.17</v>
+        <v>18</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.37</v>
+        <v>6.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="CC7" t="n">
         <v>7.44</v>
@@ -3637,16 +3637,16 @@
         <v>7.7</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI7" t="n">
         <v>1.83</v>
@@ -3655,139 +3655,139 @@
         <v>1.94</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DB7" t="n">
         <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DH7" t="n">
-        <v>78.45999999999999</v>
+        <v>81.22</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.07</v>
+        <v>34.79</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.92</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="DR7" t="n">
-        <v>11</v>
+        <v>10.64</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>39.54</v>
+        <v>40.86</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.31</v>
+        <v>17.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.14</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AI8" t="n">
-        <v>98.67</v>
+        <v>102</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>50.5</v>
+        <v>50.86</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>11.71</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.67</v>
+        <v>13.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.67</v>
+        <v>5.14</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.33</v>
+        <v>17.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.77</v>
+        <v>5.43</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY8" t="n">
         <v>2.02</v>
@@ -4028,16 +4028,16 @@
         <v>2.09</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC8" t="n">
         <v>1.96</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4046,13 +4046,13 @@
         <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.69</v>
@@ -4061,13 +4061,13 @@
         <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
@@ -4076,121 +4076,121 @@
         <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO8" t="n">
         <v>2.86</v>
       </c>
-      <c r="DE8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>102.54</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>3</v>
-      </c>
       <c r="DP8" t="n">
-        <v>11.31</v>
+        <v>11.42</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.77</v>
+        <v>13.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.08</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.77</v>
+        <v>58.72</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.69</v>
+        <v>8.93</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.47</v>
+        <v>5.21</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.53</v>
+        <v>17</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.5</v>
+        <v>37.14</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.17</v>
+        <v>10.71</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.5</v>
+        <v>42.43</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.17</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.17</v>
+        <v>6.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>16.57</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.23</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.54</v>
+        <v>4.29</v>
       </c>
       <c r="BR9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>2.41</v>
@@ -4431,169 +4431,169 @@
         <v>2.48</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>1.78</v>
       </c>
-      <c r="CX9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>78.15000000000001</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DK9" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.23</v>
+        <v>40.79</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.54</v>
+        <v>10.36</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.609999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.69</v>
+        <v>42.64</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.23</v>
+        <v>11.57</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.92</v>
+        <v>7.36</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.69</v>
+        <v>17.86</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="10">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>91.83</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>42.5</v>
+        <v>41.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="P12" t="n">
-        <v>11.33</v>
+        <v>11.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="R12" t="n">
-        <v>8.67</v>
+        <v>8.43</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.33</v>
+        <v>44.71</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.5</v>
+        <v>15.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AC12" t="n">
-        <v>16</v>
+        <v>15.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.54</v>
+        <v>7.43</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="CA12" t="n">
         <v>3.72</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
         <v>4.85</v>
@@ -5655,40 +5655,40 @@
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH12" t="n">
         <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5697,112 +5697,112 @@
         <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV12" t="n">
         <v>1.97</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
         <v>2.07</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.77</v>
+        <v>81.86</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DK12" t="n">
         <v>3.92</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM12" t="n">
-        <v>43</v>
+        <v>42.28</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.31</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.46</v>
+        <v>46.14</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.92</v>
+        <v>12.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.31</v>
+        <v>8.58</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.16</v>
+        <v>15.86</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="H13" t="n">
-        <v>100.33</v>
+        <v>105.57</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K13" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M13" t="n">
-        <v>57</v>
+        <v>61.57</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P13" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.17</v>
+        <v>10.43</v>
       </c>
       <c r="R13" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>60.5</v>
+        <v>61.57</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.83</v>
+        <v>16.86</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.83</v>
+        <v>12</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.67</v>
+        <v>22.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,34 +5983,34 @@
         <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.46</v>
+        <v>10.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BN13" t="n">
         <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
         <v>6</v>
@@ -6019,34 +6019,34 @@
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.44</v>
+        <v>4.51</v>
       </c>
       <c r="CC13" t="n">
         <v>2.03</v>
@@ -6055,22 +6055,22 @@
         <v>2.19</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.35</v>
@@ -6091,25 +6091,25 @@
         <v>1.53</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CT13" t="n">
         <v>3.33</v>
       </c>
       <c r="CU13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CW13" t="n">
         <v>1.67</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.65</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6121,7 +6121,7 @@
         <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DB13" t="n">
         <v>1.25</v>
@@ -6130,82 +6130,82 @@
         <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.07</v>
+        <v>107.36</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.15</v>
+        <v>5.29</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.54</v>
+        <v>58.86</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.46</v>
+        <v>10.43</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.85</v>
+        <v>11.43</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.92</v>
+        <v>6.79</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.38</v>
+        <v>61.86</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.84</v>
+        <v>15.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.61</v>
+        <v>11.22</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.08</v>
+        <v>20.72</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="14">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>113.83</v>
+        <v>109.57</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="L15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M15" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="P15" t="n">
-        <v>9.67</v>
+        <v>10.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="R15" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>54.67</v>
+        <v>56.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.67</v>
+        <v>18.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.33</v>
+        <v>21.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6789,70 +6789,70 @@
         <v>1.29</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.92</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="CC15" t="n">
         <v>2.98</v>
@@ -6864,46 +6864,46 @@
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
         <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP15" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CT15" t="n">
         <v>3.31</v>
@@ -6912,34 +6912,34 @@
         <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.52</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -6948,70 +6948,70 @@
         <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>107.3</v>
+        <v>105.64</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.23</v>
+        <v>4.35</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.77</v>
+        <v>50.28</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.92</v>
+        <v>10.14</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.77</v>
+        <v>12.57</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.54</v>
+        <v>53.42</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.15</v>
+        <v>15.28</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.92</v>
+        <v>10.14</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.61</v>
+        <v>20.22</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7514,52 +7514,52 @@
         <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>87.33</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.67</v>
+        <v>4.43</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>45.17</v>
+        <v>45.57</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.33</v>
+        <v>14.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.33</v>
+        <v>8.57</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,73 +7571,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.17</v>
+        <v>48.43</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
         <v>1.24</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.08</v>
+        <v>5.14</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY17" t="n">
         <v>2.41</v>
@@ -7655,55 +7655,55 @@
         <v>2.45</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.92</v>
+        <v>4.52</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.08</v>
+        <v>4.7</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7718,34 +7718,34 @@
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
         <v>0.92</v>
@@ -7754,70 +7754,70 @@
         <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.08</v>
+        <v>97.72</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.46</v>
+        <v>5.71</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.85</v>
+        <v>56.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.69</v>
+        <v>10.72</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.69</v>
+        <v>12.36</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.92</v>
+        <v>7.64</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.39</v>
+        <v>50.36</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.69</v>
+        <v>12.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.46</v>
+        <v>18.72</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7923,46 +7923,46 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL18" t="n">
         <v>3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.17</v>
+        <v>37.86</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.67</v>
+        <v>42</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.83</v>
+        <v>16.57</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BH18" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP18" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU18" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
         <v>3.56</v>
@@ -8058,169 +8058,169 @@
         <v>3.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.64</v>
+        <v>3.77</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.06</v>
+        <v>5.58</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.14</v>
+        <v>5.61</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
         <v>1.84</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CN18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="CR18" t="n">
         <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="CT18" t="n">
         <v>2.86</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CV18" t="n">
         <v>1.92</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX18" t="n">
         <v>1.58</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DG18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>39</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="EC18" t="n">
         <v>2</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>89.92</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="EA18" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="EB18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="EC18" t="n">
-        <v>2.08</v>
       </c>
     </row>
     <row r="19">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0.14</v>
@@ -8722,115 +8722,115 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AI20" t="n">
-        <v>92.67</v>
+        <v>90.86</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK20" t="n">
         <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>37.17</v>
+        <v>39.14</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="AR20" t="n">
-        <v>10.67</v>
+        <v>11.43</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>44.67</v>
+        <v>43.29</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.33</v>
+        <v>9.57</v>
       </c>
       <c r="BB20" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.67</v>
+        <v>18.71</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BF20" t="n">
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BH20" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.92</v>
+        <v>6.07</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,19 +8839,19 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV20" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX20" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
         <v>3.83</v>
@@ -8860,67 +8860,67 @@
         <v>3.78</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.12</v>
+        <v>6.28</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.72</v>
+        <v>6.9</v>
       </c>
       <c r="CE20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CK20" t="n">
         <v>1.35</v>
-      </c>
-      <c r="CF20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CG20" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="CH20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CI20" t="n">
-        <v>2</v>
-      </c>
-      <c r="CJ20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CK20" t="n">
-        <v>1.36</v>
       </c>
       <c r="CL20" t="n">
         <v>1.73</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CT20" t="n">
         <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV20" t="n">
         <v>2.13</v>
@@ -8932,88 +8932,88 @@
         <v>1.5</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.54</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.92</v>
+        <v>88.28</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.39</v>
+        <v>42.07</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.7</v>
+        <v>10.58</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.92</v>
+        <v>11.28</v>
       </c>
       <c r="DR20" t="n">
         <v>8.93</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.85</v>
+        <v>43.22</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.77</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.16</v>
+        <v>6.29</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="EA20" t="n">
         <v>19</v>
@@ -9022,7 +9022,7 @@
         <v>1.18</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="21">
@@ -9032,94 +9032,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>99.67</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K21" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>43.5</v>
+        <v>40.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="P21" t="n">
-        <v>12.83</v>
+        <v>13.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>9.57</v>
       </c>
       <c r="R21" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>50.67</v>
+        <v>50.57</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>11</v>
+        <v>10.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,70 +9203,70 @@
         <v>2.57</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.08</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU21" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV21" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CC21" t="n">
         <v>5.81</v>
@@ -9275,34 +9275,34 @@
         <v>6.42</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI21" t="n">
         <v>1.89</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CN21" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CO21" t="n">
         <v>1.31</v>
@@ -9311,7 +9311,7 @@
         <v>1.98</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
@@ -9335,97 +9335,97 @@
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DH21" t="n">
-        <v>94.54000000000001</v>
+        <v>94.36</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DK21" t="n">
         <v>3.08</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM21" t="n">
-        <v>41.77</v>
+        <v>40.57</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DP21" t="n">
-        <v>14</v>
+        <v>14.36</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.08</v>
+        <v>10.28</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.46</v>
+        <v>47.64</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.380000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.31</v>
+        <v>6.14</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="EA21" t="n">
-        <v>20</v>
+        <v>19.78</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>109</v>
+        <v>106.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>58.43</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.14</v>
+        <v>11.38</v>
       </c>
       <c r="R2" t="n">
-        <v>6.43</v>
+        <v>6.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.57</v>
+        <v>55.25</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.57</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.57</v>
+        <v>22.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.43</v>
@@ -1550,64 +1550,64 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.07</v>
+        <v>9.73</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
         <v>3.69</v>
@@ -1625,46 +1625,46 @@
         <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG2" t="n">
         <v>3.16</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK2" t="n">
         <v>1.34</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO2" t="n">
         <v>1.24</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CT2" t="n">
         <v>3.12</v>
@@ -1673,10 +1673,10 @@
         <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1694,64 +1694,64 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.56999999999999</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.28</v>
+        <v>51.4</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.07</v>
+        <v>7.27</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.22</v>
+        <v>52.27</v>
       </c>
       <c r="DW2" t="n">
         <v>0.07000000000000001</v>
@@ -1760,19 +1760,19 @@
         <v>13.07</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.93</v>
+        <v>20.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>90.43000000000001</v>
+        <v>89.12</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.57</v>
+        <v>58.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.57</v>
+        <v>11.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.14</v>
+        <v>55.75</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.43</v>
+        <v>17.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL3" t="n">
         <v>0.93</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO3" t="n">
         <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
         <v>1.46</v>
@@ -2013,67 +2013,67 @@
         <v>1.47</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="CC3" t="n">
         <v>1.87</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CE3" t="n">
         <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CV3" t="n">
         <v>1.93</v>
@@ -2082,67 +2082,67 @@
         <v>2.02</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.36</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.86</v>
+        <v>60.6</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.43</v>
+        <v>10.27</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.36</v>
+        <v>11.27</v>
       </c>
       <c r="DR3" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.22</v>
+        <v>58.8</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.43</v>
+        <v>14.47</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.07</v>
+        <v>5.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.86</v>
+        <v>17.74</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>91.86</v>
+        <v>89.62</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>42.43</v>
+        <v>41.88</v>
       </c>
       <c r="N4" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.43</v>
+        <v>16.62</v>
       </c>
       <c r="R4" t="n">
-        <v>6.57</v>
+        <v>7.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.29</v>
+        <v>49.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.57</v>
+        <v>6.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>14.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>1.71</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.36</v>
+        <v>10.07</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="CA4" t="n">
         <v>3.56</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC4" t="n">
         <v>3.12</v>
@@ -2431,121 +2431,121 @@
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL4" t="n">
         <v>1.73</v>
       </c>
-      <c r="CK4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1.7</v>
-      </c>
       <c r="CM4" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
         <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CY4" t="n">
         <v>1.77</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.43000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.72</v>
+        <v>44.27</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.93</v>
+        <v>16.53</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.07</v>
+        <v>8.26</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.93</v>
+        <v>52.54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.64</v>
+        <v>11.86</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.57</v>
+        <v>15.67</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.29</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.86</v>
+        <v>81.38</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.43</v>
+        <v>40.88</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.57</v>
+        <v>47.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.86</v>
+        <v>17.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.43</v>
+        <v>5.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>3.5</v>
@@ -2819,25 +2819,25 @@
         <v>3.57</v>
       </c>
       <c r="CA5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="CB5" t="n">
         <v>3.74</v>
       </c>
-      <c r="CB5" t="n">
-        <v>3.76</v>
-      </c>
       <c r="CC5" t="n">
-        <v>4.08</v>
+        <v>3.93</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH5" t="n">
         <v>1.47</v>
@@ -2855,31 +2855,31 @@
         <v>1.68</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV5" t="n">
         <v>2.2</v>
@@ -2891,97 +2891,97 @@
         <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.48</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DB5" t="n">
         <v>1.29</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DH5" t="n">
-        <v>84.93000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="DI5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.43</v>
+        <v>5.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.14</v>
+        <v>41.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.79</v>
+        <v>10.67</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.92</v>
+        <v>7.13</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.86</v>
+        <v>43.13</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.5</v>
+        <v>10.06</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.36</v>
+        <v>6.14</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.78</v>
+        <v>18.53</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="H6" t="n">
-        <v>93.14</v>
+        <v>93.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>51.86</v>
+        <v>56.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="R6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.29</v>
+        <v>50.75</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>14.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.43</v>
+        <v>8.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.86</v>
+        <v>14.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,19 +3162,19 @@
         <v>3.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.5</v>
+        <v>9.93</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
         <v>0.93</v>
@@ -3183,49 +3183,49 @@
         <v>0.93</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="CC6" t="n">
         <v>2.85</v>
@@ -3237,16 +3237,16 @@
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.62</v>
@@ -3255,7 +3255,7 @@
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM6" t="n">
         <v>2.56</v>
@@ -3264,127 +3264,127 @@
         <v>1.94</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
         <v>3.22</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CZ6" t="n">
         <v>2.38</v>
       </c>
-      <c r="CW6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.35</v>
-      </c>
       <c r="DA6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="DH6" t="n">
-        <v>92.64</v>
+        <v>92.73</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.36</v>
+        <v>54</v>
       </c>
       <c r="DN6" t="n">
         <v>0.93</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="DP6" t="n">
         <v>11.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.36</v>
+        <v>51.53</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.86</v>
+        <v>13.46</v>
       </c>
       <c r="DY6" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.58</v>
+        <v>16.53</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.56999999999999</v>
+        <v>80.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>34.14</v>
+        <v>33.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.14</v>
+        <v>11.88</v>
       </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.14</v>
+        <v>40.62</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.43</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG7" t="n">
         <v>3.07</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.210000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>3.07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.64</v>
+        <v>5.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY7" t="n">
         <v>5.77</v>
@@ -3625,31 +3625,31 @@
         <v>6.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.44</v>
+        <v>7.45</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.94</v>
@@ -3658,10 +3658,10 @@
         <v>1.41</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
         <v>2.08</v>
@@ -3670,10 +3670,10 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3697,13 +3697,13 @@
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.37</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB7" t="n">
         <v>1.34</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.22</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.86</v>
+        <v>3.27</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.79</v>
+        <v>34.53</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.08</v>
+        <v>9.93</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.64</v>
+        <v>11.07</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.86</v>
+        <v>40.13</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.14</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>102</v>
+        <v>102.38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.86</v>
+        <v>4.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>50.86</v>
+        <v>51.38</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59</v>
+        <v>59.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.43</v>
+        <v>13.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.859999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.43</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.02</v>
@@ -4028,40 +4028,40 @@
         <v>2.09</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="n">
         <v>3.89</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM8" t="n">
         <v>2.67</v>
@@ -4073,16 +4073,16 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
         <v>3.26</v>
@@ -4091,10 +4091,10 @@
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX8" t="n">
         <v>1.56</v>
@@ -4112,52 +4112,52 @@
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>103.93</v>
+        <v>104</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.08</v>
+        <v>5.67</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM8" t="n">
         <v>55.14</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.42</v>
+        <v>11.53</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.72</v>
+        <v>13.8</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.14</v>
+        <v>7.2</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.72</v>
+        <v>58.87</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.14</v>
+        <v>13.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.93</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="EA8" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>78</v>
+        <v>76.88</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.14</v>
+        <v>37.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.71</v>
+        <v>10.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.43</v>
+        <v>41.75</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.57</v>
+        <v>16.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.71</v>
+        <v>4.93</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="BR9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY9" t="n">
         <v>2.41</v>
@@ -4431,22 +4431,22 @@
         <v>2.48</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG9" t="n">
         <v>2.93</v>
@@ -4455,7 +4455,7 @@
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.79</v>
@@ -4464,7 +4464,7 @@
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM9" t="n">
         <v>2.6</v>
@@ -4476,10 +4476,10 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4497,103 +4497,103 @@
         <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
         <v>1.57</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.4</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DE9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.78</v>
+        <v>78.14</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.79</v>
+        <v>40.94</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.36</v>
+        <v>10.2</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.64</v>
+        <v>42.27</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.57</v>
+        <v>11.53</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.36</v>
+        <v>7.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.86</v>
+        <v>17.6</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>63</v>
+        <v>60.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
-        <v>9.710000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.29</v>
+        <v>14.38</v>
       </c>
       <c r="R10" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T10" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.29</v>
+        <v>48.25</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.43</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.29</v>
+        <v>20.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,70 +4774,70 @@
         <v>1.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP10" t="n">
         <v>3.93</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC10" t="n">
         <v>4.15</v>
@@ -4849,16 +4849,16 @@
         <v>1.4</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH10" t="n">
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.8</v>
@@ -4867,10 +4867,10 @@
         <v>1.41</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN10" t="n">
         <v>2.03</v>
@@ -4879,10 +4879,10 @@
         <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4897,7 +4897,7 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW10" t="n">
         <v>1.85</v>
@@ -4906,7 +4906,7 @@
         <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.42</v>
@@ -4924,79 +4924,79 @@
         <v>3.23</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.43000000000001</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="DL10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>52.72</v>
+        <v>51.93</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.36</v>
+        <v>10.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.93</v>
+        <v>13.07</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>44.14</v>
+        <v>43.93</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.64</v>
+        <v>7.53</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.29</v>
+        <v>20.34</v>
       </c>
       <c r="EB10" t="n">
         <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,61 +5006,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G11" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="H11" t="n">
-        <v>91.56999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="J11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="K11" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>11.57</v>
+        <v>10.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.29</v>
+        <v>54.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AB11" t="n">
         <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.14</v>
+        <v>21.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.43</v>
@@ -5180,67 +5180,67 @@
         <v>2.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="BI11" t="n">
         <v>2.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.07</v>
+        <v>5.27</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC11" t="n">
         <v>3.88</v>
@@ -5252,7 +5252,7 @@
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
         <v>2.91</v>
@@ -5273,7 +5273,7 @@
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN11" t="n">
         <v>2.14</v>
@@ -5285,7 +5285,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,22 +5300,22 @@
         <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
@@ -5324,49 +5324,49 @@
         <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.56999999999999</v>
+        <v>86.87</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.36</v>
+        <v>47.2</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.36</v>
+        <v>12.2</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.71</v>
+        <v>7.66</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.22</v>
+        <v>51.07</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.71</v>
+        <v>11.73</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.64</v>
+        <v>20.93</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>90.56999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="K12" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M12" t="n">
-        <v>41.14</v>
+        <v>40.38</v>
       </c>
       <c r="N12" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>11.14</v>
+        <v>11.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
       <c r="R12" t="n">
-        <v>8.43</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.71</v>
+        <v>44.75</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.71</v>
+        <v>15.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.29</v>
+        <v>10.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.43</v>
+        <v>16.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.43</v>
+        <v>7.53</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL12" t="n">
         <v>1.07</v>
       </c>
-      <c r="BK12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP12" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>80</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CA12" t="n">
         <v>3.71</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>92.86</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>3.72</v>
-      </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CC12" t="n">
         <v>4.85</v>
@@ -5652,10 +5652,10 @@
         <v>5.67</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG12" t="n">
         <v>2.98</v>
@@ -5664,7 +5664,7 @@
         <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.81</v>
@@ -5673,10 +5673,10 @@
         <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN12" t="n">
         <v>2</v>
@@ -5688,25 +5688,25 @@
         <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CR12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CU12" t="n">
         <v>1.43</v>
       </c>
-      <c r="CS12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="CV12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5715,94 +5715,94 @@
         <v>1.9</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
         <v>1.95</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
         <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.86</v>
+        <v>84</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.28</v>
+        <v>41.8</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
         <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.64</v>
+        <v>10.87</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13</v>
+        <v>13.13</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.220000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.14</v>
+        <v>46.07</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.28</v>
+        <v>12.27</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.58</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.86</v>
+        <v>16.34</v>
       </c>
       <c r="EB12" t="n">
         <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.14</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>109.14</v>
+        <v>107.38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>56.14</v>
+        <v>57.12</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.29</v>
+        <v>11.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>62.14</v>
+        <v>61.25</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.86</v>
+        <v>18.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.43</v>
+        <v>10.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.93</v>
       </c>
-      <c r="BM13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>1.56</v>
@@ -6043,169 +6043,169 @@
         <v>1.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="CE13" t="n">
         <v>1.26</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="DE13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.36</v>
+        <v>106.54</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.29</v>
+        <v>5.2</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>58.86</v>
+        <v>59.2</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.43</v>
+        <v>10.66</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.43</v>
+        <v>11.74</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.79</v>
+        <v>6.67</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.86</v>
+        <v>61.4</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.43</v>
+        <v>15.47</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.22</v>
+        <v>11.07</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.72</v>
+        <v>20.34</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>95.86</v>
+        <v>99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K14" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>60.71</v>
+        <v>62.62</v>
       </c>
       <c r="N14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="P14" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="S14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>57.86</v>
+        <v>58.62</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.71</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.43</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
         <v>0.29</v>
@@ -6386,70 +6386,70 @@
         <v>2.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.14</v>
+        <v>10.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.14</v>
+        <v>5.33</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.51</v>
+        <v>4.6</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.69</v>
+        <v>4.81</v>
       </c>
       <c r="CC14" t="n">
         <v>1.98</v>
@@ -6461,25 +6461,25 @@
         <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK14" t="n">
         <v>1.42</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM14" t="n">
         <v>2.7</v>
@@ -6488,31 +6488,31 @@
         <v>2.06</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6530,52 +6530,52 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.08</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.42</v>
+        <v>57.73</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.640000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.5</v>
+        <v>13.26</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.64</v>
+        <v>57.13</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.14</v>
+        <v>14.4</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.859999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>91</v>
+        <v>94.88</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="K16" t="n">
-        <v>7.29</v>
+        <v>7.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>53.14</v>
+        <v>54.75</v>
       </c>
       <c r="N16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>11.43</v>
+        <v>11.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.86</v>
+        <v>13.38</v>
       </c>
       <c r="R16" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.71</v>
+        <v>48.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>14.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.57</v>
+        <v>8.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0.29</v>
@@ -7192,70 +7192,70 @@
         <v>1.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.64</v>
+        <v>12.07</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.43</v>
+        <v>5.8</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.57</v>
+        <v>4.73</v>
       </c>
       <c r="BR16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.81</v>
+        <v>3.94</v>
       </c>
       <c r="CC16" t="n">
         <v>2.42</v>
@@ -7264,22 +7264,22 @@
         <v>2.5</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
@@ -7288,19 +7288,19 @@
         <v>1.65</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CO16" t="n">
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,10 +7315,10 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
@@ -7330,7 +7330,7 @@
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7345,76 +7345,76 @@
         <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="DH16" t="n">
-        <v>100.15</v>
+        <v>101.6</v>
       </c>
       <c r="DI16" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.93</v>
+        <v>6.13</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.78</v>
+        <v>58.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.93</v>
+        <v>10.8</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.72</v>
+        <v>11.6</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.14</v>
+        <v>6.07</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50</v>
+        <v>51.34</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.28</v>
+        <v>12.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.28</v>
+        <v>4.46</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.07</v>
+        <v>19.53</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7514,52 +7514,52 @@
         <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI17" t="n">
-        <v>90</v>
+        <v>90.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>45.57</v>
+        <v>44.88</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.43</v>
+        <v>14.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,73 +7571,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.43</v>
+        <v>49.75</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BD17" t="n">
-        <v>19</v>
+        <v>20.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.14</v>
+        <v>5.07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
         <v>2.41</v>
@@ -7655,67 +7655,67 @@
         <v>2.45</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.52</v>
+        <v>4.38</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
         <v>1.99</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK17" t="n">
         <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV17" t="n">
         <v>2.08</v>
@@ -7727,64 +7727,64 @@
         <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.35</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
         <v>3.2</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.72</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.71</v>
+        <v>5.53</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.22</v>
+        <v>55.14</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.72</v>
+        <v>11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.36</v>
+        <v>12.67</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.64</v>
+        <v>7.66</v>
       </c>
       <c r="DS17" t="n">
         <v>0.07000000000000001</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.36</v>
+        <v>50.94</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.5</v>
+        <v>12.13</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.72</v>
+        <v>19.4</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7923,46 +7923,46 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>87.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>37.86</v>
+        <v>36.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>42</v>
+        <v>41.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.57</v>
+        <v>16.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL18" t="n">
         <v>1.07</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BP18" t="n">
         <v>3.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY18" t="n">
         <v>3.56</v>
@@ -8058,40 +8058,40 @@
         <v>3.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.69</v>
+        <v>3.84</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.77</v>
+        <v>3.95</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.58</v>
+        <v>6.02</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.61</v>
+        <v>6.29</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK18" t="n">
         <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM18" t="n">
         <v>2.6</v>
@@ -8100,25 +8100,25 @@
         <v>2.02</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="CR18" t="n">
         <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="CT18" t="n">
         <v>2.86</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CV18" t="n">
         <v>1.92</v>
@@ -8142,52 +8142,52 @@
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.84999999999999</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
         <v>2.14</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM18" t="n">
-        <v>39</v>
+        <v>38.13</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.72</v>
+        <v>10.6</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.43</v>
+        <v>42</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.720000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.64</v>
+        <v>16.46</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>99.86</v>
+        <v>97.62</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="K19" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M19" t="n">
-        <v>56.86</v>
+        <v>58.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
-        <v>12.29</v>
+        <v>11.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.43</v>
+        <v>11.12</v>
       </c>
       <c r="R19" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.86</v>
+        <v>56.38</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.710000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>22.57</v>
+        <v>22</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.29</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.79</v>
+        <v>4.73</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC19" t="n">
         <v>3.94</v>
@@ -8476,10 +8476,10 @@
         <v>1.33</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH19" t="n">
         <v>1.48</v>
@@ -8488,7 +8488,7 @@
         <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
         <v>1.3</v>
@@ -8497,7 +8497,7 @@
         <v>1.61</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CN19" t="n">
         <v>2.35</v>
@@ -8506,25 +8506,25 @@
         <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU19" t="n">
         <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW19" t="n">
         <v>1.72</v>
@@ -8535,58 +8535,58 @@
       </c>
       <c r="CZ19" t="inlineStr"/>
       <c r="DA19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.36</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DK19" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.43</v>
+        <v>48.73</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.79</v>
+        <v>11.54</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.36</v>
+        <v>10.27</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8604,22 +8604,22 @@
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.29</v>
+        <v>6.4</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.28</v>
+        <v>20.13</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0.14</v>
@@ -8722,115 +8722,115 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>90.86</v>
+        <v>88.38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK20" t="n">
         <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>39.14</v>
+        <v>40.12</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.57</v>
+        <v>10.62</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>43.29</v>
+        <v>41.88</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.57</v>
+        <v>10.12</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.71</v>
+        <v>18</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BF20" t="n">
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BH20" t="n">
-        <v>12.07</v>
+        <v>12.33</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BN20" t="n">
         <v>1.93</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP20" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>6.07</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>5.86</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,19 +8839,19 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
         <v>3.83</v>
@@ -8860,169 +8860,169 @@
         <v>3.78</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.9</v>
+        <v>6.71</v>
       </c>
       <c r="CE20" t="n">
         <v>1.34</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL20" t="n">
         <v>1.73</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO20" t="n">
         <v>1.24</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CT20" t="n">
         <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CY20" t="n">
         <v>1.66</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="DE20" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.28</v>
+        <v>87.13</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ20" t="n">
         <v>1.86</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.58</v>
+        <v>5.6</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.07</v>
+        <v>42.4</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.58</v>
+        <v>10.4</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.28</v>
+        <v>11.4</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.93</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.22</v>
+        <v>42.47</v>
       </c>
       <c r="DW20" t="n">
         <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.859999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.29</v>
+        <v>6.47</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="EA20" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,139 +6708,139 @@
         <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>101.71</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.57</v>
+        <v>44.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.14</v>
+        <v>10.38</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.71</v>
+        <v>52.25</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.14</v>
+        <v>14</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.86</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.29</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM15" t="n">
         <v>1</v>
       </c>
-      <c r="BM15" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BN15" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.57</v>
+        <v>4.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.11</v>
@@ -6855,40 +6855,40 @@
         <v>4.07</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.61</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
@@ -6897,13 +6897,13 @@
         <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CT15" t="n">
         <v>3.31</v>
@@ -6912,106 +6912,106 @@
         <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DH15" t="n">
-        <v>105.64</v>
+        <v>103.93</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.35</v>
+        <v>4.66</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="DM15" t="n">
-        <v>50.28</v>
+        <v>51.6</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.57</v>
+        <v>12.93</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.43</v>
+        <v>7.33</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.42</v>
+        <v>54.07</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.28</v>
+        <v>16.07</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.14</v>
+        <v>10.6</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.14</v>
+        <v>5.47</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.22</v>
+        <v>20.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -9032,94 +9032,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
-        <v>98.56999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>40.86</v>
+        <v>41.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O21" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="P21" t="n">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.57</v>
+        <v>10.25</v>
       </c>
       <c r="R21" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>50.57</v>
+        <v>48.88</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.14</v>
+        <v>20.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,70 +9203,70 @@
         <v>2.57</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.289999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP21" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU21" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV21" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CC21" t="n">
         <v>5.81</v>
@@ -9275,61 +9275,61 @@
         <v>6.42</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL21" t="n">
         <v>1.88</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CT21" t="n">
         <v>2.97</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
@@ -9338,94 +9338,94 @@
         <v>1.87</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="DH21" t="n">
-        <v>94.36</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.57</v>
+        <v>40.8</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.36</v>
+        <v>14.53</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.28</v>
+        <v>10.6</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.22</v>
+        <v>7.07</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.64</v>
+        <v>46.93</v>
       </c>
       <c r="DW21" t="n">
         <v>0.14</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.78</v>
+        <v>19.74</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G3" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>112.29</v>
+        <v>112.25</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="K3" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>63.14</v>
+        <v>65.25</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.71</v>
+        <v>12.25</v>
       </c>
       <c r="R3" t="n">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62.29</v>
+        <v>63.12</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.57</v>
+        <v>15.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.43</v>
+        <v>10.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.29</v>
+        <v>18.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.42</v>
+        <v>4.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.55</v>
+        <v>4.86</v>
       </c>
       <c r="CC3" t="n">
         <v>1.87</v>
@@ -2025,43 +2025,43 @@
         <v>2.01</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
         <v>1.44</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CN3" t="n">
         <v>2.08</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2076,106 +2076,106 @@
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="CX3" t="n">
         <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.49</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.93000000000001</v>
+        <v>100.68</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.6</v>
+        <v>61.82</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.27</v>
+        <v>10.06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.27</v>
+        <v>11.57</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.07</v>
+        <v>4.81</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.8</v>
+        <v>59.44</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.47</v>
+        <v>14.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.130000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.33</v>
+        <v>5.12</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.74</v>
+        <v>17.88</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" t="n">
-        <v>87</v>
+        <v>87.38</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>47</v>
+        <v>45.88</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.43</v>
+        <v>16.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.57</v>
+        <v>9.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>55.57</v>
+        <v>56</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.43</v>
+        <v>7.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.14</v>
+        <v>16.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.54</v>
@@ -2416,16 +2416,16 @@
         <v>2.63</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="CE4" t="n">
         <v>1.37</v>
@@ -2434,13 +2434,13 @@
         <v>2.74</v>
       </c>
       <c r="CG4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2452,10 +2452,10 @@
         <v>1.73</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2464,7 +2464,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,73 +2479,73 @@
         <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.56</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.4</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.27</v>
+        <v>43.88</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.53</v>
+        <v>16.69</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.26</v>
+        <v>8.18</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.54</v>
+        <v>52.94</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.86</v>
+        <v>11.56</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.6</v>
+        <v>7.32</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.67</v>
+        <v>15.44</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>89</v>
+        <v>93.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.14</v>
-      </c>
       <c r="U5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>38.14</v>
+        <v>40.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.14</v>
+        <v>10.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.71</v>
+        <v>20.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.2</v>
+        <v>9.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.67</v>
+        <v>5.38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="CA5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CB5" t="n">
         <v>3.72</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>3.93</v>
@@ -2831,43 +2831,43 @@
         <v>3.91</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CO5" t="n">
         <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2882,106 +2882,106 @@
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
         <v>1.88</v>
       </c>
-      <c r="DD5" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>84.94</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>2</v>
-      </c>
       <c r="DK5" t="n">
-        <v>5.47</v>
+        <v>5.12</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.8</v>
+        <v>41.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.13</v>
+        <v>7.19</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.13</v>
+        <v>44</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.06</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.14</v>
+        <v>6.06</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.53</v>
+        <v>18.94</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>92.14</v>
+        <v>93.88</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>50.86</v>
+        <v>52</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.14</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.71</v>
+        <v>10.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.43</v>
+        <v>52.25</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.71</v>
+        <v>12.88</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.29</v>
+        <v>17.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.93</v>
+        <v>9.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.6</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY6" t="n">
         <v>2.2</v>
@@ -3222,34 +3222,34 @@
         <v>2.33</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK6" t="n">
         <v>1.46</v>
@@ -3258,19 +3258,19 @@
         <v>1.86</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
@@ -3294,97 +3294,97 @@
         <v>1.57</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.38</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DH6" t="n">
-        <v>92.73</v>
+        <v>93.56</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.34</v>
+        <v>5.13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>54</v>
+        <v>54.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.86</v>
+        <v>12.06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.73</v>
+        <v>10.57</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.53</v>
+        <v>51.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.46</v>
+        <v>13.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>8.93</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.8</v>
+        <v>4.56</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.53</v>
+        <v>15.93</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G7" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>80.86</v>
+        <v>87.38</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>2.14</v>
+        <v>3.12</v>
       </c>
       <c r="L7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>35.43</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="R7" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.88</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.07</v>
+        <v>5.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.77</v>
+        <v>5.52</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.18</v>
+        <v>5.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="CC7" t="n">
         <v>7.45</v>
@@ -3637,19 +3637,19 @@
         <v>7.9</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF7" t="n">
         <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.94</v>
@@ -3661,133 +3661,133 @@
         <v>1.77</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO7" t="n">
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CT7" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV7" t="n">
         <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB7" t="n">
         <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.27</v>
+        <v>3.68</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.53</v>
+        <v>36.38</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.93</v>
+        <v>9.81</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.93</v>
+        <v>9.81</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.07</v>
+        <v>10.82</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.13</v>
+        <v>40.94</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.27</v>
+        <v>8.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.93</v>
+        <v>17.31</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="H8" t="n">
-        <v>105.86</v>
+        <v>105</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K8" t="n">
-        <v>7.29</v>
+        <v>6.88</v>
       </c>
       <c r="L8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M8" t="n">
-        <v>59.43</v>
+        <v>56.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>11.14</v>
+        <v>11.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="R8" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.43</v>
+        <v>58.38</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.86</v>
+        <v>15.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.71</v>
+        <v>15.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,64 +3968,64 @@
         <v>2.38</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="CA8" t="n">
         <v>3.9</v>
@@ -4043,16 +4043,16 @@
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.68</v>
@@ -4061,136 +4061,136 @@
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
         <v>2.67</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY8" t="n">
         <v>1.77</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
         <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>104</v>
+        <v>103.69</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.14</v>
+        <v>53.82</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.53</v>
+        <v>11.63</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.8</v>
+        <v>13.62</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.87</v>
+        <v>58.82</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.93</v>
+        <v>14.12</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.2</v>
+        <v>16.62</v>
       </c>
       <c r="EB8" t="n">
         <v>1.64</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>79.56999999999999</v>
+        <v>79.88</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M9" t="n">
-        <v>44.43</v>
+        <v>44.38</v>
       </c>
       <c r="N9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.14</v>
+        <v>10.75</v>
       </c>
       <c r="R9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.86</v>
+        <v>42.25</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.14</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.57</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.88</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.07</v>
+        <v>8.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.93</v>
+        <v>4.69</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CC9" t="n">
         <v>3.45</v>
@@ -4443,157 +4443,157 @@
         <v>3.61</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CT9" t="n">
         <v>3.06</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
         <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.4</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.14</v>
+        <v>78.38</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.94</v>
+        <v>41.13</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.2</v>
+        <v>10.13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.73</v>
+        <v>10.57</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.27</v>
+        <v>42</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.53</v>
+        <v>11.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.26</v>
+        <v>7.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.6</v>
+        <v>17.62</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.12</v>
@@ -4693,52 +4693,52 @@
         <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.86</v>
+        <v>87.88</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>42.43</v>
+        <v>42.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.57</v>
+        <v>11.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>39</v>
+        <v>39.38</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.86</v>
+        <v>8.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.29</v>
+        <v>20.38</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.53</v>
+        <v>4.69</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
         <v>2.36</v>
@@ -4834,22 +4834,22 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="CE10" t="n">
         <v>1.4</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG10" t="n">
         <v>2.87</v>
@@ -4867,7 +4867,7 @@
         <v>1.41</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM10" t="n">
         <v>2.67</v>
@@ -4879,22 +4879,22 @@
         <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV10" t="n">
         <v>2.04</v>
@@ -4903,67 +4903,67 @@
         <v>1.85</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
         <v>1.86</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DA10" t="n">
         <v>2</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
         <v>3.23</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.93000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.93</v>
+        <v>51.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DQ10" t="n">
         <v>13.07</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.2</v>
+        <v>7.37</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.93</v>
+        <v>43.82</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.6</v>
+        <v>10.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.53</v>
+        <v>7.62</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.34</v>
+        <v>20.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5096,52 +5096,52 @@
         <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>81.56999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.71</v>
+        <v>39.75</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.43</v>
+        <v>12.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT11" t="n">
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.14</v>
+        <v>47.12</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.2</v>
+        <v>10.44</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.27</v>
+        <v>5.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
         <v>3.21</v>
@@ -5237,25 +5237,25 @@
         <v>3.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="CC11" t="n">
         <v>3.65</v>
       </c>
-      <c r="CC11" t="n">
-        <v>3.88</v>
-      </c>
       <c r="CD11" t="n">
-        <v>4.27</v>
+        <v>3.99</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
@@ -5267,106 +5267,106 @@
         <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.87</v>
+        <v>86.06</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.2</v>
+        <v>45.88</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DP11" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="DQ11" t="n">
         <v>12</v>
       </c>
-      <c r="DQ11" t="n">
-        <v>12.2</v>
-      </c>
       <c r="DR11" t="n">
-        <v>7.66</v>
+        <v>7.82</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.07</v>
+        <v>50.81</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.73</v>
+        <v>11.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.93</v>
+        <v>7.56</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.93</v>
+        <v>20.81</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.38</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>73.14</v>
+        <v>76.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.43</v>
+        <v>44.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.43</v>
+        <v>12.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.57</v>
+        <v>47</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.86</v>
+        <v>6.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.29</v>
+        <v>16.88</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.53</v>
+        <v>7.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
         <v>3.03</v>
@@ -5640,22 +5640,22 @@
         <v>3.22</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.67</v>
+        <v>5.41</v>
       </c>
       <c r="CE12" t="n">
         <v>1.38</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CG12" t="n">
         <v>2.98</v>
@@ -5664,7 +5664,7 @@
         <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.81</v>
@@ -5673,13 +5673,13 @@
         <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO12" t="n">
         <v>1.29</v>
@@ -5688,7 +5688,7 @@
         <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5712,97 +5712,97 @@
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DH12" t="n">
-        <v>84</v>
+        <v>85.12</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.8</v>
+        <v>42.25</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.87</v>
+        <v>10.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.13</v>
+        <v>12.93</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.07</v>
+        <v>45.88</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.27</v>
+        <v>12.57</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.34</v>
+        <v>16.63</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G13" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H13" t="n">
-        <v>105.57</v>
+        <v>104.38</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K13" t="n">
-        <v>5.57</v>
+        <v>5.12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M13" t="n">
-        <v>61.57</v>
+        <v>58.88</v>
       </c>
       <c r="N13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>9.57</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.43</v>
+        <v>11</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>6.88</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>61.57</v>
+        <v>60</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.86</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.57</v>
+        <v>20.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.33</v>
+        <v>9.94</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.93</v>
+        <v>5.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="CC13" t="n">
         <v>1.98</v>
@@ -6061,22 +6061,22 @@
         <v>2.27</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CH13" t="n">
         <v>1.62</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM13" t="n">
         <v>2.9</v>
@@ -6109,7 +6109,7 @@
         <v>2.33</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6127,52 +6127,52 @@
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD13" t="n">
         <v>2.52</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.54</v>
+        <v>105.88</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>59.2</v>
+        <v>58</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.66</v>
+        <v>10.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.74</v>
+        <v>11.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.67</v>
+        <v>7.06</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.4</v>
+        <v>60.62</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.47</v>
+        <v>15.62</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.07</v>
+        <v>11.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.34</v>
+        <v>19.63</v>
       </c>
       <c r="EB13" t="n">
         <v>1.72</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6305,139 +6305,139 @@
         <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>102</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>100.29</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AL14" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>52.14</v>
+        <v>49.38</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AP14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU14" t="n">
         <v>2</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>55.43</v>
+        <v>56.25</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.57</v>
+        <v>11.88</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.859999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.57</v>
+        <v>16.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.2</v>
+        <v>9.81</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.87</v>
+        <v>4.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.33</v>
+        <v>5.19</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY14" t="n">
         <v>1.46</v>
@@ -6446,16 +6446,16 @@
         <v>1.46</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CE14" t="n">
         <v>1.27</v>
@@ -6464,16 +6464,16 @@
         <v>2.3</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI14" t="n">
         <v>2.18</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK14" t="n">
         <v>1.42</v>
@@ -6482,16 +6482,16 @@
         <v>1.76</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.43</v>
@@ -6500,115 +6500,115 @@
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.8</v>
+        <v>5.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>57.73</v>
+        <v>56</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.26</v>
+        <v>13.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.13</v>
+        <v>57.44</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.4</v>
+        <v>13.94</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.07</v>
+        <v>8.56</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.4</v>
+        <v>18.88</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="15">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,52 +7111,52 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>109.29</v>
+        <v>106</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>62.43</v>
+        <v>60.25</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.29</v>
+        <v>54.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.57</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.43</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.14</v>
+        <v>20.38</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.07</v>
+        <v>11.88</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.8</v>
+        <v>5.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
         <v>2.25</v>
@@ -7252,43 +7252,43 @@
         <v>2.27</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN16" t="n">
         <v>2.23</v>
@@ -7297,22 +7297,22 @@
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
         <v>2.21</v>
@@ -7324,13 +7324,13 @@
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7339,82 +7339,82 @@
         <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="DH16" t="n">
-        <v>101.6</v>
+        <v>100.44</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>58.33</v>
+        <v>57.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.8</v>
+        <v>10.75</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.07</v>
+        <v>6.12</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.34</v>
+        <v>51.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.6</v>
+        <v>12.19</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.130000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.53</v>
+        <v>19.69</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G17" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>105.43</v>
+        <v>104.62</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M17" t="n">
-        <v>66.86</v>
+        <v>65.38</v>
       </c>
       <c r="N17" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>10.86</v>
+        <v>10.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.29</v>
+        <v>10.75</v>
       </c>
       <c r="R17" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="S17" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>52.29</v>
+        <v>51.75</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.14</v>
+        <v>15.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.43</v>
+        <v>18.88</v>
       </c>
       <c r="AD17" t="n">
         <v>1.72</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7595,49 +7595,49 @@
         <v>1.88</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.4</v>
+        <v>10.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC17" t="n">
         <v>4.38</v>
@@ -7670,10 +7670,10 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7691,28 +7691,28 @@
         <v>1.74</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU17" t="n">
         <v>1.45</v>
@@ -7727,97 +7727,97 @@
         <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.35</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.59999999999999</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.53</v>
+        <v>5.38</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.14</v>
+        <v>55.13</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>11</v>
+        <v>10.87</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.67</v>
+        <v>12.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.66</v>
+        <v>7.56</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.94</v>
+        <v>50.75</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.13</v>
+        <v>12.31</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.4</v>
+        <v>19.56</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>87.70999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L18" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>40.14</v>
+        <v>42.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="P18" t="n">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>8.43</v>
+        <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>42.86</v>
+        <v>43.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.29</v>
+        <v>10.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.71</v>
+        <v>17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>1.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CC18" t="n">
         <v>6.02</v>
@@ -8076,7 +8076,7 @@
         <v>2.89</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH18" t="n">
         <v>1.41</v>
@@ -8085,25 +8085,25 @@
         <v>1.85</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK18" t="n">
         <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO18" t="n">
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
         <v>3.55</v>
@@ -8115,112 +8115,112 @@
         <v>2.92</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CU18" t="n">
         <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX18" t="n">
         <v>1.58</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
         <v>2.05</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.45999999999999</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DM18" t="n">
-        <v>38.13</v>
+        <v>39.32</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.6</v>
+        <v>10.56</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42</v>
+        <v>42.25</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.6</v>
+        <v>9.31</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.6</v>
+        <v>6.44</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.46</v>
+        <v>16.62</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8323,49 +8323,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>72.86</v>
+        <v>77.62</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL19" t="n">
-        <v>6.14</v>
+        <v>5.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN19" t="n">
-        <v>38</v>
+        <v>38.25</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.43</v>
+        <v>49.75</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BD19" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.6</v>
+        <v>11.25</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.12</v>
@@ -8461,31 +8461,31 @@
         <v>2.32</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="CC19" t="n">
         <v>3.78</v>
       </c>
-      <c r="CB19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>3.94</v>
-      </c>
       <c r="CD19" t="n">
-        <v>4.21</v>
+        <v>4.02</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
@@ -8503,31 +8503,31 @@
         <v>2.35</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="inlineStr"/>
       <c r="CY19" t="n">
@@ -8538,55 +8538,55 @@
         <v>2.37</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.06999999999999</v>
+        <v>87.62</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.73</v>
+        <v>48.18</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.27</v>
+        <v>10.43</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.27</v>
+        <v>8.31</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.14</v>
+        <v>53.06</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.4</v>
+        <v>6.31</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.13</v>
+        <v>20.38</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="20">
@@ -8629,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="H20" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K20" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="L20" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M20" t="n">
-        <v>45</v>
+        <v>44.12</v>
       </c>
       <c r="N20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>10.29</v>
+        <v>11.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.14</v>
+        <v>11.5</v>
       </c>
       <c r="R20" t="n">
-        <v>8.289999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,28 +8695,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>43.14</v>
+        <v>42.88</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.29</v>
+        <v>19.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8800,37 +8800,37 @@
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BH20" t="n">
-        <v>12.33</v>
+        <v>12.06</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,31 +8839,31 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV20" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CC20" t="n">
         <v>6.15</v>
@@ -8872,22 +8872,22 @@
         <v>6.71</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH20" t="n">
         <v>1.49</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK20" t="n">
         <v>1.36</v>
@@ -8896,13 +8896,13 @@
         <v>1.73</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP20" t="n">
         <v>1.8</v>
@@ -8923,7 +8923,7 @@
         <v>1.54</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW20" t="n">
         <v>1.77</v>
@@ -8938,7 +8938,7 @@
         <v>2.57</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
@@ -8950,46 +8950,46 @@
         <v>2.92</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.13</v>
+        <v>87.94</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.4</v>
+        <v>42.12</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.4</v>
+        <v>10.88</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.4</v>
+        <v>11.56</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DS20" t="n">
         <v>0.06</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>42.47</v>
+        <v>42.38</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.6</v>
+        <v>18.56</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="21">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0.12</v>
@@ -9125,49 +9125,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" t="n">
-        <v>90.14</v>
+        <v>88</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK21" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.29</v>
+        <v>37.62</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21" t="n">
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.86</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9179,82 +9179,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.71</v>
+        <v>43</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>7.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.71</v>
+        <v>5.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.43</v>
+        <v>17.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP21" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV21" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY21" t="n">
         <v>3.71</v>
@@ -9263,55 +9263,55 @@
         <v>3.94</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.81</v>
+        <v>4.16</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.81</v>
+        <v>7.39</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.42</v>
+        <v>8.99</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM21" t="n">
         <v>2.67</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
@@ -9326,73 +9326,73 @@
         <v>1.45</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.39</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="DH21" t="n">
-        <v>92.59999999999999</v>
+        <v>91.38</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.8</v>
+        <v>39.44</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.53</v>
+        <v>14.56</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.6</v>
+        <v>10.43</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.07</v>
+        <v>7.75</v>
       </c>
       <c r="DS21" t="n">
         <v>0.06</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.93</v>
+        <v>45.94</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>9</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.13</v>
+        <v>5.81</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.74</v>
+        <v>19.25</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="EC21" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1469,52 +1469,52 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>88.14</v>
+        <v>90.38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.14</v>
+        <v>46.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AP2" t="n">
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.71</v>
+        <v>11.38</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.71</v>
+        <v>8.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.86</v>
+        <v>48.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.57</v>
+        <v>12.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.71</v>
+        <v>5.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.73</v>
+        <v>9.69</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
         <v>2.14</v>
@@ -1610,34 +1610,34 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="CE2" t="n">
         <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK2" t="n">
         <v>1.34</v>
@@ -1652,37 +1652,37 @@
         <v>2.21</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
         <v>3.12</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.48</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.93000000000001</v>
+        <v>98.44</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.46</v>
+        <v>5.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.4</v>
+        <v>51.12</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.07</v>
+        <v>11.38</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.27</v>
+        <v>7.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.27</v>
+        <v>51.68</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.07</v>
+        <v>13.12</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.27</v>
+        <v>8.06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.8</v>
+        <v>5.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.25</v>
+        <v>42.38</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         <v>4.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19</v>
+        <v>19.12</v>
       </c>
       <c r="AD9" t="n">
         <v>1.49</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42</v>
+        <v>42.06</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>4.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.62</v>
+        <v>17.69</v>
       </c>
       <c r="EB9" t="n">
         <v>1.34</v>
@@ -5562,10 +5562,10 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="BC12" t="n">
         <v>3.12</v>
@@ -5574,7 +5574,7 @@
         <v>16.88</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BF12" t="n">
         <v>1.12</v>
@@ -5787,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.57</v>
+        <v>12.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.81</v>
@@ -5799,7 +5799,7 @@
         <v>16.63</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
         <v>1.62</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.25</v>
+        <v>56.12</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.44</v>
+        <v>57.37</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>109.57</v>
+        <v>107.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="K15" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>58.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>10.14</v>
+        <v>10.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.14</v>
+        <v>13.12</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.14</v>
+        <v>56.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.43</v>
+        <v>19.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.43</v>
+        <v>21.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.12</v>
@@ -6789,70 +6789,70 @@
         <v>1.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU15" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CC15" t="n">
         <v>2.82</v>
@@ -6861,22 +6861,22 @@
         <v>2.97</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK15" t="n">
         <v>1.38</v>
@@ -6885,34 +6885,34 @@
         <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CT15" t="n">
         <v>3.31</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CW15" t="n">
         <v>1.64</v>
@@ -6921,97 +6921,97 @@
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.51</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.93</v>
+        <v>103.25</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.27</v>
+        <v>10.57</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.93</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.33</v>
+        <v>7.12</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54.07</v>
+        <v>54.25</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.07</v>
+        <v>16.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.6</v>
+        <v>10.94</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.47</v>
+        <v>5.69</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.4</v>
+        <v>20.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.25</v>
+        <v>54.12</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.12</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.5</v>
+        <v>51.44</v>
       </c>
       <c r="DW16" t="n">
         <v>0.12</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>43.25</v>
+        <v>43.38</v>
       </c>
       <c r="Y18" t="n">
         <v>0.12</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.25</v>
+        <v>42.32</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>106.5</v>
+        <v>106.56</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K2" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>56.89</v>
       </c>
       <c r="N2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="R2" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="S2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.25</v>
+        <v>56.44</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>13.78</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.619999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.88</v>
+        <v>4.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.5</v>
+        <v>22.89</v>
       </c>
       <c r="AD2" t="n">
         <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF2" t="n">
         <v>0.38</v>
@@ -1550,70 +1550,70 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.69</v>
+        <v>9.59</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
         <v>1.88</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT2" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="CC2" t="n">
         <v>4.22</v>
@@ -1622,19 +1622,19 @@
         <v>4.61</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG2" t="n">
         <v>3.2</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.66</v>
@@ -1646,7 +1646,7 @@
         <v>1.66</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CN2" t="n">
         <v>2.21</v>
@@ -1655,16 +1655,16 @@
         <v>1.23</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
         <v>3.12</v>
@@ -1673,10 +1673,10 @@
         <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1694,52 +1694,52 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.44</v>
+        <v>98.95</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.12</v>
+        <v>51.88</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.94</v>
+        <v>12.82</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.38</v>
+        <v>11.35</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DS2" t="n">
         <v>0.12</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.68</v>
+        <v>52.52</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.12</v>
+        <v>13.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.06</v>
+        <v>20.41</v>
       </c>
       <c r="EB2" t="n">
         <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.12</v>
+        <v>92.44</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL3" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.38</v>
+        <v>57.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.12</v>
+        <v>10.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.88</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.75</v>
+        <v>56.78</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.5</v>
+        <v>13.44</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.25</v>
+        <v>17.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY3" t="n">
         <v>1.42</v>
@@ -2013,169 +2013,169 @@
         <v>1.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
         <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CN3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CW3" t="n">
         <v>2.08</v>
       </c>
-      <c r="CO3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>2.07</v>
-      </c>
       <c r="CX3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.68</v>
+        <v>101.76</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.82</v>
+        <v>61.12</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.06</v>
+        <v>9.76</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.57</v>
+        <v>11</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.44</v>
+        <v>59.76</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.56</v>
+        <v>14.47</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.88</v>
+        <v>17.82</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>81.38</v>
+        <v>83.44</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.88</v>
+        <v>41.11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>11.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.25</v>
+        <v>9.56</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.5</v>
+        <v>48.56</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>5.44</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.75</v>
+        <v>9.59</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
         <v>3.3</v>
@@ -2819,25 +2819,25 @@
         <v>3.4</v>
       </c>
       <c r="CA5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CB5" t="n">
         <v>3.7</v>
       </c>
-      <c r="CB5" t="n">
-        <v>3.72</v>
-      </c>
       <c r="CC5" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.91</v>
+        <v>3.71</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
@@ -2849,25 +2849,25 @@
         <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL5" t="n">
         <v>1.7</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2888,100 +2888,100 @@
         <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="DE5" t="n">
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.31999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="DL5" t="n">
         <v>0.18</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.63</v>
+        <v>41.71</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.5</v>
+        <v>10.76</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.19</v>
+        <v>7.06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44</v>
+        <v>44.77</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.869999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.06</v>
+        <v>5.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.81</v>
+        <v>3.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.94</v>
+        <v>19.12</v>
       </c>
       <c r="EB5" t="n">
         <v>1.2</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>93.25</v>
+        <v>95.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K6" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>56.75</v>
+        <v>57.67</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P6" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.75</v>
+        <v>11.22</v>
       </c>
       <c r="R6" t="n">
-        <v>9.5</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.75</v>
+        <v>51.44</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.12</v>
+        <v>14.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.75</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.12</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,64 +3162,64 @@
         <v>3.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.56</v>
+        <v>9.41</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CA6" t="n">
         <v>3.58</v>
@@ -3237,28 +3237,28 @@
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK6" t="n">
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN6" t="n">
         <v>1.96</v>
@@ -3270,13 +3270,13 @@
         <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CT6" t="n">
         <v>3.22</v>
@@ -3285,10 +3285,10 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX6" t="n">
         <v>1.57</v>
@@ -3306,52 +3306,52 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.56</v>
+        <v>94.53</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.38</v>
+        <v>55</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.57</v>
+        <v>10.82</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.19</v>
+        <v>8.06</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.5</v>
+        <v>51.82</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.5</v>
+        <v>13.65</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.93</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.93</v>
+        <v>16.29</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>80.38</v>
+        <v>80.78</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.75</v>
+        <v>34.11</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.88</v>
+        <v>12.56</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>40.62</v>
+        <v>39.89</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>16.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
         <v>1.12</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY7" t="n">
         <v>5.52</v>
@@ -3625,136 +3625,136 @@
         <v>5.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.45</v>
+        <v>7.34</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
         <v>1.41</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="CT7" t="n">
         <v>2.99</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX7" t="n">
         <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.38</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB7" t="n">
         <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.88</v>
+        <v>83.89</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.38</v>
+        <v>36.41</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.82</v>
+        <v>11.24</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.94</v>
+        <v>40.53</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.75</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.38</v>
+        <v>5.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.31</v>
+        <v>17.35</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AI8" t="n">
-        <v>102.38</v>
+        <v>101.89</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.38</v>
+        <v>50.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.88</v>
+        <v>12.11</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.25</v>
+        <v>58.56</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.119999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.62</v>
+        <v>17.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
         <v>1.98</v>
@@ -4028,61 +4028,61 @@
         <v>2.05</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF8" t="n">
         <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH8" t="n">
         <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.68</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
         <v>1.83</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
         <v>3.25</v>
@@ -4091,73 +4091,73 @@
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX8" t="n">
         <v>1.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DG8" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DH8" t="n">
-        <v>103.69</v>
+        <v>103.35</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM8" t="n">
-        <v>53.82</v>
+        <v>53.12</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.63</v>
+        <v>11.77</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.62</v>
+        <v>13.71</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.25</v>
+        <v>7.47</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.82</v>
+        <v>58.48</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.12</v>
+        <v>14.06</v>
       </c>
       <c r="DY8" t="n">
         <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.62</v>
+        <v>16.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AT9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
-        <v>76.88</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.62</v>
-      </c>
       <c r="AU9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.75</v>
+        <v>42.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.25</v>
+        <v>15.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.75</v>
+        <v>9.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.06</v>
+        <v>4.41</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY9" t="n">
         <v>2.62</v>
@@ -4431,91 +4431,91 @@
         <v>2.7</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="DD9" t="n">
         <v>3.15</v>
@@ -4524,76 +4524,76 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.38</v>
+        <v>78.3</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.68</v>
+        <v>3.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.13</v>
+        <v>40.77</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.57</v>
+        <v>10.29</v>
       </c>
       <c r="DR9" t="n">
         <v>8.18</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.06</v>
+        <v>42.35</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.81</v>
+        <v>11.65</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.69</v>
+        <v>17.11</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>102</v>
+        <v>100.22</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K10" t="n">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>60.25</v>
+        <v>57.33</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>10.62</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.38</v>
+        <v>13.44</v>
       </c>
       <c r="R10" t="n">
-        <v>4.62</v>
+        <v>5.11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>48.25</v>
+        <v>46.78</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>12.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.38</v>
+        <v>20.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,70 +4774,70 @@
         <v>1.62</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.56</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.69</v>
+        <v>4.53</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="CC10" t="n">
         <v>4.21</v>
@@ -4849,7 +4849,7 @@
         <v>1.4</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
         <v>2.87</v>
@@ -4858,34 +4858,34 @@
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO10" t="n">
         <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS10" t="n">
         <v>3.06</v>
@@ -4897,73 +4897,73 @@
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB10" t="n">
         <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.94</v>
+        <v>94.41</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="DL10" t="n">
         <v>0.12</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.25</v>
+        <v>50.23</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.81</v>
+        <v>10.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.07</v>
+        <v>12.64</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.37</v>
+        <v>7.47</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.82</v>
+        <v>43.3</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.62</v>
+        <v>10.29</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.62</v>
+        <v>7.41</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.38</v>
+        <v>20.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="H12" t="n">
-        <v>93.5</v>
+        <v>94.33</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.75</v>
+        <v>5.22</v>
       </c>
       <c r="L12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>40.38</v>
+        <v>41.56</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="P12" t="n">
-        <v>11.5</v>
+        <v>10.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.75</v>
+        <v>13.67</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>7.56</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.75</v>
+        <v>45.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.25</v>
+        <v>15.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.38</v>
+        <v>18.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.25</v>
+        <v>7.65</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CC12" t="n">
         <v>4.73</v>
@@ -5652,13 +5652,13 @@
         <v>5.41</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CH12" t="n">
         <v>1.42</v>
@@ -5667,109 +5667,109 @@
         <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CO12" t="n">
         <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CR12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CU12" t="n">
         <v>1.42</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.43</v>
       </c>
       <c r="CV12" t="n">
         <v>1.98</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
         <v>3.25</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
         <v>1.06</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.12</v>
+        <v>86.06</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.94</v>
+        <v>4.23</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.25</v>
+        <v>42.76</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.75</v>
+        <v>10.41</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.94</v>
+        <v>7.71</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.88</v>
+        <v>46.3</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.62</v>
+        <v>13.06</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.81</v>
+        <v>4.06</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.63</v>
+        <v>17.65</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>107.38</v>
+        <v>109.22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.12</v>
+        <v>59.11</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.62</v>
+        <v>11.11</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>61.25</v>
+        <v>61.67</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.25</v>
+        <v>13.56</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.25</v>
+        <v>9.56</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.38</v>
+        <v>19.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG13" t="n">
         <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.94</v>
+        <v>9.82</v>
       </c>
       <c r="BI13" t="n">
         <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL13" t="n">
         <v>1.06</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP13" t="n">
         <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
         <v>1.58</v>
@@ -6043,28 +6043,28 @@
         <v>1.66</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI13" t="n">
         <v>2.27</v>
@@ -6073,25 +6073,25 @@
         <v>1.61</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
@@ -6109,13 +6109,13 @@
         <v>2.33</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.49</v>
@@ -6127,52 +6127,52 @@
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="DE13" t="n">
         <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.88</v>
+        <v>106.94</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.94</v>
+        <v>11.83</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.06</v>
+        <v>6.94</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.62</v>
+        <v>60.88</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.62</v>
+        <v>15.18</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.25</v>
+        <v>10.83</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.63</v>
+        <v>20.06</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H14" t="n">
-        <v>99</v>
+        <v>103.44</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="K14" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M14" t="n">
-        <v>62.62</v>
+        <v>63.22</v>
       </c>
       <c r="N14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="P14" t="n">
-        <v>9.5</v>
+        <v>10.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.62</v>
+        <v>12.33</v>
       </c>
       <c r="R14" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>58.62</v>
+        <v>59.44</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6386,70 +6386,70 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.81</v>
+        <v>9.59</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU14" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW14" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="CC14" t="n">
         <v>1.97</v>
@@ -6458,124 +6458,124 @@
         <v>2.05</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.5</v>
+        <v>102.76</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM14" t="n">
-        <v>56</v>
+        <v>56.71</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.380000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.12</v>
+        <v>12.94</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.37</v>
+        <v>57.88</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.94</v>
+        <v>14.12</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.56</v>
+        <v>8.59</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.88</v>
+        <v>18.47</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="15">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="H16" t="n">
-        <v>94.88</v>
+        <v>94.67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>54.75</v>
+        <v>53.89</v>
       </c>
       <c r="N16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="P16" t="n">
-        <v>11.12</v>
+        <v>11.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.38</v>
+        <v>13.44</v>
       </c>
       <c r="R16" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>48.75</v>
+        <v>48.56</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.38</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.75</v>
+        <v>8.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="AC16" t="n">
         <v>19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
         <v>0.25</v>
@@ -7192,70 +7192,70 @@
         <v>1.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.88</v>
+        <v>11.76</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.62</v>
+        <v>5.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="BR16" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CC16" t="n">
         <v>2.39</v>
@@ -7267,7 +7267,7 @@
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG16" t="n">
         <v>3.11</v>
@@ -7276,16 +7276,16 @@
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM16" t="n">
         <v>2.91</v>
@@ -7297,28 +7297,28 @@
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CT16" t="n">
         <v>3.21</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
@@ -7336,85 +7336,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD16" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DH16" t="n">
-        <v>100.44</v>
+        <v>100</v>
       </c>
       <c r="DI16" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DK16" t="n">
         <v>6.12</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.5</v>
+        <v>56.88</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.75</v>
+        <v>10.88</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.5</v>
+        <v>11.64</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.12</v>
+        <v>6.41</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.44</v>
+        <v>51.18</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.19</v>
+        <v>12.12</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.88</v>
+        <v>7.76</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.69</v>
+        <v>19.65</v>
       </c>
       <c r="EB16" t="n">
         <v>1.48</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,136 +7920,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BL18" t="n">
         <v>1</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>87.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT18" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU18" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY18" t="n">
         <v>3.54</v>
@@ -8058,31 +8058,31 @@
         <v>3.92</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC18" t="n">
-        <v>6.02</v>
+        <v>5.83</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.29</v>
+        <v>6.1</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CG18" t="n">
         <v>2.89</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>2.88</v>
       </c>
       <c r="CH18" t="n">
         <v>1.41</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.89</v>
@@ -8094,37 +8094,37 @@
         <v>1.82</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN18" t="n">
         <v>2.03</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CU18" t="n">
         <v>1.44</v>
       </c>
       <c r="CV18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CW18" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1.95</v>
       </c>
       <c r="CX18" t="n">
         <v>1.58</v>
@@ -8142,7 +8142,7 @@
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DD18" t="n">
         <v>3.17</v>
@@ -8151,43 +8151,43 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.31999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.32</v>
+        <v>40.35</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.81</v>
+        <v>10.12</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.56</v>
+        <v>8.59</v>
       </c>
       <c r="DS18" t="n">
         <v>0.12</v>
@@ -8199,25 +8199,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.31</v>
+        <v>9.59</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="EC18" t="n">
         <v>2.06</v>
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H19" t="n">
-        <v>97.62</v>
+        <v>95.22</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5.56</v>
       </c>
       <c r="L19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>58.12</v>
+        <v>56.44</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>11.75</v>
+        <v>11.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="R19" t="n">
-        <v>6.5</v>
+        <v>6.11</v>
       </c>
       <c r="S19" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.38</v>
+        <v>54</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.38</v>
+        <v>10.89</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>7.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>21.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8404,67 +8404,67 @@
         <v>2.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.25</v>
+        <v>11.06</v>
       </c>
       <c r="BI19" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC19" t="n">
         <v>3.78</v>
@@ -8476,7 +8476,7 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG19" t="n">
         <v>3.15</v>
@@ -8485,10 +8485,10 @@
         <v>1.47</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK19" t="n">
         <v>1.3</v>
@@ -8497,7 +8497,7 @@
         <v>1.61</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CN19" t="n">
         <v>2.35</v>
@@ -8509,7 +8509,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8524,10 +8524,10 @@
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="inlineStr"/>
       <c r="CY19" t="n">
@@ -8538,7 +8538,7 @@
         <v>2.37</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC19" t="n">
         <v>1.84</v>
@@ -8550,43 +8550,43 @@
         <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.62</v>
+        <v>86.94</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.88</v>
+        <v>5.65</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.18</v>
+        <v>47.88</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO19" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.62</v>
+        <v>11.47</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.43</v>
+        <v>10.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.31</v>
+        <v>8</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.06</v>
+        <v>52</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.31</v>
+        <v>6.58</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.38</v>
+        <v>20</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0.25</v>
@@ -8722,115 +8722,115 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI20" t="n">
-        <v>88.38</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL20" t="n">
-        <v>5</v>
+        <v>4.44</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.12</v>
+        <v>37.56</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.62</v>
+        <v>12.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.62</v>
+        <v>10.56</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>41</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BM20" t="n">
         <v>1.12</v>
       </c>
-      <c r="AV20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BN20" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.94</v>
+        <v>5.82</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>5.76</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
@@ -8839,19 +8839,19 @@
         <v>100</v>
       </c>
       <c r="BT20" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU20" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX20" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY20" t="n">
         <v>3.76</v>
@@ -8860,43 +8860,43 @@
         <v>3.73</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.19</v>
+        <v>4.43</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.15</v>
+        <v>6.91</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.71</v>
+        <v>7.52</v>
       </c>
       <c r="CE20" t="n">
         <v>1.33</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN20" t="n">
         <v>2.18</v>
@@ -8905,91 +8905,91 @@
         <v>1.23</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="CT20" t="n">
         <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX20" t="n">
         <v>1.48</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.57</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DE20" t="n">
         <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.94</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.56</v>
+        <v>5.23</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.12</v>
+        <v>40.65</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.88</v>
+        <v>10.82</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.56</v>
+        <v>11.82</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS20" t="n">
         <v>0.06</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>42.38</v>
+        <v>41.88</v>
       </c>
       <c r="DW20" t="n">
         <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.56</v>
+        <v>18.29</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="21">
@@ -9032,94 +9032,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="H21" t="n">
-        <v>94.75</v>
+        <v>94.67</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="K21" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>41.25</v>
+        <v>41.44</v>
       </c>
       <c r="N21" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>14.12</v>
+        <v>13.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.25</v>
+        <v>10.67</v>
       </c>
       <c r="R21" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48.88</v>
+        <v>48.22</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.88</v>
+        <v>20.89</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,70 +9203,70 @@
         <v>2.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP21" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU21" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="CC21" t="n">
         <v>7.39</v>
@@ -9284,34 +9284,34 @@
         <v>2.94</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL21" t="n">
         <v>1.86</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO21" t="n">
         <v>1.29</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
@@ -9326,22 +9326,22 @@
         <v>1.45</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
@@ -9350,49 +9350,49 @@
         <v>1.97</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.38</v>
+        <v>91.53</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.44</v>
+        <v>39.64</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.56</v>
+        <v>14.41</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.43</v>
+        <v>10.65</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.75</v>
+        <v>7.58</v>
       </c>
       <c r="DS21" t="n">
         <v>0.06</v>
@@ -9404,22 +9404,22 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.94</v>
+        <v>45.76</v>
       </c>
       <c r="DW21" t="n">
         <v>0.12</v>
       </c>
       <c r="DX21" t="n">
-        <v>8.630000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.81</v>
+        <v>5.88</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.25</v>
+        <v>19.35</v>
       </c>
       <c r="EB21" t="n">
         <v>1.03</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>89.62</v>
+        <v>85.44</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>41.88</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.62</v>
+        <v>16.44</v>
       </c>
       <c r="R4" t="n">
-        <v>7.12</v>
+        <v>7.78</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.88</v>
+        <v>49.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
         <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.38</v>
+        <v>13.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,67 +2356,67 @@
         <v>1.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BH4" t="n">
         <v>9.94</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT4" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB4" t="n">
         <v>3.68</v>
@@ -2428,28 +2428,28 @@
         <v>2.87</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM4" t="n">
         <v>2.78</v>
@@ -2458,52 +2458,52 @@
         <v>2.13</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CT4" t="n">
         <v>3.08</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY4" t="n">
         <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
@@ -2512,40 +2512,40 @@
         <v>1.06</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.5</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DK4" t="n">
         <v>5.06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.88</v>
+        <v>42.24</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.38</v>
+        <v>10.41</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.69</v>
+        <v>16.59</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.18</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.94</v>
+        <v>52.35</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.56</v>
+        <v>11.59</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.44</v>
+        <v>15</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="5">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>91.5</v>
+        <v>89.33</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="J11" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6.25</v>
+        <v>5.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>52</v>
+        <v>51.78</v>
       </c>
       <c r="N11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>10.75</v>
+        <v>10.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="R11" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.62</v>
+        <v>21.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0.5</v>
@@ -5177,70 +5177,70 @@
         <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.44</v>
+        <v>10.18</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.44</v>
+        <v>5.24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.37</v>
+        <v>3.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC11" t="n">
         <v>3.65</v>
@@ -5255,7 +5255,7 @@
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
@@ -5267,7 +5267,7 @@
         <v>1.8</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL11" t="n">
         <v>1.68</v>
@@ -5285,7 +5285,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,16 +5300,16 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.48</v>
@@ -5327,79 +5327,79 @@
         <v>3.38</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.06</v>
+        <v>85.23</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.12</v>
+        <v>4.88</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.88</v>
+        <v>46.12</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.75</v>
+        <v>11.35</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.82</v>
+        <v>7.88</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.81</v>
+        <v>50.76</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.38</v>
+        <v>11.35</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.56</v>
+        <v>7.71</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.81</v>
+        <v>20.65</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="12">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6708,139 +6708,139 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI15" t="n">
-        <v>99</v>
+        <v>101.78</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.25</v>
+        <v>46.78</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.38</v>
+        <v>10.78</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.75</v>
+        <v>12.89</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.5</v>
+        <v>7.89</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>52.25</v>
+        <v>52.78</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14</v>
+        <v>14.11</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.19</v>
+        <v>9.24</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BJ15" t="n">
         <v>0.88</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU15" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY15" t="n">
         <v>2.07</v>
@@ -6849,16 +6849,16 @@
         <v>2.09</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="CE15" t="n">
         <v>1.29</v>
@@ -6867,7 +6867,7 @@
         <v>2.35</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
@@ -6879,7 +6879,7 @@
         <v>1.6</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
         <v>1.67</v>
@@ -6894,40 +6894,40 @@
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CT15" t="n">
         <v>3.31</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
@@ -6939,79 +6939,79 @@
         <v>2.6</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.25</v>
+        <v>104.47</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.5</v>
+        <v>52.41</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.57</v>
+        <v>10.77</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.12</v>
+        <v>6.88</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54.25</v>
+        <v>54.41</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.62</v>
+        <v>16.53</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.31</v>
+        <v>20.23</v>
       </c>
       <c r="EB15" t="n">
         <v>1.82</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7514,52 +7514,52 @@
         <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.75</v>
+        <v>94.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.88</v>
+        <v>44.56</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.75</v>
+        <v>13.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,73 +7571,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49.75</v>
+        <v>49.78</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.62</v>
+        <v>6.11</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.25</v>
+        <v>20.44</v>
       </c>
       <c r="BE17" t="n">
         <v>1.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.12</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO17" t="n">
         <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.88</v>
+        <v>4.71</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY17" t="n">
         <v>2.45</v>
@@ -7655,16 +7655,16 @@
         <v>2.48</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.38</v>
+        <v>4.23</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
@@ -7673,7 +7673,7 @@
         <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7682,10 +7682,10 @@
         <v>1.99</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL17" t="n">
         <v>1.74</v>
@@ -7703,25 +7703,25 @@
         <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT17" t="n">
         <v>3.09</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX17" t="n">
         <v>1.59</v>
@@ -7742,49 +7742,49 @@
         <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.68000000000001</v>
+        <v>99.23</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.13</v>
+        <v>54.36</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.87</v>
+        <v>10.76</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.75</v>
+        <v>12.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.75</v>
+        <v>50.71</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.31</v>
+        <v>12.29</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.25</v>
+        <v>8.35</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.56</v>
+        <v>19.71</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="18">
@@ -8242,7 +8242,7 @@
         <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
         <v>2.33</v>
@@ -8254,7 +8254,7 @@
         <v>-0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="K19" t="n">
         <v>5.56</v>
@@ -8317,7 +8317,7 @@
         <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
         <v>2.23</v>
@@ -8562,7 +8562,7 @@
         <v>-0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="DK19" t="n">
         <v>5.65</v>
@@ -8619,7 +8619,7 @@
         <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1469,52 +1469,52 @@
         <v>1.89</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>4.56</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.38</v>
+        <v>91.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.5</v>
+        <v>6.56</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.25</v>
+        <v>50.44</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>12.89</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.38</v>
+        <v>11.11</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.12</v>
+        <v>48.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.75</v>
+        <v>13.56</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.25</v>
+        <v>5.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.62</v>
+        <v>17.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.59</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.12</v>
+        <v>5.61</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT2" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW2" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY2" t="n">
         <v>2.06</v>
@@ -1610,28 +1610,28 @@
         <v>2.17</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.22</v>
+        <v>4.09</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.61</v>
+        <v>4.44</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
         <v>2.2</v>
@@ -1643,19 +1643,19 @@
         <v>1.34</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO2" t="n">
         <v>1.23</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.81</v>
@@ -1664,13 +1664,13 @@
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
         <v>2.28</v>
@@ -1682,97 +1682,97 @@
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.48</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
         <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.95</v>
+        <v>99.06</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.35</v>
+        <v>5.89</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.88</v>
+        <v>53.66</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.82</v>
+        <v>12.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.35</v>
+        <v>11.22</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.52</v>
+        <v>52.44</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.3</v>
+        <v>13.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.82</v>
+        <v>5.11</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.41</v>
+        <v>20.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="H3" t="n">
-        <v>112.25</v>
+        <v>109.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>65.25</v>
+        <v>65.78</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="R3" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63.12</v>
+        <v>62</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.62</v>
+        <v>16.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.88</v>
+        <v>11.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.5</v>
+        <v>18.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>1.42</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1.43</v>
-      </c>
       <c r="CA3" t="n">
-        <v>4.69</v>
+        <v>4.73</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="CC3" t="n">
         <v>1.84</v>
@@ -2028,154 +2028,154 @@
         <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CH3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK3" t="n">
         <v>1.46</v>
       </c>
-      <c r="CI3" t="n">
+      <c r="CL3" t="n">
         <v>1.81</v>
       </c>
-      <c r="CJ3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CM3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CT3" t="n">
         <v>3.17</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV3" t="n">
         <v>1.89</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.76</v>
+        <v>101.11</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.12</v>
+        <v>61.61</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.76</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.76</v>
+        <v>59.39</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.47</v>
+        <v>15</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.529999999999999</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.82</v>
+        <v>17.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>87.38</v>
+        <v>81.33</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>45.88</v>
+        <v>43.78</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.75</v>
+        <v>16.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>56</v>
+        <v>53.89</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.38</v>
+        <v>3.89</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.5</v>
+        <v>16.11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.94</v>
+        <v>10.11</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.06</v>
+        <v>3.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>2.5</v>
@@ -2416,22 +2416,22 @@
         <v>2.56</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="CC4" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2446,25 +2446,25 @@
         <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO4" t="n">
         <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,73 +2479,73 @@
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CY4" t="n">
         <v>1.77</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CZ4" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.34999999999999</v>
+        <v>83.38</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.24</v>
+        <v>41.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.41</v>
+        <v>10.28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.59</v>
+        <v>16.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.35</v>
+        <v>51.5</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.59</v>
+        <v>11.56</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.35</v>
+        <v>7.11</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.24</v>
+        <v>4.44</v>
       </c>
       <c r="EA4" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>93.25</v>
+        <v>90.89</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>42.38</v>
+        <v>42.56</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="S5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>40.5</v>
+        <v>41.44</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.62</v>
+        <v>11.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.38</v>
+        <v>20.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.59</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.18</v>
+        <v>4.72</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
         <v>3.7</v>
@@ -2834,10 +2834,10 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
@@ -2846,19 +2846,19 @@
         <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
         <v>1.39</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CO5" t="n">
         <v>1.25</v>
@@ -2867,16 +2867,16 @@
         <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU5" t="n">
         <v>1.49</v>
@@ -2897,7 +2897,7 @@
         <v>2.41</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
@@ -2906,19 +2906,19 @@
         <v>1.9</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.06</v>
+        <v>87.16</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,58 +2927,58 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.71</v>
+        <v>41.84</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.76</v>
+        <v>10.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.06</v>
+        <v>7.16</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.77</v>
+        <v>45</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.12</v>
+        <v>19.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.22</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI6" t="n">
-        <v>93.88</v>
+        <v>92.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>52</v>
+        <v>49.33</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.88</v>
+        <v>7.11</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.25</v>
+        <v>51.67</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.75</v>
+        <v>17.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.16</v>
@@ -3222,169 +3222,169 @@
         <v>2.28</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.08</v>
+        <v>3.71</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU6" t="n">
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.57</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.38</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="DH6" t="n">
-        <v>94.53</v>
+        <v>93.89</v>
       </c>
       <c r="DI6" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DM6" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>12.06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.82</v>
+        <v>10.61</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.82</v>
+        <v>51.56</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.65</v>
+        <v>13.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.29</v>
+        <v>16.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>87.38</v>
+        <v>90.89</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>41.22</v>
       </c>
       <c r="N7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="R7" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>41.25</v>
+        <v>42.78</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>6.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.62</v>
+        <v>19.44</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.78</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.94</v>
+        <v>10.06</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.76</v>
+        <v>4.44</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.52</v>
+        <v>5.32</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.92</v>
+        <v>5.68</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="CC7" t="n">
         <v>7.34</v>
@@ -3640,40 +3640,40 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CM7" t="n">
         <v>2.69</v>
       </c>
-      <c r="CG7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.71</v>
-      </c>
       <c r="CN7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3688,28 +3688,28 @@
         <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
         <v>2.02</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="DD7" t="n">
         <v>3.05</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.89</v>
+        <v>85.84</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.41</v>
+        <v>37.66</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.880000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.53</v>
+        <v>41.34</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.23</v>
+        <v>5.83</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.23</v>
+        <v>3.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.35</v>
+        <v>17.83</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>106.22</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M8" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="H8" t="n">
-        <v>105</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M8" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.88</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.38</v>
+        <v>58.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.12</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.62</v>
+        <v>14.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.65</v>
+        <v>9.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.24</v>
+        <v>3.94</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CA8" t="n">
         <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CC8" t="n">
         <v>2.04</v>
@@ -4046,7 +4046,7 @@
         <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.5</v>
@@ -4061,13 +4061,13 @@
         <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM8" t="n">
         <v>2.68</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
@@ -4097,16 +4097,16 @@
         <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
@@ -4115,49 +4115,49 @@
         <v>1.78</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="DH8" t="n">
-        <v>103.35</v>
+        <v>104.06</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>53.12</v>
+        <v>54.56</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.77</v>
+        <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.71</v>
+        <v>13.39</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.47</v>
+        <v>7.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.48</v>
+        <v>58.72</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
         <v>14.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.47</v>
+        <v>15.89</v>
       </c>
       <c r="EB8" t="n">
         <v>1.63</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4693,52 +4693,52 @@
         <v>2.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>87.88</v>
+        <v>90.22</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>42.25</v>
+        <v>42.33</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>39.38</v>
+        <v>40</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="BC10" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.38</v>
+        <v>19.44</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.289999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.53</v>
+        <v>4.22</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>2.78</v>
@@ -4834,55 +4834,55 @@
         <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.49</v>
+        <v>4.23</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP10" t="n">
         <v>2.02</v>
       </c>
-      <c r="CO10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>2</v>
-      </c>
       <c r="CQ10" t="n">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
@@ -4897,28 +4897,28 @@
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
         <v>3.26</v>
@@ -4927,43 +4927,43 @@
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.41</v>
+        <v>95.22</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.23</v>
+        <v>49.83</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.41</v>
+        <v>10.28</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.64</v>
+        <v>12.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.47</v>
+        <v>7.61</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.3</v>
+        <v>43.39</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.29</v>
+        <v>10.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.3</v>
+        <v>19.83</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5096,52 +5096,52 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI11" t="n">
-        <v>80.62</v>
+        <v>83.78</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.75</v>
+        <v>42.56</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.12</v>
+        <v>48.11</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.62</v>
+        <v>6.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>20.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.18</v>
+        <v>10.11</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
         <v>3.11</v>
@@ -5237,46 +5237,46 @@
         <v>3.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.99</v>
+        <v>3.82</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK11" t="n">
         <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
@@ -5285,7 +5285,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,10 +5300,10 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5315,7 +5315,7 @@
         <v>2.48</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
@@ -5324,49 +5324,49 @@
         <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>85.23</v>
+        <v>86.56</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.12</v>
+        <v>47.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.35</v>
+        <v>11.16</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.88</v>
+        <v>11.66</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.88</v>
+        <v>7.84</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.76</v>
+        <v>51.06</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.35</v>
+        <v>11.56</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.71</v>
+        <v>7.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.65</v>
+        <v>20.83</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F13" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="H13" t="n">
-        <v>104.38</v>
+        <v>109.33</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K13" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="L13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>58.88</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P13" t="n">
-        <v>9.380000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="R13" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>60</v>
+        <v>60.78</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.88</v>
+        <v>19.89</v>
       </c>
       <c r="AD13" t="n">
         <v>1.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.44</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.41</v>
+        <v>4.53</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -6055,25 +6055,25 @@
         <v>2.13</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF13" t="n">
         <v>2.28</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL13" t="n">
         <v>1.64</v>
@@ -6082,22 +6082,22 @@
         <v>2.91</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT13" t="n">
         <v>3.32</v>
@@ -6106,73 +6106,73 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.94</v>
+        <v>109.28</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>59</v>
+        <v>60.56</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.83</v>
+        <v>11.89</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.94</v>
+        <v>6.89</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.88</v>
+        <v>61.22</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.18</v>
+        <v>15.12</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.83</v>
+        <v>10.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.06</v>
+        <v>19.61</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.22</v>
@@ -6305,16 +6305,16 @@
         <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>102</v>
+        <v>103.11</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -6323,121 +6323,121 @@
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.38</v>
+        <v>50.33</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.62</v>
+        <v>12.78</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.12</v>
+        <v>57.22</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.88</v>
+        <v>12.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.75</v>
+        <v>16.67</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BF14" t="n">
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT14" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
         <v>1.42</v>
@@ -6446,25 +6446,25 @@
         <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF14" t="n">
         <v>2.28</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH14" t="n">
         <v>1.6</v>
@@ -6476,13 +6476,13 @@
         <v>1.7</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN14" t="n">
         <v>2.06</v>
@@ -6494,7 +6494,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
@@ -6509,22 +6509,22 @@
         <v>1.65</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6536,46 +6536,46 @@
         <v>2.48</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.76</v>
+        <v>103.28</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.71</v>
+        <v>56.78</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.76</v>
+        <v>9.94</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.94</v>
+        <v>12.56</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.88</v>
+        <v>58.33</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.12</v>
+        <v>14.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.59</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.47</v>
+        <v>18.34</v>
       </c>
       <c r="EB14" t="n">
         <v>1.69</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>107.5</v>
+        <v>103.44</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="K15" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="L15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M15" t="n">
-        <v>58.75</v>
+        <v>54.56</v>
       </c>
       <c r="N15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.12</v>
+        <v>12.33</v>
       </c>
       <c r="R15" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.25</v>
+        <v>53.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.25</v>
+        <v>18.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.88</v>
+        <v>12.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.12</v>
+        <v>21</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6789,70 +6789,70 @@
         <v>1.44</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.24</v>
+        <v>9.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM15" t="n">
         <v>1</v>
       </c>
-      <c r="BM15" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BN15" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV15" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CC15" t="n">
         <v>2.84</v>
@@ -6864,19 +6864,19 @@
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
@@ -6885,7 +6885,7 @@
         <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CN15" t="n">
         <v>2.14</v>
@@ -6897,7 +6897,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6912,10 +6912,10 @@
         <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
@@ -6942,43 +6942,43 @@
         <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DH15" t="n">
-        <v>104.47</v>
+        <v>102.61</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.71</v>
+        <v>4.56</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM15" t="n">
-        <v>52.41</v>
+        <v>50.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.77</v>
+        <v>10.67</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13</v>
+        <v>12.61</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.88</v>
+        <v>6.94</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54.41</v>
+        <v>53.22</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.53</v>
+        <v>16.11</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.83</v>
+        <v>10.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.23</v>
+        <v>20.22</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7111,52 +7111,52 @@
         <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>106</v>
+        <v>112.56</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.75</v>
+        <v>5.44</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN16" t="n">
-        <v>60.25</v>
+        <v>64.11</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AS16" t="n">
         <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.12</v>
+        <v>55.56</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="BC16" t="n">
         <v>3</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.38</v>
+        <v>19.89</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.76</v>
+        <v>11.83</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.53</v>
+        <v>5.61</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
         <v>2.3</v>
@@ -7252,55 +7252,55 @@
         <v>2.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN16" t="n">
         <v>2.23</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7315,10 +7315,10 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
@@ -7336,85 +7336,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="DH16" t="n">
-        <v>100</v>
+        <v>103.62</v>
       </c>
       <c r="DI16" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.12</v>
+        <v>6.39</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.88</v>
+        <v>59</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.88</v>
+        <v>10.56</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.64</v>
+        <v>11.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.18</v>
+        <v>52.06</v>
       </c>
       <c r="DW16" t="n">
         <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.12</v>
+        <v>12.34</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.76</v>
+        <v>8.06</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.65</v>
+        <v>19.44</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="H17" t="n">
-        <v>104.62</v>
+        <v>102.22</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="K17" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>65.38</v>
+        <v>61.78</v>
       </c>
       <c r="N17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P17" t="n">
-        <v>10.62</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.75</v>
+        <v>11.22</v>
       </c>
       <c r="R17" t="n">
-        <v>6.62</v>
+        <v>6.78</v>
       </c>
       <c r="S17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.62</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7595,49 +7595,49 @@
         <v>2.11</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CC17" t="n">
         <v>4.23</v>
@@ -7670,40 +7670,40 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL17" t="n">
         <v>1.74</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7718,22 +7718,22 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
@@ -7748,43 +7748,43 @@
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="DH17" t="n">
-        <v>99.23</v>
+        <v>98.33</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.36</v>
+        <v>53.17</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.76</v>
+        <v>10.44</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.41</v>
+        <v>12.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.53</v>
+        <v>7.56</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.71</v>
+        <v>49.78</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.35</v>
+        <v>8.16</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.71</v>
+        <v>19.56</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="18">
@@ -8629,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G20" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="H20" t="n">
-        <v>87.5</v>
+        <v>88.11</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K20" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>44.12</v>
+        <v>44.67</v>
       </c>
       <c r="N20" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="P20" t="n">
-        <v>11.25</v>
+        <v>10.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="R20" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,28 +8695,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>42.88</v>
+        <v>43</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.38</v>
+        <v>6.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.12</v>
+        <v>19.11</v>
       </c>
       <c r="AD20" t="n">
         <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8800,70 +8800,70 @@
         <v>1.89</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="BH20" t="n">
-        <v>11.71</v>
+        <v>11.56</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="BT20" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU20" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV20" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="BZ20" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="CA20" t="n">
         <v>3.73</v>
       </c>
-      <c r="CA20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="CB20" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="CC20" t="n">
         <v>6.91</v>
@@ -8875,37 +8875,37 @@
         <v>1.33</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH20" t="n">
         <v>1.5</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK20" t="n">
         <v>1.35</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CO20" t="n">
         <v>1.23</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ20" t="n">
         <v>2.93</v>
@@ -8926,7 +8926,7 @@
         <v>2.14</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX20" t="n">
         <v>1.48</v>
@@ -8944,52 +8944,52 @@
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>86.18000000000001</v>
+        <v>86.56</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>40.65</v>
+        <v>41.12</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.82</v>
+        <v>10.66</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.82</v>
+        <v>11.61</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.300000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS20" t="n">
         <v>0.06</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>41.88</v>
+        <v>42</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.29</v>
+        <v>18.33</v>
       </c>
       <c r="EB20" t="n">
         <v>1.17</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="21">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0.11</v>
@@ -9125,49 +9125,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>88</v>
+        <v>87.33</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN21" t="n">
-        <v>37.62</v>
+        <v>37.11</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14.78</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.62</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.119999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9179,82 +9179,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43</v>
+        <v>41.89</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.38</v>
+        <v>7.56</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.62</v>
+        <v>17.44</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.119999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP21" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV21" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY21" t="n">
         <v>3.67</v>
@@ -9263,28 +9263,28 @@
         <v>3.91</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="CC21" t="n">
-        <v>7.39</v>
+        <v>7.79</v>
       </c>
       <c r="CD21" t="n">
-        <v>8.99</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="CE21" t="n">
         <v>1.38</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI21" t="n">
         <v>1.89</v>
@@ -9296,37 +9296,37 @@
         <v>1.45</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CT21" t="n">
         <v>2.97</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW21" t="n">
         <v>1.97</v>
@@ -9335,64 +9335,64 @@
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB21" t="n">
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.53</v>
+        <v>91</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.64</v>
+        <v>39.28</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.41</v>
+        <v>14.34</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.65</v>
+        <v>10.34</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.58</v>
+        <v>7.83</v>
       </c>
       <c r="DS21" t="n">
         <v>0.06</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.76</v>
+        <v>45.06</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.88</v>
+        <v>5.84</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.35</v>
+        <v>19.17</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -3409,7 +3409,7 @@
         <v>0.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>90.89</v>
@@ -3421,10 +3421,10 @@
         <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="M7" t="n">
         <v>41.22</v>
@@ -3433,7 +3433,7 @@
         <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
         <v>9.779999999999999</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>42.78</v>
+        <v>42.67</v>
       </c>
       <c r="Y7" t="n">
         <v>0.11</v>
@@ -3475,7 +3475,7 @@
         <v>2.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.44</v>
+        <v>19.56</v>
       </c>
       <c r="AD7" t="n">
         <v>1.05</v>
@@ -3568,7 +3568,7 @@
         <v>2.94</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="BI7" t="n">
         <v>2.94</v>
@@ -3592,10 +3592,10 @@
         <v>1.28</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.78</v>
+        <v>4.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>94.44</v>
@@ -3721,7 +3721,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="DH7" t="n">
         <v>85.84</v>
@@ -3733,10 +3733,10 @@
         <v>1.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
         <v>37.66</v>
@@ -3745,7 +3745,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="DP7" t="n">
         <v>9.779999999999999</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.34</v>
+        <v>41.28</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
@@ -3781,7 +3781,7 @@
         <v>3.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.83</v>
+        <v>17.89</v>
       </c>
       <c r="EB7" t="n">
         <v>1.06</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="H9" t="n">
-        <v>79.88</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M9" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>42.38</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.06</v>
+        <v>8.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BR9" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="CA9" t="n">
         <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC9" t="n">
         <v>3.37</v>
@@ -4446,7 +4446,7 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG9" t="n">
         <v>2.93</v>
@@ -4455,13 +4455,13 @@
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL9" t="n">
         <v>1.79</v>
@@ -4476,10 +4476,10 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4494,106 +4494,106 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
         <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
         <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.3</v>
+        <v>81.44</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.77</v>
+        <v>42.72</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.29</v>
+        <v>10.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.35</v>
+        <v>43.44</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.65</v>
+        <v>11.84</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.47</v>
+        <v>7.78</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.11</v>
+        <v>17.33</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="10">
@@ -4699,7 +4699,7 @@
         <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
         <v>90.22</v>
@@ -4714,7 +4714,7 @@
         <v>3.44</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="AN10" t="n">
         <v>42.33</v>
@@ -4723,7 +4723,7 @@
         <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ10" t="n">
         <v>10.67</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>40</v>
+        <v>40.11</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
@@ -4777,7 +4777,7 @@
         <v>2.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.44</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>2.11</v>
@@ -4801,10 +4801,10 @@
         <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.61</v>
+        <v>3.78</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.22</v>
+        <v>4.78</v>
       </c>
       <c r="BR10" t="n">
         <v>88.89</v>
@@ -4930,7 +4930,7 @@
         <v>1.44</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="DH10" t="n">
         <v>95.22</v>
@@ -4945,7 +4945,7 @@
         <v>4.44</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DM10" t="n">
         <v>49.83</v>
@@ -4954,7 +4954,7 @@
         <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="DP10" t="n">
         <v>10.28</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.39</v>
+        <v>43.44</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
@@ -5159,19 +5159,19 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.890000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.22</v>
+        <v>6.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="BD11" t="n">
         <v>20.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BF11" t="n">
         <v>2.33</v>
@@ -5384,19 +5384,19 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.56</v>
+        <v>11.66</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.89</v>
+        <v>7.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="EA11" t="n">
         <v>20.83</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>76.75</v>
+        <v>80.56</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.12</v>
+        <v>3.78</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.12</v>
+        <v>46.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.12</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47</v>
+        <v>48.11</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>10.78</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.88</v>
+        <v>16.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.65</v>
+        <v>7.89</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
         <v>2.99</v>
@@ -5640,169 +5640,169 @@
         <v>3.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.73</v>
+        <v>4.51</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.41</v>
+        <v>5.11</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.82</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CU12" t="n">
         <v>1.42</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW12" t="n">
         <v>1.9</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.06</v>
+        <v>87.44</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.23</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.76</v>
+        <v>43.94</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.41</v>
+        <v>10.34</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.94</v>
+        <v>12.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.3</v>
+        <v>46.89</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.06</v>
+        <v>13.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.65</v>
+        <v>17.38</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -6690,19 +6690,19 @@
         <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.11</v>
+        <v>18.22</v>
       </c>
       <c r="AA15" t="n">
         <v>12.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="AC15" t="n">
         <v>21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE15" t="n">
         <v>1.56</v>
@@ -6996,13 +6996,13 @@
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.11</v>
+        <v>16.16</v>
       </c>
       <c r="DY15" t="n">
         <v>10.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="EA15" t="n">
         <v>20.22</v>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>89.38</v>
+        <v>88.44</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>42.25</v>
+        <v>42.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P18" t="n">
-        <v>10.62</v>
+        <v>10.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="R18" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>43.38</v>
+        <v>43.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>17</v>
+        <v>17.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>1.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS18" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC18" t="n">
         <v>5.83</v>
@@ -8073,13 +8073,13 @@
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
         <v>1.86</v>
@@ -8088,139 +8088,139 @@
         <v>1.89</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CN18" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CP18" t="n">
         <v>2.03</v>
       </c>
-      <c r="CO18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>2.02</v>
-      </c>
       <c r="CQ18" t="n">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="CR18" t="n">
         <v>1.43</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.06</v>
+        <v>87.66</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.35</v>
+        <v>40.72</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.59</v>
+        <v>10.66</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.59</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.35</v>
+        <v>42.38</v>
       </c>
       <c r="DW18" t="n">
         <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.59</v>
+        <v>9.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.53</v>
+        <v>6.44</v>
       </c>
       <c r="DZ18" t="n">
         <v>3.06</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.65</v>
+        <v>16.77</v>
       </c>
       <c r="EB18" t="n">
         <v>1.12</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.22</v>
@@ -8323,49 +8323,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>77.62</v>
+        <v>78.44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.25</v>
+        <v>37</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>10.78</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.12</v>
+        <v>10.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.75</v>
+        <v>48.44</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.75</v>
+        <v>18.89</v>
       </c>
       <c r="BE19" t="n">
         <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.06</v>
+        <v>10.72</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.18</v>
+        <v>4.94</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.28</v>
@@ -8461,16 +8461,16 @@
         <v>2.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
@@ -8479,7 +8479,7 @@
         <v>2.63</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH19" t="n">
         <v>1.47</v>
@@ -8494,19 +8494,19 @@
         <v>1.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.96</v>
@@ -8515,78 +8515,82 @@
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW19" t="n">
         <v>1.72</v>
       </c>
-      <c r="CX19" t="inlineStr"/>
+      <c r="CX19" t="n">
+        <v>1.47</v>
+      </c>
       <c r="CY19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CZ19" t="inlineStr"/>
+        <v>1.59</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.64</v>
+      </c>
       <c r="DA19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.94</v>
+        <v>86.83</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.65</v>
+        <v>5.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.88</v>
+        <v>46.72</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.47</v>
+        <v>11.11</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.53</v>
+        <v>10.39</v>
       </c>
       <c r="DR19" t="n">
-        <v>8</v>
+        <v>8.34</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,19 +8602,19 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52</v>
+        <v>51.22</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="EA19" t="n">
         <v>20</v>
@@ -8619,7 +8623,7 @@
         <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,259 +1379,259 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>106.56</v>
+        <v>105.2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>56.89</v>
+        <v>54.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>12.22</v>
+        <v>12.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.33</v>
+        <v>11.1</v>
       </c>
       <c r="R2" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>56.44</v>
+        <v>55.1</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.78</v>
+        <v>13.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.33</v>
+        <v>9.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.89</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="CD2" t="n">
         <v>4.56</v>
       </c>
-      <c r="AI2" t="n">
-        <v>91.56</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>72.22</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>4.44</v>
-      </c>
       <c r="CE2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
         <v>2.2</v>
@@ -1640,25 +1640,25 @@
         <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1673,106 +1673,106 @@
         <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CY2" t="n">
         <v>1.69</v>
       </c>
-      <c r="CX2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CZ2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.06</v>
+        <v>97.45</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.66</v>
+        <v>52.55</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.22</v>
+        <v>10.8</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.44</v>
+        <v>51</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.67</v>
+        <v>13.9</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.56</v>
+        <v>8.85</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.06</v>
+        <v>19.4</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
@@ -1782,286 +1782,286 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>109.78</v>
+        <v>106.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>6.22</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>65.78</v>
+        <v>65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>8.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62</v>
+        <v>60.4</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.56</v>
+        <v>17.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.67</v>
+        <v>17.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>92.44</v>
+        <v>94.7</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.44</v>
+        <v>56.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.44</v>
+        <v>10.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.890000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.78</v>
+        <v>56.8</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.44</v>
+        <v>13.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.22</v>
+        <v>16.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.22</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>1.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK3" t="n">
         <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2076,16 +2076,16 @@
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.46</v>
@@ -2097,10 +2097,10 @@
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2109,73 +2109,73 @@
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.11</v>
+        <v>100.7</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.94</v>
+        <v>5.75</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.61</v>
+        <v>60.85</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.11</v>
+        <v>11.15</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.77</v>
+        <v>4.8</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.39</v>
+        <v>58.6</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.94</v>
+        <v>17.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>85.44</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>43.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.44</v>
+        <v>17.2</v>
       </c>
       <c r="R4" t="n">
-        <v>7.78</v>
+        <v>7.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,187 +2251,187 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.11</v>
+        <v>51.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AA4" t="n">
         <v>7</v>
       </c>
       <c r="AB4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW4" t="n">
         <v>5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>43.78</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>72.22</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>5.56</v>
-      </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.16</v>
+        <v>3.62</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2440,22 +2440,22 @@
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CO4" t="n">
         <v>1.27</v>
@@ -2464,7 +2464,7 @@
         <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2473,16 +2473,16 @@
         <v>2.79</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2500,52 +2500,52 @@
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
         <v>3.12</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.38</v>
+        <v>85.55</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.39</v>
+        <v>43.5</v>
       </c>
       <c r="DN4" t="n">
         <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.28</v>
+        <v>10.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.56</v>
+        <v>17.2</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.5</v>
+        <v>52.7</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.89</v>
+        <v>15.1</v>
       </c>
       <c r="EB4" t="n">
         <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
-        <v>90.89</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>42.56</v>
+        <v>43.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.33</v>
+        <v>9.4</v>
       </c>
       <c r="R5" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>41.44</v>
+        <v>42.9</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.22</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.17</v>
+        <v>4.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC5" t="n">
         <v>3.74</v>
@@ -2843,19 +2843,19 @@
         <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.71</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL5" t="n">
         <v>1.72</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CN5" t="n">
         <v>2.15</v>
@@ -2867,19 +2867,19 @@
         <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
         <v>2.18</v>
@@ -2903,85 +2903,85 @@
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.16</v>
+        <v>89</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.84</v>
+        <v>42.42</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.66</v>
+        <v>10.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.16</v>
+        <v>7.05</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45</v>
+        <v>45.58</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10</v>
+        <v>9.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.89</v>
+        <v>5.84</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.11</v>
+        <v>19.05</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -2991,247 +2991,247 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>95.11</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>57.67</v>
+        <v>57.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.22</v>
+        <v>11.7</v>
       </c>
       <c r="R6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.44</v>
+        <v>52.3</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.33</v>
+        <v>14.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.109999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>92.67</v>
+        <v>91.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.33</v>
+        <v>50.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.56</v>
+        <v>13.1</v>
       </c>
       <c r="AR6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BV6" t="n">
         <v>10</v>
       </c>
-      <c r="AS6" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BW6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CD6" t="n">
         <v>3.67</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>3.84</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3240,34 +3240,34 @@
         <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.8</v>
@@ -3285,106 +3285,106 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.57</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.38</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.89</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="DL6" t="n">
         <v>0.45</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.5</v>
+        <v>54.15</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.06</v>
+        <v>12.1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.61</v>
+        <v>10.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.109999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.56</v>
+        <v>52.45</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.33</v>
+        <v>13.55</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.890000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.06</v>
+        <v>15.9</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7">
@@ -3394,274 +3394,274 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q7" t="n">
         <v>9</v>
       </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="R7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>90.89</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M7" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="R7" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80.78</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>85</v>
       </c>
       <c r="BT7" t="n">
         <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>35</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.78</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.56</v>
+        <v>5</v>
       </c>
       <c r="BX7" t="n">
-        <v>55.56</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.68</v>
+        <v>5.71</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.34</v>
+        <v>7.36</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.79</v>
+        <v>7.69</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CH7" t="n">
         <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
         <v>1.42</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN7" t="n">
         <v>2.06</v>
@@ -3670,16 +3670,16 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CT7" t="n">
         <v>2.99</v>
@@ -3688,106 +3688,106 @@
         <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX7" t="n">
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.36</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB7" t="n">
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.84</v>
+        <v>85.75</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.66</v>
+        <v>37.65</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.779999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.77</v>
+        <v>9.4</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.17</v>
+        <v>10.8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.28</v>
+        <v>41.55</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.89</v>
+        <v>18.05</v>
       </c>
       <c r="EB7" t="n">
         <v>1.06</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>106.22</v>
+        <v>107</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="K8" t="n">
-        <v>6.78</v>
+        <v>7.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="M8" t="n">
-        <v>58.78</v>
+        <v>63.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>11.89</v>
+        <v>11.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="R8" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.89</v>
+        <v>59.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.56</v>
+        <v>14.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.83</v>
+        <v>10.11</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>5.37</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CC8" t="n">
         <v>2.04</v>
@@ -4040,22 +4040,22 @@
         <v>2.12</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK8" t="n">
         <v>1.41</v>
@@ -4067,16 +4067,16 @@
         <v>2.68</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
@@ -4091,106 +4091,106 @@
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX8" t="n">
         <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.06</v>
+        <v>104.58</v>
       </c>
       <c r="DI8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.11</v>
       </c>
-      <c r="DJ8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>12</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.72</v>
+        <v>59.16</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.06</v>
+        <v>14.21</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.109999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.89</v>
+        <v>15.95</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>47.89</v>
+        <v>48.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
-        <v>9.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
       <c r="R9" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.56</v>
+        <v>44.1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.67</v>
+        <v>13.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.44</v>
+        <v>9.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.33</v>
+        <v>18.9</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU9" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
         <v>3.37</v>
@@ -4446,16 +4446,16 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.78</v>
@@ -4464,7 +4464,7 @@
         <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM9" t="n">
         <v>2.55</v>
@@ -4476,10 +4476,10 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4494,7 +4494,7 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
         <v>1.81</v>
@@ -4506,94 +4506,94 @@
         <v>1.88</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="DH9" t="n">
-        <v>81.44</v>
+        <v>81.47</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.72</v>
+        <v>43.32</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="DR9" t="n">
-        <v>8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.44</v>
+        <v>43.26</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.84</v>
+        <v>11.79</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.78</v>
+        <v>7.84</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.33</v>
+        <v>17.21</v>
       </c>
       <c r="EB9" t="n">
         <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4693,52 +4693,52 @@
         <v>2.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>90.22</v>
+        <v>88</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>42.33</v>
+        <v>41</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.11</v>
+        <v>39.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.44</v>
+        <v>18.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG10" t="n">
         <v>2.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.390000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>2.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.78</v>
+        <v>4.89</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY10" t="n">
         <v>2.78</v>
@@ -4834,43 +4834,43 @@
         <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
         <v>3.58</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="CE10" t="n">
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL10" t="n">
         <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CN10" t="n">
         <v>2</v>
@@ -4879,10 +4879,10 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
@@ -4897,10 +4897,10 @@
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
@@ -4924,79 +4924,79 @@
         <v>3.26</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.22</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.83</v>
+        <v>48.74</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.28</v>
+        <v>10.21</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.38</v>
+        <v>12.31</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.61</v>
+        <v>7.89</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.44</v>
+        <v>42.74</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.83</v>
+        <v>19.53</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5096,52 +5096,52 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>83.78</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.56</v>
+        <v>43.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
         <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.11</v>
+        <v>49.3</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.11</v>
+        <v>10.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.33</v>
+        <v>6.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.44</v>
+        <v>20.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.33</v>
+        <v>5.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY11" t="n">
         <v>3.11</v>
@@ -5237,25 +5237,25 @@
         <v>3.29</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
@@ -5267,25 +5267,25 @@
         <v>1.79</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL11" t="n">
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,106 +5300,106 @@
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="DG11" t="n">
         <v>2.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.56</v>
+        <v>88.31</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.84</v>
+        <v>4.74</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.17</v>
+        <v>47.26</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.16</v>
+        <v>11.1</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.66</v>
+        <v>11.68</v>
       </c>
       <c r="DR11" t="n">
         <v>7.84</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.06</v>
+        <v>51.53</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.66</v>
+        <v>11.95</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.94</v>
+        <v>8.16</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.83</v>
+        <v>20.63</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AT12" t="n">
         <v>2</v>
       </c>
-      <c r="AI12" t="n">
-        <v>80.56</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AU12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BL12" t="n">
         <v>1</v>
       </c>
-      <c r="AL12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="BE12" t="n">
+      <c r="BM12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.26</v>
       </c>
-      <c r="BF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BP12" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.11</v>
+        <v>4.26</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU12" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY12" t="n">
         <v>2.99</v>
@@ -5640,43 +5640,43 @@
         <v>3.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.51</v>
+        <v>4.61</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.11</v>
+        <v>5.32</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.82</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
         <v>1.94</v>
@@ -5685,10 +5685,10 @@
         <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5712,97 +5712,97 @@
         <v>1.62</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.33</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
         <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.44</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.94</v>
+        <v>43.27</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.34</v>
+        <v>10.21</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.84</v>
+        <v>12.95</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.56</v>
+        <v>7.63</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.89</v>
+        <v>46.11</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.28</v>
+        <v>12.79</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.109999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.38</v>
+        <v>17.42</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>114</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H13" t="n">
-        <v>109.33</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M13" t="n">
-        <v>62</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>60.78</v>
+        <v>61.5</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.67</v>
+        <v>16.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.89</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.44</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
         <v>1.54</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CA13" t="n">
         <v>4.34</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -6055,43 +6055,43 @@
         <v>2.13</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM13" t="n">
         <v>2.91</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
@@ -6106,106 +6106,106 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DE13" t="n">
         <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>109.28</v>
+        <v>111.74</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.11</v>
+        <v>5.26</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM13" t="n">
-        <v>60.56</v>
+        <v>61.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP13" t="n">
         <v>10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.89</v>
+        <v>11.74</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.89</v>
+        <v>6.74</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.22</v>
+        <v>61.58</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.12</v>
+        <v>15.32</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.78</v>
+        <v>11</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.61</v>
+        <v>19.68</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.22</v>
@@ -6305,139 +6305,139 @@
         <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>103.11</v>
+        <v>103.4</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.33</v>
+        <v>52.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.22</v>
+        <v>58.3</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.33</v>
+        <v>12.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.67</v>
+        <v>17.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.609999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY14" t="n">
         <v>1.42</v>
@@ -6446,73 +6446,73 @@
         <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="CB14" t="n">
         <v>4.91</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="CE14" t="n">
         <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK14" t="n">
         <v>1.42</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6524,91 +6524,91 @@
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DH14" t="n">
-        <v>103.28</v>
+        <v>103.42</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.78</v>
+        <v>57.47</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.94</v>
+        <v>9.74</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.56</v>
+        <v>12.37</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.66</v>
+        <v>5.74</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.33</v>
+        <v>58.84</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.22</v>
+        <v>14.21</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.720000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.34</v>
+        <v>18.63</v>
       </c>
       <c r="EB14" t="n">
         <v>1.69</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
-        <v>103.44</v>
+        <v>105.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="M15" t="n">
-        <v>54.56</v>
+        <v>57.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.33</v>
+        <v>12.4</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>53.67</v>
+        <v>53.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.22</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.11</v>
+        <v>11.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AD15" t="n">
         <v>1.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6789,70 +6789,70 @@
         <v>1.44</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.44</v>
+        <v>9.58</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BJ15" t="n">
         <v>0.89</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV15" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="CC15" t="n">
         <v>2.84</v>
@@ -6873,10 +6873,10 @@
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
@@ -6885,13 +6885,13 @@
         <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN15" t="n">
         <v>2.14</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP15" t="n">
         <v>1.63</v>
@@ -6903,19 +6903,19 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CT15" t="n">
         <v>3.31</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
@@ -6933,85 +6933,85 @@
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.61</v>
+        <v>103.53</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DM15" t="n">
-        <v>50.67</v>
+        <v>52.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.67</v>
+        <v>10.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.61</v>
+        <v>12.63</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.22</v>
+        <v>53.37</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.16</v>
+        <v>16.1</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.56</v>
+        <v>10.47</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.22</v>
+        <v>20.16</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7111,52 +7111,52 @@
         <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>112.56</v>
+        <v>109.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>64.11</v>
+        <v>61.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>55.56</v>
+        <v>55.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.67</v>
+        <v>11.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.89</v>
+        <v>19.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.83</v>
+        <v>11.58</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.61</v>
+        <v>5.47</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY16" t="n">
         <v>2.3</v>
@@ -7252,22 +7252,22 @@
         <v>2.34</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="CE16" t="n">
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG16" t="n">
         <v>3.14</v>
@@ -7276,10 +7276,10 @@
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK16" t="n">
         <v>1.34</v>
@@ -7288,10 +7288,10 @@
         <v>1.66</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
@@ -7300,7 +7300,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7315,10 +7315,10 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
@@ -7330,7 +7330,7 @@
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7342,46 +7342,46 @@
         <v>2.95</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="DH16" t="n">
-        <v>103.62</v>
+        <v>102.32</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.39</v>
+        <v>6.26</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>59</v>
+        <v>57.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DO16" t="n">
         <v>2.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.56</v>
+        <v>10.16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.5</v>
+        <v>11.42</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.39</v>
+        <v>6.74</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.06</v>
+        <v>52.05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.34</v>
+        <v>12.74</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.06</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.28</v>
+        <v>4.53</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.44</v>
+        <v>19.26</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="17">
@@ -7424,142 +7424,142 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>102.22</v>
+        <v>103.1</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M17" t="n">
-        <v>61.78</v>
+        <v>64.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.78</v>
+        <v>51.8</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.22</v>
+        <v>14.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.22</v>
+        <v>10.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.67</v>
+        <v>19.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.44</v>
+        <v>90.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.56</v>
+        <v>41.9</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.89</v>
+        <v>11.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.89</v>
+        <v>13.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,73 +7571,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49.78</v>
+        <v>47.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.44</v>
+        <v>19.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>85</v>
       </c>
       <c r="BT17" t="n">
-        <v>55.56</v>
+        <v>55</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,82 +7646,82 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>35</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX17" t="n">
         <v>1.57</v>
@@ -7739,85 +7739,85 @@
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="DH17" t="n">
-        <v>98.33</v>
+        <v>96.8</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.33</v>
+        <v>5.45</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM17" t="n">
-        <v>53.17</v>
+        <v>53.35</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.44</v>
+        <v>10.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.78</v>
+        <v>49.65</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12</v>
+        <v>12.35</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.16</v>
+        <v>8.35</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.56</v>
+        <v>19.15</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>88.44</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>42.78</v>
+        <v>43.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P18" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="R18" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>43.33</v>
+        <v>42.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.22</v>
+        <v>17.4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>1.67</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.44</v>
+        <v>3.82</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.82</v>
+        <v>4.21</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="CC18" t="n">
         <v>5.83</v>
@@ -8070,16 +8070,16 @@
         <v>6.1</v>
       </c>
       <c r="CE18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CH18" t="n">
         <v>1.41</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
         <v>1.86</v>
@@ -8091,7 +8091,7 @@
         <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM18" t="n">
         <v>2.56</v>
@@ -8103,37 +8103,37 @@
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="CR18" t="n">
         <v>1.43</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CT18" t="n">
         <v>2.88</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW18" t="n">
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY18" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
         <v>1.98</v>
@@ -8142,52 +8142,52 @@
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.66</v>
+        <v>87.53</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.72</v>
+        <v>41.16</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.94</v>
+        <v>9.9</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.66</v>
+        <v>10.47</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.609999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="DS18" t="n">
         <v>0.11</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.38</v>
+        <v>41.84</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.77</v>
+        <v>16.89</v>
       </c>
       <c r="EB18" t="n">
         <v>1.12</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.22</v>
@@ -8323,49 +8323,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP19" t="n">
         <v>2</v>
       </c>
-      <c r="AI19" t="n">
-        <v>78.44</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>37</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>48.44</v>
+        <v>48</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.89</v>
+        <v>18.6</v>
       </c>
       <c r="BE19" t="n">
         <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.72</v>
+        <v>10.37</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.94</v>
+        <v>4.74</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY19" t="n">
         <v>2.28</v>
@@ -8461,25 +8461,25 @@
         <v>2.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH19" t="n">
         <v>1.47</v>
@@ -8494,13 +8494,13 @@
         <v>1.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
@@ -8509,25 +8509,25 @@
         <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT19" t="n">
         <v>3.15</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV19" t="n">
         <v>2.23</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
         <v>1.47</v>
@@ -8542,55 +8542,55 @@
         <v>2.35</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.83</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.44</v>
+        <v>5.21</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.72</v>
+        <v>46.31</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.34</v>
+        <v>8.26</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.22</v>
+        <v>50.84</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="EA19" t="n">
-        <v>20</v>
+        <v>19.79</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="20">
@@ -8633,277 +8633,277 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>88.11</v>
+        <v>86.7</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>44.67</v>
+        <v>43.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.11</v>
+        <v>11.8</v>
       </c>
       <c r="R20" t="n">
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.11</v>
+        <v>18.6</v>
       </c>
       <c r="AD20" t="n">
         <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>37.56</v>
+        <v>40.4</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.44</v>
+        <v>10.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.56</v>
+        <v>9.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.779999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.56</v>
+        <v>17.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.56</v>
+        <v>5.75</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>94.44</v>
+        <v>95</v>
       </c>
       <c r="BT20" t="n">
-        <v>61.11</v>
+        <v>65</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.78</v>
+        <v>30</v>
       </c>
       <c r="BV20" t="n">
-        <v>16.67</v>
+        <v>15</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.56</v>
+        <v>5</v>
       </c>
       <c r="BX20" t="n">
-        <v>55.56</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.91</v>
+        <v>6.47</v>
       </c>
       <c r="CD20" t="n">
-        <v>7.52</v>
+        <v>7.06</v>
       </c>
       <c r="CE20" t="n">
         <v>1.33</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH20" t="n">
         <v>1.5</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CN20" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CO20" t="n">
         <v>1.23</v>
@@ -8912,22 +8912,22 @@
         <v>1.78</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW20" t="n">
         <v>1.77</v>
@@ -8936,97 +8936,97 @@
         <v>1.48</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.57</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DH20" t="n">
-        <v>86.56</v>
+        <v>88.55</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.12</v>
+        <v>42.05</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.279999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>42</v>
+        <v>43.1</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="21">
@@ -9036,142 +9036,142 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="H21" t="n">
-        <v>94.67</v>
+        <v>91.8</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>41.44</v>
+        <v>39.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="P21" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.78</v>
-      </c>
       <c r="U21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48.22</v>
+        <v>46.7</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.89</v>
+        <v>21.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>87.33</v>
+        <v>89</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN21" t="n">
-        <v>37.11</v>
+        <v>39.3</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.78</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,163 +9183,163 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>41.89</v>
+        <v>42.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.56</v>
+        <v>7.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.44</v>
+        <v>17.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.17</v>
+        <v>9.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="BP21" t="n">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.11</v>
+        <v>4.55</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT21" t="n">
         <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>27.78</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>16.67</v>
+        <v>15</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>44.44</v>
+        <v>45</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.91</v>
+        <v>3.77</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CB21" t="n">
         <v>4.38</v>
       </c>
       <c r="CC21" t="n">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="CD21" t="n">
-        <v>9.289999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH21" t="n">
         <v>1.45</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK21" t="n">
         <v>1.45</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN21" t="n">
         <v>1.99</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CT21" t="n">
         <v>2.97</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.4</v>
@@ -9351,85 +9351,85 @@
         <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DH21" t="n">
-        <v>91</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.28</v>
+        <v>39.55</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.34</v>
+        <v>14.05</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.83</v>
+        <v>7.95</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.06</v>
+        <v>44.4</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX21" t="n">
-        <v>8.67</v>
+        <v>8.9</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.17</v>
+        <v>19.3</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1472,7 +1472,7 @@
         <v>0.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
         <v>4.3</v>
@@ -1484,7 +1484,7 @@
         <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AL2" t="n">
         <v>6.2</v>
@@ -1529,7 +1529,7 @@
         <v>46.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
         <v>13.9</v>
@@ -1607,13 +1607,13 @@
         <v>2.43</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CA2" t="n">
         <v>3.82</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
         <v>4.23</v>
@@ -1664,13 +1664,13 @@
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
         <v>3.14</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
         <v>2.29</v>
@@ -1679,16 +1679,16 @@
         <v>1.68</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
@@ -1703,7 +1703,7 @@
         <v>0.3</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
         <v>3.45</v>
@@ -1715,7 +1715,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="DK2" t="n">
         <v>5.8</v>
@@ -1754,7 +1754,7 @@
         <v>51</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
         <v>13.9</v>
@@ -2016,13 +2016,13 @@
         <v>4.71</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="CC3" t="n">
         <v>1.81</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
@@ -2067,7 +2067,7 @@
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CT3" t="n">
         <v>3.17</v>
@@ -2413,13 +2413,13 @@
         <v>2.43</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CA4" t="n">
         <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC4" t="n">
         <v>3.62</v>
@@ -2473,7 +2473,7 @@
         <v>2.79</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
@@ -2488,19 +2488,19 @@
         <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
         <v>3.12</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.3</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3</v>
       </c>
-      <c r="AI5" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.84</v>
-      </c>
       <c r="BH5" t="n">
-        <v>9.68</v>
+        <v>9.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP5" t="n">
         <v>4.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV5" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>3.07</v>
@@ -2819,70 +2819,70 @@
         <v>3.2</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO5" t="n">
         <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW5" t="n">
         <v>1.76</v>
@@ -2891,7 +2891,7 @@
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.41</v>
@@ -2903,22 +2903,22 @@
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD5" t="n">
         <v>3.15</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DH5" t="n">
-        <v>89</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,58 +2927,58 @@
         <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.42</v>
+        <v>42.15</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.52</v>
+        <v>10.4</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.48</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.58</v>
+        <v>46.05</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.84</v>
+        <v>9.9</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="EA5" t="n">
         <v>19.05</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
         <v>1.95</v>
@@ -3036,7 +3036,7 @@
         <v>11.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="R6" t="n">
         <v>8.6</v>
@@ -3276,7 +3276,7 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
@@ -3288,7 +3288,7 @@
         <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.57</v>
@@ -3306,7 +3306,7 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
         <v>2.86</v>
@@ -3348,7 +3348,7 @@
         <v>12.1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.8</v>
+        <v>10.85</v>
       </c>
       <c r="DR6" t="n">
         <v>7.65</v>
@@ -3499,7 +3499,7 @@
         <v>-0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>4.1</v>
@@ -3511,7 +3511,7 @@
         <v>33.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP7" t="n">
         <v>2</v>
@@ -3562,7 +3562,7 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BG7" t="n">
         <v>2.95</v>
@@ -3634,7 +3634,7 @@
         <v>7.36</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.69</v>
+        <v>7.77</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
@@ -3679,7 +3679,7 @@
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT7" t="n">
         <v>2.99</v>
@@ -3712,7 +3712,7 @@
         <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>-0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="DK7" t="n">
         <v>3.75</v>
@@ -3742,7 +3742,7 @@
         <v>37.65</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
         <v>1.65</v>
@@ -3787,7 +3787,7 @@
         <v>1.06</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>101.89</v>
+        <v>98.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>50.33</v>
+        <v>48.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.11</v>
+        <v>12.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58.56</v>
+        <v>57</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.11</v>
+        <v>12.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.220000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.22</v>
+        <v>17.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BM8" t="n">
         <v>1.05</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>1.92</v>
@@ -4028,55 +4028,55 @@
         <v>1.98</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.67</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
         <v>1.84</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
@@ -4094,103 +4094,103 @@
         <v>2.29</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.58</v>
+        <v>102.6</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.84</v>
+        <v>5.65</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.47</v>
+        <v>56.3</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.63</v>
+        <v>11.75</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.37</v>
+        <v>13.4</v>
       </c>
       <c r="DR8" t="n">
         <v>7.1</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.16</v>
+        <v>58.35</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.21</v>
+        <v>13.9</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.369999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.95</v>
+        <v>16.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.89</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.56</v>
+        <v>39</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.109999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.33</v>
+        <v>42.2</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.11</v>
+        <v>6.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.33</v>
+        <v>15.5</v>
       </c>
       <c r="BE9" t="n">
         <v>1.18</v>
       </c>
       <c r="BF9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.84</v>
+        <v>9.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.37</v>
+        <v>4.55</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU9" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY9" t="n">
         <v>2.54</v>
@@ -4431,31 +4431,31 @@
         <v>2.62</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.51</v>
+        <v>3.68</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.78</v>
@@ -4473,22 +4473,22 @@
         <v>1.99</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP9" t="n">
         <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
@@ -4503,97 +4503,97 @@
         <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.39</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
         <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DH9" t="n">
-        <v>81.47</v>
+        <v>82.25</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.32</v>
+        <v>43.75</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.050000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.26</v>
+        <v>43.15</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.79</v>
+        <v>11.75</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.84</v>
+        <v>7.95</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.21</v>
+        <v>17.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>100.22</v>
+        <v>101.4</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>57.33</v>
+        <v>57.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="P10" t="n">
-        <v>9.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="R10" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>46.78</v>
+        <v>46.6</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.11</v>
+        <v>12.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.22</v>
+        <v>20.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,70 +4774,70 @@
         <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
       <c r="BR10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT10" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU10" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC10" t="n">
         <v>3.93</v>
@@ -4846,13 +4846,13 @@
         <v>4.26</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
@@ -4867,31 +4867,31 @@
         <v>1.44</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO10" t="n">
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4906,13 +4906,13 @@
         <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
@@ -4927,43 +4927,43 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.79000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.74</v>
+        <v>49.35</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.31</v>
+        <v>12.2</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.89</v>
+        <v>7.8</v>
       </c>
       <c r="DS10" t="n">
         <v>0.05</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.74</v>
+        <v>42.85</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.58</v>
+        <v>10.75</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.52</v>
+        <v>7.55</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.53</v>
+        <v>19.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>89.33</v>
+        <v>87.3</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>51.78</v>
+        <v>50.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54</v>
+        <v>52.8</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.22</v>
+        <v>12.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.22</v>
+        <v>20.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0.4</v>
@@ -5177,70 +5177,70 @@
         <v>2.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1.05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CC11" t="n">
         <v>3.51</v>
@@ -5249,13 +5249,13 @@
         <v>3.79</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF11" t="n">
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
@@ -5273,7 +5273,7 @@
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN11" t="n">
         <v>2.12</v>
@@ -5285,25 +5285,25 @@
         <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5315,58 +5315,58 @@
         <v>2.47</v>
       </c>
       <c r="DA11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DG11" t="n">
         <v>2.15</v>
       </c>
-      <c r="DB11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.16</v>
-      </c>
       <c r="DH11" t="n">
-        <v>88.31</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.26</v>
+        <v>46.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DP11" t="n">
         <v>11.1</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.68</v>
+        <v>11.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.84</v>
+        <v>7.9</v>
       </c>
       <c r="DS11" t="n">
         <v>0.05</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.53</v>
+        <v>51.05</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.95</v>
+        <v>11.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.63</v>
+        <v>20.45</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>94.33</v>
+        <v>96.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>41.56</v>
+        <v>42.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="R12" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.67</v>
+        <v>45.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.78</v>
+        <v>15.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.33</v>
+        <v>18.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC12" t="n">
         <v>4.61</v>
@@ -5655,7 +5655,7 @@
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CG12" t="n">
         <v>2.94</v>
@@ -5664,16 +5664,16 @@
         <v>1.42</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK12" t="n">
         <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM12" t="n">
         <v>2.49</v>
@@ -5688,7 +5688,7 @@
         <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5703,73 +5703,73 @@
         <v>1.42</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.73999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.27</v>
+        <v>43.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.11</v>
+        <v>46.05</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.79</v>
+        <v>12.7</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.74</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.42</v>
+        <v>17.55</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>109.22</v>
+        <v>112.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>59.11</v>
+        <v>59</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.11</v>
+        <v>10.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.56</v>
+        <v>12.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>61.67</v>
+        <v>61.3</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.56</v>
+        <v>13.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.56</v>
+        <v>9.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.33</v>
+        <v>20.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.890000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL13" t="n">
         <v>0.95</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.63</v>
+        <v>5.65</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>1.54</v>
@@ -6043,34 +6043,34 @@
         <v>1.6</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="CC13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CE13" t="n">
         <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.36</v>
@@ -6079,7 +6079,7 @@
         <v>1.65</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CN13" t="n">
         <v>2.2</v>
@@ -6088,22 +6088,22 @@
         <v>1.17</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV13" t="n">
         <v>2.28</v>
@@ -6121,58 +6121,58 @@
         <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>111.74</v>
+        <v>113.2</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.26</v>
+        <v>5.4</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>61.32</v>
+        <v>61.15</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="DP13" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.74</v>
+        <v>11.8</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.74</v>
+        <v>6.6</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.58</v>
+        <v>61.4</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.32</v>
+        <v>15.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.68</v>
+        <v>20.05</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
-        <v>103.44</v>
+        <v>106.6</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="L14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>63.22</v>
+        <v>63.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="P14" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.33</v>
+        <v>12.7</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.44</v>
+        <v>59.2</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.11</v>
+        <v>15.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6386,70 +6386,70 @@
         <v>1.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.529999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT14" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU14" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="CC14" t="n">
         <v>1.88</v>
@@ -6458,43 +6458,43 @@
         <v>1.95</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
@@ -6509,73 +6509,73 @@
         <v>1.64</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH14" t="n">
-        <v>103.42</v>
+        <v>105</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.52</v>
+        <v>5.65</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>57.47</v>
+        <v>58.05</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.74</v>
+        <v>9.85</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.37</v>
+        <v>12.55</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.84</v>
+        <v>58.75</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="EB14" t="n">
         <v>1.69</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6708,139 +6708,139 @@
         <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AI15" t="n">
-        <v>101.78</v>
+        <v>103.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.78</v>
+        <v>44.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.89</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>52.78</v>
+        <v>53</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.11</v>
+        <v>14.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.44</v>
+        <v>19.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
         <v>0.95</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT15" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
         <v>2.05</v>
@@ -6849,25 +6849,25 @@
         <v>2.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CE15" t="n">
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
@@ -6876,28 +6876,28 @@
         <v>2.27</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6918,67 +6918,67 @@
         <v>1.63</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY15" t="n">
         <v>1.72</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DE15" t="n">
         <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.53</v>
+        <v>104.15</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DM15" t="n">
-        <v>52.47</v>
+        <v>51.2</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.58</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.63</v>
+        <v>12.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.84</v>
+        <v>7.05</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.37</v>
+        <v>53.45</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.1</v>
+        <v>16.05</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.47</v>
+        <v>10.6</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.63</v>
+        <v>5.45</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.16</v>
+        <v>19.95</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>94.67</v>
+        <v>96.8</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>53.89</v>
+        <v>53.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>11.33</v>
+        <v>10.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="R16" t="n">
-        <v>6.78</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>48.56</v>
+        <v>49.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.66</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF16" t="n">
         <v>0.4</v>
@@ -7192,70 +7192,70 @@
         <v>1.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.58</v>
+        <v>11.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.47</v>
+        <v>5.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="BR16" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT16" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV16" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC16" t="n">
         <v>2.34</v>
@@ -7267,7 +7267,7 @@
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG16" t="n">
         <v>3.14</v>
@@ -7285,10 +7285,10 @@
         <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CN16" t="n">
         <v>2.22</v>
@@ -7303,7 +7303,7 @@
         <v>2.93</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
         <v>2.66</v>
@@ -7315,22 +7315,22 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
@@ -7342,79 +7342,79 @@
         <v>2.95</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF16" t="n">
         <v>1.1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="DH16" t="n">
-        <v>102.32</v>
+        <v>103</v>
       </c>
       <c r="DI16" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.26</v>
+        <v>6.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.95</v>
+        <v>57.65</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.16</v>
+        <v>9.9</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.42</v>
+        <v>11.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.74</v>
+        <v>6.85</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.05</v>
+        <v>52.4</v>
       </c>
       <c r="DW16" t="n">
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.210000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.26</v>
+        <v>19.1</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
@@ -7658,13 +7658,13 @@
         <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC17" t="n">
         <v>4.2</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
@@ -7706,19 +7706,19 @@
         <v>3.2</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW17" t="n">
         <v>1.81</v>
@@ -7727,7 +7727,7 @@
         <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.38</v>
@@ -7742,7 +7742,7 @@
         <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE17" t="n">
         <v>0.1</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>86.89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.67</v>
+        <v>39.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.109999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>41.44</v>
+        <v>42.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.33</v>
+        <v>16.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.470000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI18" t="n">
         <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="BQ18" t="n">
         <v>5.05</v>
       </c>
       <c r="BR18" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS18" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY18" t="n">
         <v>3.82</v>
@@ -8058,28 +8058,28 @@
         <v>4.21</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.83</v>
+        <v>5.67</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.1</v>
+        <v>5.94</v>
       </c>
       <c r="CE18" t="n">
         <v>1.4</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
         <v>1.86</v>
@@ -8091,7 +8091,7 @@
         <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM18" t="n">
         <v>2.56</v>
@@ -8103,25 +8103,25 @@
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU18" t="n">
         <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
         <v>1.94</v>
@@ -8130,97 +8130,97 @@
         <v>1.6</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.53</v>
+        <v>87.75</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.16</v>
+        <v>41.6</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.47</v>
+        <v>10.6</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.68</v>
+        <v>8.75</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>41.84</v>
+        <v>42.3</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.529999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.89</v>
+        <v>17.05</v>
       </c>
       <c r="EB18" t="n">
         <v>1.12</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>95.22</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>56.44</v>
+        <v>55.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>11.44</v>
+        <v>11.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="R19" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.89</v>
+        <v>11.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.11</v>
+        <v>21.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.37</v>
+        <v>10.25</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC19" t="n">
         <v>3.63</v>
@@ -8473,124 +8473,124 @@
         <v>3.85</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX19" t="n">
         <v>1.47</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.64</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DB19" t="n">
         <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="DE19" t="n">
         <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.73999999999999</v>
+        <v>86.75</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.31</v>
+        <v>46.55</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.05</v>
+        <v>11</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.47</v>
+        <v>10.35</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.84</v>
+        <v>50.75</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.74</v>
+        <v>9.9</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.79</v>
+        <v>19.9</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="20">
@@ -8873,7 +8873,7 @@
         <v>6.47</v>
       </c>
       <c r="CD20" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
       <c r="CE20" t="n">
         <v>1.33</v>
@@ -8918,22 +8918,22 @@
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU20" t="n">
         <v>1.55</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY20" t="n">
         <v>1.66</v>
@@ -8948,10 +8948,10 @@
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE20" t="n">
         <v>0.15</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="n">
         <v>1.5</v>
@@ -9153,7 +9153,7 @@
         <v>39.3</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AP21" t="n">
         <v>1.6</v>
@@ -9264,7 +9264,7 @@
         <v>3.56</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CA21" t="n">
         <v>4.21</v>
@@ -9321,46 +9321,46 @@
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU21" t="n">
         <v>1.48</v>
       </c>
       <c r="CV21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CW21" t="n">
         <v>1.95</v>
       </c>
-      <c r="CW21" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CX21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA21" t="n">
         <v>2.01</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE21" t="n">
         <v>0.1</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DG21" t="n">
         <v>1.65</v>
@@ -9384,7 +9384,7 @@
         <v>39.55</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="DO21" t="n">
         <v>1.4</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>105.2</v>
+        <v>103.18</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>54.1</v>
+        <v>52.18</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="P2" t="n">
-        <v>12.3</v>
+        <v>12.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.1</v>
+        <v>53.91</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AF2" t="n">
         <v>0.4</v>
@@ -1550,70 +1550,70 @@
         <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
         <v>1.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.35</v>
+        <v>4.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="BR2" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB2" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC2" t="n">
         <v>4.23</v>
@@ -1622,7 +1622,7 @@
         <v>4.56</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF2" t="n">
         <v>2.49</v>
@@ -1646,10 +1646,10 @@
         <v>1.69</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1697,82 +1697,82 @@
         <v>1.73</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.45</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.55</v>
+        <v>51.62</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.55</v>
+        <v>12.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.8</v>
+        <v>10.76</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51</v>
+        <v>50.57</v>
       </c>
       <c r="DW2" t="n">
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.9</v>
+        <v>13.76</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.85</v>
+        <v>8.81</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.4</v>
+        <v>19.34</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.5</v>
+        <v>82.73</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.7</v>
+        <v>44.09</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>9.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.2</v>
+        <v>16.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>53.9</v>
+        <v>54.36</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.3</v>
+        <v>7.73</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
         <v>2.43</v>
@@ -2416,22 +2416,22 @@
         <v>2.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2443,19 +2443,19 @@
         <v>2.08</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO4" t="n">
         <v>1.27</v>
@@ -2464,7 +2464,7 @@
         <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2503,49 +2503,49 @@
         <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="DE4" t="n">
         <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.55</v>
+        <v>86</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DK4" t="n">
         <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.5</v>
+        <v>43.71</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.2</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ4" t="n">
-        <v>17.2</v>
+        <v>16.86</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.35</v>
+        <v>8.43</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="DW4" t="n">
         <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.5</v>
+        <v>11.66</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.15</v>
+        <v>7.38</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.1</v>
+        <v>15.24</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>43.6</v>
+        <v>44.82</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="P5" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.4</v>
+        <v>9.82</v>
       </c>
       <c r="R5" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>42.9</v>
+        <v>43.64</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.7</v>
+        <v>11.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>6.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>19.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2762,67 +2762,67 @@
         <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
         <v>4.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC5" t="n">
         <v>3.66</v>
@@ -2834,40 +2834,40 @@
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
@@ -2882,10 +2882,10 @@
         <v>1.47</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
@@ -2903,22 +2903,22 @@
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.34999999999999</v>
+        <v>88.52</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,58 +2927,58 @@
         <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.15</v>
+        <v>42.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.4</v>
+        <v>10.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.95</v>
+        <v>6.86</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.05</v>
+        <v>46.29</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.9</v>
+        <v>10.28</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.05</v>
+        <v>18.76</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
         <v>1.95</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.2</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>91.3</v>
+        <v>88.64</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>50.7</v>
+        <v>48.09</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.1</v>
+        <v>13.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.9</v>
+        <v>9.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.7</v>
+        <v>7.18</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.6</v>
+        <v>51.45</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.7</v>
+        <v>12.09</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.35</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT6" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.08</v>
@@ -3222,40 +3222,40 @@
         <v>2.2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.55</v>
+        <v>3.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.67</v>
+        <v>3.95</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
@@ -3267,28 +3267,28 @@
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
         <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.57</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="DE6" t="n">
         <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DH6" t="n">
-        <v>94.59999999999999</v>
+        <v>93.05</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.8</v>
+        <v>4.66</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.15</v>
+        <v>52.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.1</v>
+        <v>12.28</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.85</v>
+        <v>10.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.65</v>
+        <v>7.86</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.45</v>
+        <v>51.85</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.55</v>
+        <v>13.19</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.050000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.9</v>
+        <v>16.19</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>90.36</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>41.5</v>
+        <v>40.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="R7" t="n">
-        <v>9.5</v>
+        <v>10.27</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>43.2</v>
+        <v>42.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW7" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.71</v>
+        <v>5.61</v>
       </c>
       <c r="CA7" t="n">
         <v>4.23</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="CC7" t="n">
         <v>7.36</v>
@@ -3640,19 +3640,19 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH7" t="n">
         <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK7" t="n">
         <v>1.42</v>
@@ -3661,10 +3661,10 @@
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO7" t="n">
         <v>1.27</v>
@@ -3673,7 +3673,7 @@
         <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3688,10 +3688,10 @@
         <v>1.48</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX7" t="n">
         <v>1.59</v>
@@ -3709,52 +3709,52 @@
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.75</v>
+        <v>86.14</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.65</v>
+        <v>37.19</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.8</v>
+        <v>11.14</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.55</v>
+        <v>41.24</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.05</v>
+        <v>17.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>98.2</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.64</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.7</v>
+        <v>47.73</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.3</v>
+        <v>11.73</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.9</v>
+        <v>13.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.3</v>
+        <v>7.18</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57</v>
+        <v>55.91</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.1</v>
+        <v>10.24</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BM8" t="n">
         <v>1.05</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP8" t="n">
         <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>5.48</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY8" t="n">
         <v>1.92</v>
@@ -4028,22 +4028,22 @@
         <v>1.98</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG8" t="n">
         <v>3.27</v>
@@ -4055,37 +4055,37 @@
         <v>2.17</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN8" t="n">
         <v>2.06</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP8" t="n">
         <v>1.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
@@ -4121,43 +4121,43 @@
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="DH8" t="n">
-        <v>102.6</v>
+        <v>102.19</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.65</v>
+        <v>5.91</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.3</v>
+        <v>55.43</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.75</v>
+        <v>11.48</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.4</v>
+        <v>13.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="DS8" t="n">
         <v>0.1</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.35</v>
+        <v>57.71</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.2</v>
+        <v>15.95</v>
       </c>
       <c r="EB8" t="n">
         <v>1.62</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H9" t="n">
-        <v>85.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>48.5</v>
+        <v>47.09</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.5</v>
+        <v>9.82</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.1</v>
+        <v>43.82</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.4</v>
+        <v>13.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.4</v>
+        <v>9.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.9</v>
+        <v>18.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BR9" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS9" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC9" t="n">
         <v>3.51</v>
@@ -4446,7 +4446,7 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG9" t="n">
         <v>2.93</v>
@@ -4458,19 +4458,19 @@
         <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO9" t="n">
         <v>1.29</v>
@@ -4479,7 +4479,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4524,76 +4524,76 @@
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.25</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.75</v>
+        <v>43.24</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.9</v>
+        <v>9.81</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.2</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.85</v>
+        <v>7.95</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.15</v>
+        <v>43.05</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.75</v>
+        <v>11.71</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.95</v>
+        <v>7.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.2</v>
+        <v>17.19</v>
       </c>
       <c r="EB9" t="n">
         <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H10" t="n">
-        <v>101.4</v>
+        <v>100.91</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M10" t="n">
-        <v>57.7</v>
+        <v>57</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.1</v>
+        <v>13.36</v>
       </c>
       <c r="R10" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>46.6</v>
+        <v>46.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.3</v>
+        <v>12.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.4</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.3</v>
+        <v>19.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,64 +4774,64 @@
         <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS10" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="CA10" t="n">
         <v>3.47</v>
@@ -4858,22 +4858,22 @@
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO10" t="n">
         <v>1.33</v>
@@ -4882,7 +4882,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
@@ -4894,13 +4894,13 @@
         <v>2.93</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
@@ -4924,46 +4924,46 @@
         <v>3.26</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.7</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.35</v>
+        <v>49.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.15</v>
+        <v>10.29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.2</v>
+        <v>12.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="DS10" t="n">
         <v>0.05</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.85</v>
+        <v>42.95</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.75</v>
+        <v>10.86</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.55</v>
+        <v>7.72</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.6</v>
+        <v>19.19</v>
       </c>
       <c r="EB10" t="n">
         <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>87.3</v>
+        <v>88.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>50.3</v>
+        <v>52.73</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.8</v>
+        <v>20.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
         <v>0.4</v>
@@ -5177,67 +5177,67 @@
         <v>2.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.1</v>
+        <v>10.24</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU11" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="BZ11" t="n">
         <v>3.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB11" t="n">
         <v>3.6</v>
@@ -5249,22 +5249,22 @@
         <v>3.79</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK11" t="n">
         <v>1.37</v>
@@ -5282,19 +5282,19 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
         <v>1.42</v>
@@ -5321,49 +5321,49 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.34999999999999</v>
+        <v>88</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.65</v>
+        <v>4.52</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.75</v>
+        <v>48.19</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="DR11" t="n">
         <v>7.9</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.05</v>
+        <v>51.24</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.75</v>
+        <v>11.95</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.050000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.45</v>
+        <v>20.19</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.3</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>79.90000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.3</v>
+        <v>12.18</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.5</v>
+        <v>45.64</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.1</v>
+        <v>10.45</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.6</v>
+        <v>16.45</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.15</v>
+        <v>8.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.9</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.25</v>
+        <v>4.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU12" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
         <v>2.94</v>
@@ -5640,22 +5640,22 @@
         <v>3.13</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.32</v>
+        <v>5.29</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG12" t="n">
         <v>2.94</v>
@@ -5670,34 +5670,34 @@
         <v>1.81</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CU12" t="n">
         <v>1.42</v>
@@ -5721,88 +5721,88 @@
         <v>1.92</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.2</v>
+        <v>88.81</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.65</v>
+        <v>43.81</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.05</v>
+        <v>45.62</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.7</v>
+        <v>12.76</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.55</v>
+        <v>17.43</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>106.6</v>
+        <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K14" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="M14" t="n">
-        <v>63.8</v>
+        <v>65.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P14" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.7</v>
+        <v>13.18</v>
       </c>
       <c r="R14" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.2</v>
+        <v>59.27</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.9</v>
+        <v>16.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>19</v>
+        <v>18.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6386,58 +6386,58 @@
         <v>1.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.550000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX14" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY14" t="n">
         <v>1.44</v>
@@ -6446,10 +6446,10 @@
         <v>1.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="CC14" t="n">
         <v>1.88</v>
@@ -6461,25 +6461,25 @@
         <v>1.26</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK14" t="n">
         <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM14" t="n">
         <v>2.66</v>
@@ -6488,31 +6488,31 @@
         <v>2.04</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CV14" t="n">
         <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6530,85 +6530,85 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DG14" t="n">
         <v>2.48</v>
       </c>
-      <c r="DE14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="DH14" t="n">
-        <v>105</v>
+        <v>106.33</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>58.05</v>
+        <v>59.19</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.85</v>
+        <v>9.67</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.55</v>
+        <v>12.81</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.75</v>
+        <v>58.81</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.2</v>
+        <v>14.57</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.9</v>
+        <v>9.24</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.2</v>
+        <v>18.19</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6708,139 +6708,139 @@
         <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" t="n">
-        <v>103.2</v>
+        <v>104.36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.8</v>
+        <v>45.64</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.6</v>
+        <v>10.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.6</v>
+        <v>12.45</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>53</v>
+        <v>54.09</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.2</v>
+        <v>15.64</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.4</v>
+        <v>10.36</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.8</v>
+        <v>5.27</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.1</v>
+        <v>18.82</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.6</v>
+        <v>9.52</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL15" t="n">
         <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BY15" t="n">
         <v>2.05</v>
@@ -6849,55 +6849,55 @@
         <v>2.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="CE15" t="n">
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL15" t="n">
         <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6912,10 +6912,10 @@
         <v>1.6</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX15" t="n">
         <v>1.5</v>
@@ -6933,85 +6933,85 @@
         <v>1.26</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG15" t="n">
         <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>104.15</v>
+        <v>104.71</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.2</v>
+        <v>51.34</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.05</v>
+        <v>6.86</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53.45</v>
+        <v>54</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.05</v>
+        <v>16.72</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.6</v>
+        <v>11.05</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.95</v>
+        <v>19.76</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="H16" t="n">
-        <v>96.8</v>
+        <v>98.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>7.45</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P16" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49.6</v>
+        <v>50.82</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.8</v>
+        <v>14.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.7</v>
+        <v>5.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.7</v>
+        <v>18.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AF16" t="n">
         <v>0.4</v>
@@ -7192,64 +7192,64 @@
         <v>1.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.6</v>
+        <v>5.48</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="BR16" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="CA16" t="n">
         <v>3.77</v>
@@ -7270,34 +7270,34 @@
         <v>2.59</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.73</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL16" t="n">
         <v>1.67</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.93</v>
@@ -7312,10 +7312,10 @@
         <v>3.21</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW16" t="n">
         <v>1.74</v>
@@ -7336,85 +7336,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="DH16" t="n">
-        <v>103</v>
+        <v>103.52</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.35</v>
+        <v>6.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.65</v>
+        <v>58.14</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.55</v>
+        <v>11.43</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.85</v>
+        <v>7.05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.4</v>
+        <v>52.91</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.7</v>
+        <v>12.95</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.050000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.65</v>
+        <v>4.81</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.1</v>
+        <v>18.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7514,130 +7514,130 @@
         <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.5</v>
+        <v>92.09</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.9</v>
+        <v>45.09</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.8</v>
+        <v>11.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.6</v>
+        <v>13.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.2</v>
+        <v>19.91</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.85</v>
+        <v>9.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO17" t="n">
         <v>1.05</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY17" t="n">
         <v>2.69</v>
@@ -7655,22 +7655,22 @@
         <v>2.73</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.42</v>
+        <v>4.22</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CG17" t="n">
         <v>2.97</v>
@@ -7679,7 +7679,7 @@
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.77</v>
@@ -7688,7 +7688,7 @@
         <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM17" t="n">
         <v>2.78</v>
@@ -7703,7 +7703,7 @@
         <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7712,7 +7712,7 @@
         <v>2.86</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7733,7 +7733,7 @@
         <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
@@ -7745,79 +7745,79 @@
         <v>3.23</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG17" t="n">
         <v>2.9</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.8</v>
+        <v>97.33</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM17" t="n">
-        <v>53.35</v>
+        <v>54.48</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.95</v>
+        <v>10.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.3</v>
+        <v>12.43</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.6</v>
+        <v>7.47</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.65</v>
+        <v>49.81</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.35</v>
+        <v>12.38</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.35</v>
+        <v>8.33</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.15</v>
+        <v>19.52</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>87.40000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.8</v>
+        <v>39.36</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.9</v>
+        <v>9.09</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.7</v>
+        <v>16.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BR18" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
         <v>3.82</v>
@@ -8058,55 +8058,55 @@
         <v>4.21</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.94</v>
+        <v>5.79</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL18" t="n">
         <v>1.89</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO18" t="n">
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CR18" t="n">
         <v>1.44</v>
@@ -8145,49 +8145,49 @@
         <v>2.05</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.75</v>
+        <v>87.81</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.6</v>
+        <v>41.28</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.6</v>
+        <v>10.72</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="DS18" t="n">
         <v>0.1</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.3</v>
+        <v>42.62</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.45</v>
+        <v>6.52</v>
       </c>
       <c r="DZ18" t="n">
         <v>3.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.05</v>
+        <v>16.76</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8320,52 +8320,52 @@
         <v>2.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.09999999999999</v>
+        <v>81.91</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN19" t="n">
-        <v>37.2</v>
+        <v>38.36</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.2</v>
+        <v>9.91</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>48</v>
+        <v>48.91</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.699999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.5</v>
+        <v>6.09</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.6</v>
+        <v>19.18</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV19" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY19" t="n">
         <v>2.26</v>
@@ -8467,37 +8467,37 @@
         <v>3.72</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CN19" t="n">
         <v>2.3</v>
@@ -8506,10 +8506,10 @@
         <v>1.25</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
@@ -8524,10 +8524,10 @@
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
         <v>1.47</v>
@@ -8545,52 +8545,52 @@
         <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.75</v>
+        <v>87.86</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.55</v>
+        <v>46.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DP19" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.35</v>
+        <v>10.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.75</v>
+        <v>51.1</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.9</v>
+        <v>10.19</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.5</v>
+        <v>6.76</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.9</v>
+        <v>20.14</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>86.7</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M20" t="n">
-        <v>43.7</v>
+        <v>44.36</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.8</v>
+        <v>11.55</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>42.6</v>
+        <v>43</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.2</v>
+        <v>10.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8807,67 +8807,67 @@
         <v>3.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>11.55</v>
+        <v>11.52</v>
       </c>
       <c r="BI20" t="n">
         <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV20" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW20" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX20" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="CC20" t="n">
         <v>6.47</v>
@@ -8882,10 +8882,10 @@
         <v>2.59</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI20" t="n">
         <v>2.06</v>
@@ -8897,7 +8897,7 @@
         <v>1.36</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM20" t="n">
         <v>2.86</v>
@@ -8909,22 +8909,22 @@
         <v>1.23</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV20" t="n">
         <v>2.16</v>
@@ -8948,85 +8948,85 @@
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="DG20" t="n">
         <v>3.1</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.55</v>
+        <v>89.05</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.05</v>
+        <v>42.47</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.65</v>
+        <v>10.86</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.9</v>
+        <v>11.76</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.1</v>
+        <v>43.29</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.45</v>
+        <v>6.67</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="EA20" t="n">
-        <v>18</v>
+        <v>18.24</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0.2</v>
@@ -9132,46 +9132,46 @@
         <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" t="n">
-        <v>89</v>
+        <v>91.27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.3</v>
+        <v>40.64</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>14.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.5</v>
+        <v>9.18</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,82 +9183,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>42.1</v>
+        <v>43.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.9</v>
+        <v>8.27</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.1</v>
+        <v>16.27</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.95</v>
+        <v>4.76</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV21" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY21" t="n">
         <v>3.56</v>
@@ -9267,25 +9267,25 @@
         <v>3.79</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="CC21" t="n">
-        <v>7.76</v>
+        <v>7.49</v>
       </c>
       <c r="CD21" t="n">
-        <v>9.18</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="CE21" t="n">
         <v>1.37</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG21" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH21" t="n">
         <v>1.45</v>
@@ -9300,37 +9300,37 @@
         <v>1.45</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW21" t="n">
         <v>1.95</v>
@@ -9348,10 +9348,10 @@
         <v>2.01</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD21" t="n">
         <v>2.96</v>
@@ -9360,43 +9360,43 @@
         <v>0.1</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.40000000000001</v>
+        <v>91.52</v>
       </c>
       <c r="DI21" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.55</v>
+        <v>40.24</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.05</v>
+        <v>14.14</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.3</v>
+        <v>10.43</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.95</v>
+        <v>7.86</v>
       </c>
       <c r="DS21" t="n">
         <v>0.1</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>8.9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.75</v>
+        <v>5.86</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.3</v>
+        <v>18.76</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1460,7 +1460,7 @@
         <v>4.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.64</v>
+        <v>21.73</v>
       </c>
       <c r="AD2" t="n">
         <v>1.53</v>
@@ -1607,13 +1607,13 @@
         <v>2.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CA2" t="n">
         <v>3.81</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CC2" t="n">
         <v>4.23</v>
@@ -1661,13 +1661,13 @@
         <v>2.76</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CU2" t="n">
         <v>1.55</v>
@@ -1688,7 +1688,7 @@
         <v>2.49</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
@@ -1697,7 +1697,7 @@
         <v>1.73</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DE2" t="n">
         <v>0.28</v>
@@ -1766,7 +1766,7 @@
         <v>4.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.34</v>
+        <v>19.38</v>
       </c>
       <c r="EB2" t="n">
         <v>1.59</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="H3" t="n">
-        <v>106.7</v>
+        <v>106.73</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>65</v>
+        <v>64.27</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>11.82</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60.4</v>
+        <v>59.27</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.1</v>
+        <v>16.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>11.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.6</v>
+        <v>17.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="CC3" t="n">
         <v>1.81</v>
@@ -2028,7 +2028,7 @@
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG3" t="n">
         <v>3.16</v>
@@ -2040,19 +2040,19 @@
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO3" t="n">
         <v>1.25</v>
@@ -2061,25 +2061,25 @@
         <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU3" t="n">
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
@@ -2088,10 +2088,10 @@
         <v>1.84</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
@@ -2109,73 +2109,73 @@
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.7</v>
+        <v>101</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.85</v>
+        <v>60.67</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP3" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.15</v>
+        <v>11.1</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.6</v>
+        <v>58.09</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.1</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.2</v>
+        <v>17.09</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
@@ -2470,16 +2470,16 @@
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
@@ -2503,7 +2503,7 @@
         <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DE4" t="n">
         <v>0.05</v>
@@ -2669,7 +2669,7 @@
         <v>4.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.36</v>
+        <v>19.45</v>
       </c>
       <c r="AD5" t="n">
         <v>1.37</v>
@@ -2816,13 +2816,13 @@
         <v>2.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CA5" t="n">
         <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC5" t="n">
         <v>3.66</v>
@@ -2885,28 +2885,28 @@
         <v>2.16</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
@@ -2975,7 +2975,7 @@
         <v>4.24</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.76</v>
+        <v>18.81</v>
       </c>
       <c r="EB5" t="n">
         <v>1.26</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="n">
         <v>2.55</v>
@@ -3096,7 +3096,7 @@
         <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AL6" t="n">
         <v>4.36</v>
@@ -3159,7 +3159,7 @@
         <v>1.38</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG6" t="n">
         <v>2.81</v>
@@ -3225,13 +3225,13 @@
         <v>3.76</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CC6" t="n">
         <v>3.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CE6" t="n">
         <v>1.32</v>
@@ -3276,28 +3276,28 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW6" t="n">
         <v>1.67</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY6" t="n">
         <v>1.85</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DA6" t="n">
         <v>2</v>
@@ -3315,7 +3315,7 @@
         <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
         <v>2.48</v>
@@ -3327,7 +3327,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DK6" t="n">
         <v>4.66</v>
@@ -3384,7 +3384,7 @@
         <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -3622,7 +3622,7 @@
         <v>5.3</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.61</v>
+        <v>5.65</v>
       </c>
       <c r="CA7" t="n">
         <v>4.23</v>
@@ -3682,7 +3682,7 @@
         <v>2.79</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU7" t="n">
         <v>1.48</v>
@@ -3697,22 +3697,22 @@
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -4031,13 +4031,13 @@
         <v>3.92</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CC8" t="n">
         <v>2.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4082,16 +4082,16 @@
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW8" t="n">
         <v>1.69</v>
@@ -4106,7 +4106,7 @@
         <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
@@ -4248,7 +4248,7 @@
         <v>9.82</v>
       </c>
       <c r="R9" t="n">
-        <v>8.18</v>
+        <v>8.27</v>
       </c>
       <c r="S9" t="n">
         <v>1.09</v>
@@ -4428,13 +4428,13 @@
         <v>2.57</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CA9" t="n">
         <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC9" t="n">
         <v>3.51</v>
@@ -4488,16 +4488,16 @@
         <v>2.88</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
         <v>1.58</v>
@@ -4515,10 +4515,10 @@
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
@@ -4560,7 +4560,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DS9" t="n">
         <v>0.19</v>
@@ -4651,7 +4651,7 @@
         <v>13.36</v>
       </c>
       <c r="R10" t="n">
-        <v>5.36</v>
+        <v>5.45</v>
       </c>
       <c r="S10" t="n">
         <v>1.36</v>
@@ -4684,7 +4684,7 @@
         <v>3.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.45</v>
+        <v>19.55</v>
       </c>
       <c r="AD10" t="n">
         <v>1.46</v>
@@ -4831,7 +4831,7 @@
         <v>2.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CA10" t="n">
         <v>3.47</v>
@@ -4891,28 +4891,28 @@
         <v>3.07</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
@@ -4921,7 +4921,7 @@
         <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
@@ -4963,7 +4963,7 @@
         <v>12.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.76</v>
+        <v>7.81</v>
       </c>
       <c r="DS10" t="n">
         <v>0.05</v>
@@ -4990,7 +4990,7 @@
         <v>3.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.19</v>
+        <v>19.24</v>
       </c>
       <c r="EB10" t="n">
         <v>1.27</v>
@@ -5234,7 +5234,7 @@
         <v>3.21</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="CA11" t="n">
         <v>3.52</v>
@@ -5288,16 +5288,16 @@
         <v>3.36</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
         <v>2.08</v>
@@ -5315,16 +5315,16 @@
         <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="DE11" t="n">
         <v>0.24</v>
@@ -5637,19 +5637,19 @@
         <v>2.94</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CA12" t="n">
         <v>3.67</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC12" t="n">
         <v>4.64</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
@@ -5697,7 +5697,7 @@
         <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CU12" t="n">
         <v>1.42</v>
@@ -5712,22 +5712,22 @@
         <v>1.61</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0.14</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" t="n">
-        <v>112.4</v>
+        <v>111.09</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.3</v>
+        <v>4.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>59</v>
+        <v>56.82</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.6</v>
+        <v>12.55</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>61.3</v>
+        <v>60.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.2</v>
+        <v>12.73</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.1</v>
+        <v>19.82</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.65</v>
+        <v>5.43</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS13" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
         <v>1.54</v>
@@ -6043,136 +6043,136 @@
         <v>1.6</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="CE13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DB13" t="n">
         <v>1.27</v>
       </c>
-      <c r="CF13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CY13" t="n">
+      <c r="DC13" t="n">
         <v>1.66</v>
       </c>
-      <c r="CZ13" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DD13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE13" t="n">
         <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="DH13" t="n">
-        <v>113.2</v>
+        <v>112.48</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.4</v>
+        <v>5.14</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>61.15</v>
+        <v>59.91</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.4</v>
+        <v>60.95</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.05</v>
+        <v>14.72</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.85</v>
+        <v>10.71</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.05</v>
+        <v>19.91</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="14">
@@ -6227,7 +6227,7 @@
         <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
         <v>2.82</v>
@@ -6239,7 +6239,7 @@
         <v>-0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="K14" t="n">
         <v>7.27</v>
@@ -6287,22 +6287,22 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.45</v>
+        <v>16.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="AB14" t="n">
         <v>6.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.91</v>
+        <v>19</v>
       </c>
       <c r="AD14" t="n">
         <v>1.96</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6449,7 +6449,7 @@
         <v>4.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="CC14" t="n">
         <v>1.88</v>
@@ -6500,7 +6500,7 @@
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT14" t="n">
         <v>3.33</v>
@@ -6509,19 +6509,19 @@
         <v>1.65</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CW14" t="n">
         <v>1.74</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY14" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
         <v>2.07</v>
@@ -6533,13 +6533,13 @@
         <v>1.58</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DE14" t="n">
         <v>0.19</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="DG14" t="n">
         <v>2.48</v>
@@ -6551,7 +6551,7 @@
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="DK14" t="n">
         <v>5.67</v>
@@ -6593,22 +6593,22 @@
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.57</v>
+        <v>14.52</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.24</v>
+        <v>9.19</v>
       </c>
       <c r="DZ14" t="n">
         <v>5.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.19</v>
+        <v>18.24</v>
       </c>
       <c r="EB14" t="n">
         <v>1.72</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="15">
@@ -6900,43 +6900,43 @@
         <v>2.59</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="DE15" t="n">
         <v>0.09</v>
@@ -7309,10 +7309,10 @@
         <v>2.66</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
         <v>2.22</v>
@@ -7336,10 +7336,10 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="DE16" t="n">
         <v>0.24</v>
@@ -7664,7 +7664,7 @@
         <v>4.03</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
@@ -7709,19 +7709,19 @@
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX17" t="n">
         <v>1.57</v>
@@ -8061,13 +8061,13 @@
         <v>3.77</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC18" t="n">
         <v>5.57</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.79</v>
+        <v>5.77</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
@@ -8109,13 +8109,13 @@
         <v>3.57</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU18" t="n">
         <v>1.44</v>
@@ -8127,22 +8127,22 @@
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DD18" t="n">
         <v>3.19</v>
@@ -8272,7 +8272,7 @@
         <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
         <v>10.9</v>
@@ -8458,19 +8458,19 @@
         <v>2.26</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
         <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC19" t="n">
         <v>3.6</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CE19" t="n">
         <v>1.34</v>
@@ -8512,13 +8512,13 @@
         <v>3.03</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CU19" t="n">
         <v>1.46</v>
@@ -8530,13 +8530,13 @@
         <v>1.73</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DA19" t="n">
         <v>2.33</v>
@@ -8548,7 +8548,7 @@
         <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="DE19" t="n">
         <v>0.14</v>
@@ -8584,7 +8584,7 @@
         <v>2.57</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.95</v>
+        <v>10.91</v>
       </c>
       <c r="DQ19" t="n">
         <v>10.95</v>
@@ -8861,7 +8861,7 @@
         <v>3.59</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CA20" t="n">
         <v>3.67</v>
@@ -8918,16 +8918,16 @@
         <v>1.37</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW20" t="n">
         <v>1.76</v>
@@ -9159,7 +9159,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.64</v>
+        <v>14.55</v>
       </c>
       <c r="AR21" t="n">
         <v>10.36</v>
@@ -9189,10 +9189,10 @@
         <v>0.18</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.55</v>
+        <v>5.64</v>
       </c>
       <c r="BC21" t="n">
         <v>2.73</v>
@@ -9276,7 +9276,7 @@
         <v>7.49</v>
       </c>
       <c r="CD21" t="n">
-        <v>8.789999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="CE21" t="n">
         <v>1.37</v>
@@ -9321,40 +9321,40 @@
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW21" t="n">
         <v>1.95</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC21" t="n">
         <v>1.93</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="DE21" t="n">
         <v>0.1</v>
@@ -9390,7 +9390,7 @@
         <v>1.38</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="DQ21" t="n">
         <v>10.43</v>
@@ -9414,10 +9414,10 @@
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.86</v>
+        <v>5.91</v>
       </c>
       <c r="DZ21" t="n">
         <v>3.19</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.7</v>
+        <v>94.91</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.6</v>
+        <v>5.91</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.7</v>
+        <v>57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.2</v>
+        <v>10.55</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.8</v>
+        <v>57.09</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.3</v>
+        <v>13.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.8</v>
+        <v>16.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY3" t="n">
         <v>1.42</v>
@@ -2013,25 +2013,25 @@
         <v>1.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2046,37 +2046,37 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO3" t="n">
         <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
         <v>2.04</v>
@@ -2085,76 +2085,76 @@
         <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.45</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>101</v>
+        <v>100.82</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.67</v>
+        <v>60.63</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.949999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.09</v>
+        <v>58.18</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
@@ -2163,19 +2163,19 @@
         <v>14.9</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.09</v>
+        <v>16.77</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="H4" t="n">
-        <v>89.59999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>43.3</v>
+        <v>44.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="P4" t="n">
-        <v>9.9</v>
+        <v>10.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.2</v>
+        <v>17.18</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.5</v>
+        <v>52.64</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.9</v>
+        <v>12.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>7.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>14.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,70 +2356,70 @@
         <v>1.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2434,7 +2434,7 @@
         <v>2.7</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
@@ -2446,25 +2446,25 @@
         <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM4" t="n">
         <v>2.72</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
         <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,22 +2479,22 @@
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
@@ -2503,49 +2503,49 @@
         <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF4" t="n">
         <v>1.09</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>86</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DK4" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.71</v>
+        <v>44.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.859999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="DQ4" t="n">
         <v>16.86</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.43</v>
+        <v>8.32</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.66</v>
+        <v>11.95</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.38</v>
+        <v>7.64</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.24</v>
+        <v>15.46</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>84.7</v>
+        <v>86.73</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.7</v>
+        <v>41.45</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.2</v>
+        <v>49.64</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.1</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>5.73</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.1</v>
+        <v>18.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP5" t="n">
         <v>4.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>2.96</v>
@@ -2819,73 +2819,73 @@
         <v>3.1</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
         <v>3.64</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL5" t="n">
         <v>1.74</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CT5" t="n">
         <v>3.16</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2912,76 +2912,76 @@
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.52</v>
+        <v>89.36</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.86</v>
+        <v>43.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.52</v>
+        <v>10.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.86</v>
+        <v>6.82</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.29</v>
+        <v>46.64</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.28</v>
+        <v>10.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.05</v>
+        <v>6.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.81</v>
+        <v>18.9</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.5</v>
+        <v>81.09</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.8</v>
+        <v>33.36</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>10.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.9</v>
+        <v>38.73</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.8</v>
+        <v>16.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY7" t="n">
         <v>5.3</v>
@@ -3625,34 +3625,34 @@
         <v>5.65</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.23</v>
+        <v>4.35</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.36</v>
+        <v>7.83</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.77</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CH7" t="n">
         <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
         <v>1.42</v>
@@ -3661,19 +3661,19 @@
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3697,97 +3697,97 @@
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.37</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB7" t="n">
         <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>86.14</v>
+        <v>85.72</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.19</v>
+        <v>36.82</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.33</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.14</v>
+        <v>11.36</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.24</v>
+        <v>40.59</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="DY7" t="n">
         <v>5.91</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.95</v>
+        <v>17.68</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>107</v>
+        <v>104.45</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="K8" t="n">
-        <v>7.3</v>
+        <v>6.91</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>63.9</v>
+        <v>61.64</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>11.2</v>
+        <v>10.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.9</v>
+        <v>12.55</v>
       </c>
       <c r="R8" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.7</v>
+        <v>58.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.2</v>
+        <v>14.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.8</v>
+        <v>14.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.24</v>
+        <v>10.32</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.86</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.48</v>
+        <v>5.55</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC8" t="n">
         <v>2.33</v>
@@ -4040,49 +4040,49 @@
         <v>2.51</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH8" t="n">
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.66</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP8" t="n">
         <v>1.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
         <v>3.25</v>
@@ -4100,13 +4100,13 @@
         <v>1.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
@@ -4118,79 +4118,79 @@
         <v>2.82</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="DH8" t="n">
-        <v>102.19</v>
+        <v>101.14</v>
       </c>
       <c r="DI8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.14</v>
       </c>
-      <c r="DJ8" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.1</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.71</v>
+        <v>57.18</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.91</v>
+        <v>13.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.1</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.81</v>
+        <v>4.68</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.95</v>
+        <v>15.82</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.90000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL9" t="n">
         <v>4</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>39</v>
+        <v>38.91</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>10.91</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.9</v>
+        <v>9.73</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.7</v>
+        <v>8.09</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.2</v>
+        <v>42.27</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.5</v>
+        <v>6.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.5</v>
+        <v>15.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="BR9" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY9" t="n">
         <v>2.57</v>
@@ -4431,169 +4431,169 @@
         <v>2.66</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
         <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN9" t="n">
         <v>1.98</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
         <v>3.17</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG9" t="n">
         <v>1.86</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.23999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DK9" t="n">
         <v>3.91</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.24</v>
+        <v>43</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="DO9" t="n">
         <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.81</v>
+        <v>10.04</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.05</v>
+        <v>43.04</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.71</v>
+        <v>11.46</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.86</v>
+        <v>7.68</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.19</v>
+        <v>16.95</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.09</v>
@@ -4693,52 +4693,52 @@
         <v>2.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>88</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>41</v>
+        <v>40.09</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.3</v>
+        <v>11.73</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>39.1</v>
+        <v>38.82</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.9</v>
+        <v>18.27</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.43</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
         <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.71</v>
+        <v>3.86</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY10" t="n">
         <v>2.66</v>
@@ -4834,22 +4834,22 @@
         <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.26</v>
+        <v>4.44</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG10" t="n">
         <v>2.83</v>
@@ -4858,7 +4858,7 @@
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.83</v>
@@ -4867,7 +4867,7 @@
         <v>1.45</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM10" t="n">
         <v>2.6</v>
@@ -4879,19 +4879,19 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4903,22 +4903,22 @@
         <v>1.89</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD10" t="n">
         <v>3.28</v>
@@ -4927,73 +4927,73 @@
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.76000000000001</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
         <v>2.09</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.38</v>
+        <v>48.54</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.29</v>
+        <v>10.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.38</v>
+        <v>12.54</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.81</v>
+        <v>7.86</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.95</v>
+        <v>42.64</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.86</v>
+        <v>10.77</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.72</v>
+        <v>7.64</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.24</v>
+        <v>18.91</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
         <v>1.86</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5096,52 +5096,52 @@
         <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AI11" t="n">
-        <v>87.40000000000001</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.2</v>
+        <v>41.27</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>11.45</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.3</v>
+        <v>49.73</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.8</v>
+        <v>10.55</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.1</v>
+        <v>19.73</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP11" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>5.14</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.1</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY11" t="n">
         <v>3.21</v>
@@ -5237,16 +5237,16 @@
         <v>3.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5261,7 +5261,7 @@
         <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.78</v>
@@ -5270,13 +5270,13 @@
         <v>1.37</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
@@ -5294,7 +5294,7 @@
         <v>2.94</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
@@ -5309,13 +5309,13 @@
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
@@ -5327,79 +5327,79 @@
         <v>3.38</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH11" t="n">
-        <v>88</v>
+        <v>88.36</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.19</v>
+        <v>47</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DP11" t="n">
         <v>11.09</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.33</v>
+        <v>11.09</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.9</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.24</v>
+        <v>51.36</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.95</v>
+        <v>11.78</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.19</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.19</v>
+        <v>20</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="H12" t="n">
-        <v>96.5</v>
+        <v>96.73</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>42.5</v>
+        <v>41.91</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>10.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.5</v>
+        <v>13.27</v>
       </c>
       <c r="R12" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.6</v>
+        <v>45.64</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.3</v>
+        <v>15.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.5</v>
+        <v>18.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.18</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.33</v>
+        <v>8.41</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC12" t="n">
         <v>4.64</v>
@@ -5655,10 +5655,10 @@
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CH12" t="n">
         <v>1.42</v>
@@ -5673,7 +5673,7 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM12" t="n">
         <v>2.5</v>
@@ -5685,19 +5685,19 @@
         <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
         <v>3.39</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU12" t="n">
         <v>1.42</v>
@@ -5709,13 +5709,13 @@
         <v>1.89</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY12" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
         <v>1.93</v>
@@ -5733,76 +5733,76 @@
         <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.81</v>
+        <v>89.28</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.48</v>
+        <v>4.59</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.81</v>
+        <v>43.46</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.14</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DQ12" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
         <v>12.81</v>
       </c>
-      <c r="DR12" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX12" t="n">
-        <v>12.76</v>
-      </c>
       <c r="DY12" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.43</v>
+        <v>17.59</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="H13" t="n">
-        <v>114</v>
+        <v>117.45</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>5.82</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>63.3</v>
+        <v>69.27</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="R13" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>61.5</v>
+        <v>62.55</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.9</v>
+        <v>18.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.3</v>
+        <v>13.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.6</v>
+        <v>5.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>20.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.27</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BO13" t="n">
         <v>0.86</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.49</v>
+        <v>4.61</v>
       </c>
       <c r="CC13" t="n">
         <v>2.34</v>
@@ -6055,40 +6055,40 @@
         <v>2.44</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CH13" t="n">
         <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CK13" t="n">
         <v>1.37</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.5</v>
@@ -6127,85 +6127,85 @@
         <v>1.27</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>112.48</v>
+        <v>114.27</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.14</v>
+        <v>5.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>59.91</v>
+        <v>63.04</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.81</v>
+        <v>11.69</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.95</v>
+        <v>61.5</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.72</v>
+        <v>15.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.71</v>
+        <v>11.18</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.91</v>
+        <v>20.14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6305,196 +6305,196 @@
         <v>1.36</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>103.4</v>
+        <v>106</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AN14" t="n">
-        <v>52.3</v>
+        <v>55.45</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.4</v>
+        <v>12.91</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>58.3</v>
+        <v>59.18</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT14" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="BZ14" t="n">
         <v>1.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="CC14" t="n">
         <v>1.88</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
@@ -6506,25 +6506,25 @@
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6533,49 +6533,49 @@
         <v>1.58</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.33</v>
+        <v>107.5</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.19</v>
+        <v>60.45</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.81</v>
+        <v>13.04</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.62</v>
+        <v>5.68</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.81</v>
+        <v>59.22</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.52</v>
+        <v>14.18</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.24</v>
+        <v>18</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
-        <v>105.1</v>
+        <v>102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M15" t="n">
-        <v>57.6</v>
+        <v>55.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>10.4</v>
+        <v>10.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.4</v>
+        <v>12.09</v>
       </c>
       <c r="R15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>53.9</v>
+        <v>51.91</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.9</v>
+        <v>17.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.8</v>
+        <v>11.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.8</v>
+        <v>20.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6789,70 +6789,70 @@
         <v>1.27</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.52</v>
+        <v>9.41</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT15" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV15" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC15" t="n">
         <v>2.71</v>
@@ -6864,70 +6864,70 @@
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK15" t="n">
         <v>1.39</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CR15" t="n">
         <v>1.35</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CT15" t="n">
         <v>3.28</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
@@ -6936,46 +6936,46 @@
         <v>1.67</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="DE15" t="n">
         <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH15" t="n">
-        <v>104.71</v>
+        <v>103.18</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.76</v>
+        <v>4.59</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.34</v>
+        <v>50.68</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.43</v>
+        <v>12.27</v>
       </c>
       <c r="DR15" t="n">
         <v>6.86</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.72</v>
+        <v>16.45</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.76</v>
+        <v>19.59</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -7111,52 +7111,52 @@
         <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AI16" t="n">
-        <v>109.2</v>
+        <v>110.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN16" t="n">
-        <v>61.6</v>
+        <v>63.09</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>55.2</v>
+        <v>56.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.5</v>
+        <v>18.82</v>
       </c>
       <c r="BE16" t="n">
         <v>1.44</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.71</v>
+        <v>11.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY16" t="n">
         <v>2.19</v>
@@ -7252,16 +7252,16 @@
         <v>2.22</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CC16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CD16" t="n">
         <v>2.34</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>2.4</v>
       </c>
       <c r="CE16" t="n">
         <v>1.33</v>
@@ -7270,7 +7270,7 @@
         <v>2.59</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
@@ -7279,16 +7279,16 @@
         <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK16" t="n">
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN16" t="n">
         <v>2.21</v>
@@ -7297,10 +7297,10 @@
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,7 +7315,7 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW16" t="n">
         <v>1.74</v>
@@ -7336,85 +7336,85 @@
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="DH16" t="n">
-        <v>103.52</v>
+        <v>104.36</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>58.14</v>
+        <v>59.04</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.949999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.43</v>
+        <v>11.59</v>
       </c>
       <c r="DR16" t="n">
         <v>7.05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.91</v>
+        <v>53.54</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.95</v>
+        <v>12.91</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.140000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.81</v>
+        <v>4.68</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.95</v>
+        <v>18.64</v>
       </c>
       <c r="EB16" t="n">
         <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="H17" t="n">
-        <v>103.1</v>
+        <v>101.91</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M17" t="n">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>11.27</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51.8</v>
+        <v>50.73</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.9</v>
+        <v>14.09</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.7</v>
+        <v>10.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.1</v>
+        <v>19.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7595,49 +7595,49 @@
         <v>1.91</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.9</v>
+        <v>10.05</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU17" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CC17" t="n">
         <v>4.03</v>
@@ -7670,7 +7670,7 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG17" t="n">
         <v>2.97</v>
@@ -7679,112 +7679,112 @@
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CJ17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CL17" t="n">
         <v>1.77</v>
       </c>
-      <c r="CK17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CM17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO17" t="n">
         <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CX17" t="n">
         <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="DE17" t="n">
         <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.33</v>
+        <v>97</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.48</v>
+        <v>54.54</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.47</v>
+        <v>7.64</v>
       </c>
       <c r="DS17" t="n">
         <v>0.09</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.81</v>
+        <v>49.36</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.38</v>
+        <v>12.09</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.52</v>
+        <v>19.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>88.09999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M18" t="n">
-        <v>43.4</v>
+        <v>45.36</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.7</v>
+        <v>11.09</v>
       </c>
       <c r="R18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>42.2</v>
+        <v>43.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.2</v>
+        <v>10.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.4</v>
+        <v>18.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>1.73</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS18" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="BZ18" t="n">
-        <v>4.21</v>
+        <v>4.06</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC18" t="n">
         <v>5.57</v>
@@ -8076,7 +8076,7 @@
         <v>2.92</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
@@ -8091,34 +8091,34 @@
         <v>1.47</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CU18" t="n">
         <v>1.43</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>1.44</v>
       </c>
       <c r="CV18" t="n">
         <v>1.94</v>
@@ -8130,19 +8130,19 @@
         <v>1.59</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD18" t="n">
         <v>3.19</v>
@@ -8151,76 +8151,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.81</v>
+        <v>88.64</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.28</v>
+        <v>42.36</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.72</v>
+        <v>10.91</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.81</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>42.62</v>
+        <v>43.28</v>
       </c>
       <c r="DW18" t="n">
         <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.76</v>
+        <v>17.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="H19" t="n">
-        <v>94.40000000000001</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>5.82</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M19" t="n">
-        <v>55.9</v>
+        <v>58.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.9</v>
+        <v>11.45</v>
       </c>
       <c r="R19" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53.5</v>
+        <v>54.27</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.5</v>
+        <v>8.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.2</v>
+        <v>20.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>0.09</v>
@@ -8401,67 +8401,67 @@
         <v>2.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.24</v>
+        <v>10.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.48</v>
+        <v>4.77</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS19" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CB19" t="n">
         <v>3.71</v>
@@ -8476,16 +8476,16 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
@@ -8497,19 +8497,19 @@
         <v>1.63</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CN19" t="n">
         <v>2.3</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8533,7 +8533,7 @@
         <v>1.48</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.62</v>
@@ -8545,52 +8545,52 @@
         <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
         <v>1.91</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.86</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.19</v>
+        <v>5.46</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.71</v>
+        <v>48.22</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.91</v>
+        <v>10.96</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.95</v>
+        <v>11.22</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.1</v>
+        <v>51.59</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.19</v>
+        <v>10.68</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.76</v>
+        <v>7.13</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.43</v>
+        <v>3.54</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.14</v>
+        <v>20.05</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0.27</v>
@@ -8726,136 +8726,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>90.40000000000001</v>
+        <v>87.91</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.4</v>
+        <v>40.18</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>43.6</v>
+        <v>43.09</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>10.09</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.3</v>
+        <v>6.91</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.4</v>
+        <v>16.91</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BH20" t="n">
-        <v>11.52</v>
+        <v>11.73</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.76</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT20" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY20" t="n">
         <v>3.59</v>
@@ -8864,55 +8864,55 @@
         <v>3.59</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.47</v>
+        <v>5.11</v>
       </c>
       <c r="CD20" t="n">
-        <v>7.04</v>
+        <v>6.8</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="CM20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CQ20" t="n">
         <v>2.86</v>
-      </c>
-      <c r="CN20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CO20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CP20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CQ20" t="n">
-        <v>2.96</v>
       </c>
       <c r="CR20" t="n">
         <v>1.37</v>
@@ -8930,7 +8930,7 @@
         <v>2.17</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX20" t="n">
         <v>1.49</v>
@@ -8957,43 +8957,43 @@
         <v>0.14</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="DH20" t="n">
-        <v>89.05</v>
+        <v>87.86</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.47</v>
+        <v>42.27</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.86</v>
+        <v>11.14</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.76</v>
+        <v>11.78</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.81</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS20" t="n">
         <v>0.09</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.29</v>
+        <v>43.04</v>
       </c>
       <c r="DW20" t="n">
         <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.67</v>
+        <v>6.95</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.24</v>
+        <v>17.95</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H21" t="n">
-        <v>91.8</v>
+        <v>90.55</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>39.8</v>
+        <v>39.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>13.6</v>
+        <v>13.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="R21" t="n">
-        <v>6.4</v>
+        <v>6.91</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.7</v>
+        <v>45.45</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9.9</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>21.5</v>
+        <v>20.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.55</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.48</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
       <c r="BR21" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS21" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV21" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.79</v>
+        <v>3.88</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="CC21" t="n">
         <v>7.49</v>
@@ -9282,19 +9282,19 @@
         <v>1.37</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH21" t="n">
         <v>1.45</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK21" t="n">
         <v>1.45</v>
@@ -9303,19 +9303,19 @@
         <v>1.86</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
@@ -9330,103 +9330,103 @@
         <v>1.48</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DB21" t="n">
         <v>1.33</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DD21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.52</v>
+        <v>90.91</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.24</v>
+        <v>40.04</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DP21" t="n">
         <v>14.1</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.43</v>
+        <v>10.46</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.86</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.9</v>
+        <v>44.36</v>
       </c>
       <c r="DW21" t="n">
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.09</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.76</v>
+        <v>18.55</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC21" t="n">
         <v>2.05</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>2.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>89.7</v>
+        <v>89.09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>51</v>
+        <v>50.45</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.8</v>
+        <v>12.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.9</v>
+        <v>45.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.8</v>
+        <v>17.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.33</v>
+        <v>10.64</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.86</v>
+        <v>6.05</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU2" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY2" t="n">
         <v>2.4</v>
@@ -1616,28 +1616,28 @@
         <v>3.98</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK2" t="n">
         <v>1.35</v>
@@ -1646,19 +1646,19 @@
         <v>1.69</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CN2" t="n">
         <v>2.19</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
@@ -1673,10 +1673,10 @@
         <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.76000000000001</v>
+        <v>96.14</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.62</v>
+        <v>51.32</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.86</v>
+        <v>12.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.76</v>
+        <v>10.59</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
       <c r="DS2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="DW2" t="n">
         <v>0.09</v>
       </c>
-      <c r="DT2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>50.57</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.1</v>
-      </c>
       <c r="DX2" t="n">
-        <v>13.76</v>
+        <v>13.64</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.38</v>
+        <v>19.45</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="3">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.64</v>
+        <v>52.55</v>
       </c>
       <c r="Y4" t="n">
         <v>0.09</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.5</v>
+        <v>53.46</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="H6" t="n">
-        <v>97.90000000000001</v>
+        <v>101.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>57.6</v>
+        <v>59.73</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="P6" t="n">
-        <v>11.1</v>
+        <v>10.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.8</v>
+        <v>11.45</v>
       </c>
       <c r="R6" t="n">
-        <v>8.6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.3</v>
+        <v>53.64</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.4</v>
+        <v>14.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.8</v>
+        <v>15.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,64 +3162,64 @@
         <v>3.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.289999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>5.14</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CA6" t="n">
         <v>3.76</v>
@@ -3237,16 +3237,16 @@
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.63</v>
@@ -3258,19 +3258,19 @@
         <v>1.86</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
@@ -3285,106 +3285,106 @@
         <v>1.54</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.56</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.41</v>
       </c>
       <c r="DA6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.05</v>
+        <v>95</v>
       </c>
       <c r="DI6" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.66</v>
+        <v>4.95</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DM6" t="n">
-        <v>52.62</v>
+        <v>53.91</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.28</v>
+        <v>12.04</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.72</v>
+        <v>10.59</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.85</v>
+        <v>52.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.19</v>
+        <v>13.37</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.76</v>
+        <v>8.91</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.19</v>
+        <v>16.45</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38.82</v>
+        <v>38.91</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.09</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.64</v>
+        <v>42.68</v>
       </c>
       <c r="DW10" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H2" t="n">
-        <v>103.18</v>
+        <v>100.58</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>52.18</v>
+        <v>50.58</v>
       </c>
       <c r="N2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>12.91</v>
+        <v>12.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="R2" t="n">
-        <v>7.09</v>
+        <v>7.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.91</v>
+        <v>52.17</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.73</v>
+        <v>21.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.36</v>
@@ -1550,67 +1550,67 @@
         <v>2.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU2" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB2" t="n">
         <v>3.98</v>
@@ -1625,16 +1625,16 @@
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CH2" t="n">
         <v>1.53</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1643,10 +1643,10 @@
         <v>1.35</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CN2" t="n">
         <v>2.19</v>
@@ -1655,16 +1655,16 @@
         <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT2" t="n">
         <v>3.16</v>
@@ -1673,7 +1673,7 @@
         <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW2" t="n">
         <v>1.67</v>
@@ -1682,7 +1682,7 @@
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.49</v>
@@ -1694,52 +1694,52 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.14</v>
+        <v>95.08</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.32</v>
+        <v>50.52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.54</v>
+        <v>12.31</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.59</v>
+        <v>10.44</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.68</v>
+        <v>7.74</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.78</v>
+        <v>49.05</v>
       </c>
       <c r="DW2" t="n">
         <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.64</v>
+        <v>13.57</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.82</v>
+        <v>8.74</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.82</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.45</v>
+        <v>19.26</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="H3" t="n">
-        <v>106.73</v>
+        <v>106.33</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="K3" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="L3" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>64.27</v>
+        <v>64</v>
       </c>
       <c r="N3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O3" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P3" t="n">
-        <v>9.73</v>
+        <v>9.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.82</v>
+        <v>11.58</v>
       </c>
       <c r="R3" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.27</v>
+        <v>59.08</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.36</v>
+        <v>16.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.36</v>
+        <v>17.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.91</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.82</v>
+        <v>8.91</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="CC3" t="n">
         <v>1.78</v>
@@ -2025,13 +2025,13 @@
         <v>1.89</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2040,16 +2040,16 @@
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN3" t="n">
         <v>2.02</v>
@@ -2058,10 +2058,10 @@
         <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
@@ -2076,10 +2076,10 @@
         <v>1.52</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
@@ -2097,49 +2097,49 @@
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.82</v>
+        <v>100.87</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.78</v>
+        <v>5.92</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.63</v>
+        <v>60.65</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.14</v>
+        <v>10.17</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="DR3" t="n">
         <v>5</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.18</v>
+        <v>58.13</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.9</v>
+        <v>14.91</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="EB3" t="n">
         <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI4" t="n">
-        <v>82.73</v>
+        <v>84</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.09</v>
+        <v>44.83</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.55</v>
+        <v>15.92</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>54.36</v>
+        <v>53.17</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.45</v>
+        <v>11.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.73</v>
+        <v>4.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.36</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.73</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO4" t="n">
         <v>1.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY4" t="n">
         <v>2.36</v>
@@ -2416,7 +2416,7 @@
         <v>2.42</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB4" t="n">
         <v>3.78</v>
@@ -2425,46 +2425,46 @@
         <v>3.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,7 +2479,7 @@
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
@@ -2488,64 +2488,64 @@
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="DE4" t="n">
         <v>0.04</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.95999999999999</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.22</v>
+        <v>44.61</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.86</v>
+        <v>16.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.46</v>
+        <v>52.87</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.95</v>
+        <v>12.04</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.32</v>
+        <v>4.48</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.46</v>
+        <v>15.31</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>92</v>
+        <v>96.83</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>44.82</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="R5" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>43.64</v>
+        <v>45.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.36</v>
+        <v>11.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.73</v>
+        <v>6.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.45</v>
+        <v>19.83</v>
       </c>
       <c r="AD5" t="n">
         <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,64 +2759,64 @@
         <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.82</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="CA5" t="n">
         <v>3.62</v>
@@ -2837,25 +2837,25 @@
         <v>2.71</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.73</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
         <v>1.74</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN5" t="n">
         <v>2.13</v>
@@ -2873,28 +2873,28 @@
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW5" t="n">
         <v>1.77</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
         <v>1.75</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DA5" t="n">
         <v>2.12</v>
@@ -2906,49 +2906,49 @@
         <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.36</v>
+        <v>92</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="DL5" t="n">
         <v>0.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>43.14</v>
+        <v>44.87</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.82</v>
+        <v>6.74</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.64</v>
+        <v>47.48</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.23</v>
+        <v>6.35</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.9</v>
+        <v>19.13</v>
       </c>
       <c r="EB5" t="n">
         <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AI6" t="n">
-        <v>88.64</v>
+        <v>89.42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.09</v>
+        <v>48.92</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.36</v>
+        <v>12.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.45</v>
+        <v>51.42</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.09</v>
+        <v>12.17</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.45</v>
+        <v>17.17</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.640000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>2.06</v>
@@ -3222,64 +3222,64 @@
         <v>2.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="CE6" t="n">
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG6" t="n">
         <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.63</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.74</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU6" t="n">
         <v>1.54</v>
@@ -3306,52 +3306,52 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DE6" t="n">
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DH6" t="n">
-        <v>95</v>
+        <v>95.13</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.91</v>
+        <v>54.09</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.04</v>
+        <v>11.78</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.77</v>
+        <v>7.78</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.54</v>
+        <v>52.48</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.37</v>
+        <v>13.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.91</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.45</v>
+        <v>16.35</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>90.36</v>
+        <v>91.17</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="L7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>40.27</v>
+        <v>39.42</v>
       </c>
       <c r="N7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="R7" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>42.45</v>
+        <v>42.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.64</v>
+        <v>6.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>18.92</v>
       </c>
       <c r="AD7" t="n">
         <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1.91</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.68</v>
+        <v>9.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX7" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.65</v>
+        <v>5.52</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="CC7" t="n">
         <v>7.83</v>
@@ -3637,22 +3637,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH7" t="n">
         <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK7" t="n">
         <v>1.42</v>
@@ -3661,19 +3661,19 @@
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN7" t="n">
         <v>2.06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3694,25 +3694,25 @@
         <v>2</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB7" t="n">
         <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3721,40 +3721,40 @@
         <v>0.96</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.72</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="DL7" t="n">
         <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.82</v>
+        <v>36.52</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.04</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.279999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.36</v>
+        <v>11.21</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.59</v>
+        <v>40.48</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
         <v>8.82</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.91</v>
+        <v>5.87</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
       <c r="EB7" t="n">
         <v>1.04</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>97.81999999999999</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.73</v>
+        <v>46.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.73</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>55.91</v>
+        <v>56</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.73</v>
+        <v>12.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.91</v>
+        <v>7.58</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>16.92</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.32</v>
+        <v>10.26</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY8" t="n">
         <v>1.91</v>
@@ -4028,19 +4028,19 @@
         <v>1.97</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.93</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.95</v>
-      </c>
       <c r="CC8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF8" t="n">
         <v>2.46</v>
@@ -4061,7 +4061,7 @@
         <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
         <v>2.69</v>
@@ -4070,22 +4070,22 @@
         <v>2.07</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP8" t="n">
         <v>1.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
@@ -4112,85 +4112,85 @@
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DH8" t="n">
-        <v>101.14</v>
+        <v>100.04</v>
       </c>
       <c r="DI8" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>54.68</v>
+        <v>53.91</v>
       </c>
       <c r="DN8" t="n">
         <v>0.87</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.28</v>
+        <v>11.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.14</v>
+        <v>13.05</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.18</v>
+        <v>57.17</v>
       </c>
       <c r="DW8" t="n">
         <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.54</v>
+        <v>13.39</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="H9" t="n">
-        <v>85.27</v>
+        <v>87.25</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>47.09</v>
+        <v>47.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.82</v>
+        <v>9.92</v>
       </c>
       <c r="R9" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="S9" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.82</v>
+        <v>43.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.09</v>
+        <v>8.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.73</v>
+        <v>18.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
         <v>0.91</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC9" t="n">
         <v>3.49</v>
@@ -4449,16 +4449,16 @@
         <v>2.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
         <v>1.48</v>
@@ -4473,31 +4473,31 @@
         <v>1.98</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
         <v>1.59</v>
@@ -4512,61 +4512,61 @@
         <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.27</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DK9" t="n">
         <v>3.91</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM9" t="n">
-        <v>43</v>
+        <v>43.26</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.04</v>
+        <v>10.09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -4575,25 +4575,25 @@
         <v>43.04</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.46</v>
+        <v>11.52</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.68</v>
+        <v>7.61</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.77</v>
+        <v>3.91</v>
       </c>
       <c r="EA9" t="n">
         <v>16.95</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H11" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M11" t="n">
+        <v>52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.45</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>88.55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>53</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0.36</v>
@@ -5177,70 +5177,70 @@
         <v>2.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.23</v>
+        <v>10.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC11" t="n">
         <v>3.48</v>
@@ -5255,16 +5255,16 @@
         <v>2.8</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CH11" t="n">
         <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK11" t="n">
         <v>1.37</v>
@@ -5279,31 +5279,31 @@
         <v>2.11</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
         <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5321,52 +5321,52 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.36</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>47</v>
+        <v>46.87</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.09</v>
+        <v>11.04</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.09</v>
+        <v>10.87</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DS11" t="n">
         <v>0.04</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.36</v>
+        <v>51.26</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="EA11" t="n">
-        <v>20</v>
+        <v>20.17</v>
       </c>
       <c r="EB11" t="n">
         <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.18</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AI13" t="n">
-        <v>111.09</v>
+        <v>112.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.82</v>
+        <v>5.33</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>56.82</v>
+        <v>58.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.27</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.55</v>
+        <v>12.17</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>60.45</v>
+        <v>61</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.27</v>
+        <v>9.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.82</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
         <v>1.09</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY13" t="n">
         <v>1.51</v>
@@ -6043,16 +6043,16 @@
         <v>1.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="CE13" t="n">
         <v>1.27</v>
@@ -6067,10 +6067,10 @@
         <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK13" t="n">
         <v>1.37</v>
@@ -6079,25 +6079,25 @@
         <v>1.68</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN13" t="n">
         <v>2.19</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP13" t="n">
         <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CT13" t="n">
         <v>3.25</v>
@@ -6106,10 +6106,10 @@
         <v>1.63</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6130,49 +6130,49 @@
         <v>1.65</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE13" t="n">
         <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>114.27</v>
+        <v>114.87</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.32</v>
+        <v>5.56</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>63.04</v>
+        <v>63.65</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.59</v>
+        <v>9.48</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.69</v>
+        <v>11.52</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.5</v>
+        <v>61.74</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.5</v>
+        <v>15.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.18</v>
+        <v>11.13</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.14</v>
+        <v>20.22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="K14" t="n">
-        <v>7.27</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M14" t="n">
-        <v>65.45</v>
+        <v>63.58</v>
       </c>
       <c r="N14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.18</v>
+        <v>13.25</v>
       </c>
       <c r="R14" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.27</v>
+        <v>59.67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.36</v>
+        <v>15.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.91</v>
+        <v>9.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>19</v>
+        <v>19.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0.18</v>
@@ -6386,70 +6386,70 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.55</v>
+        <v>4.39</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX14" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="CC14" t="n">
         <v>1.88</v>
@@ -6458,7 +6458,7 @@
         <v>1.99</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF14" t="n">
         <v>2.19</v>
@@ -6473,7 +6473,7 @@
         <v>2.1</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK14" t="n">
         <v>1.38</v>
@@ -6482,16 +6482,16 @@
         <v>1.72</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO14" t="n">
         <v>1.1</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.3</v>
@@ -6506,13 +6506,13 @@
         <v>3.33</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
@@ -6536,79 +6536,79 @@
         <v>2.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.5</v>
+        <v>108.09</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="EB14" t="n">
         <v>1.68</v>
       </c>
-      <c r="DK14" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>60.45</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV14" t="n">
-        <v>59.22</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>18</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="EC14" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.09</v>
@@ -6708,139 +6708,139 @@
         <v>1.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>104.36</v>
+        <v>102.42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>45.64</v>
+        <v>43.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.36</v>
+        <v>10.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.45</v>
+        <v>12.58</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>54.09</v>
+        <v>53.17</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>15.64</v>
+        <v>15.17</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.36</v>
+        <v>10.08</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.82</v>
+        <v>18.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.41</v>
+        <v>9.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY15" t="n">
         <v>2.18</v>
@@ -6849,22 +6849,22 @@
         <v>2.15</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="CE15" t="n">
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG15" t="n">
         <v>3.34</v>
@@ -6873,7 +6873,7 @@
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.61</v>
@@ -6882,13 +6882,13 @@
         <v>1.39</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
@@ -6897,7 +6897,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR15" t="n">
         <v>1.35</v>
@@ -6909,10 +6909,10 @@
         <v>3.28</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW15" t="n">
         <v>1.64</v>
@@ -6936,82 +6936,82 @@
         <v>1.67</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.18</v>
+        <v>102.22</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DM15" t="n">
-        <v>50.68</v>
+        <v>49.26</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.27</v>
+        <v>12.35</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>53</v>
+        <v>52.57</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.45</v>
+        <v>16.17</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.72</v>
+        <v>10.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.59</v>
+        <v>19.26</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G16" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="H16" t="n">
-        <v>98.36</v>
+        <v>99.75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="L16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.82</v>
+        <v>51.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.18</v>
+        <v>14.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.45</v>
+        <v>18.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0.36</v>
@@ -7192,70 +7192,70 @@
         <v>1.45</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.68</v>
+        <v>11.65</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="BR16" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CA16" t="n">
         <v>3.78</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC16" t="n">
         <v>2.28</v>
@@ -7267,19 +7267,19 @@
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK16" t="n">
         <v>1.35</v>
@@ -7300,7 +7300,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,16 +7315,16 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
@@ -7339,82 +7339,82 @@
         <v>1.8</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.36</v>
+        <v>104.82</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>59.04</v>
+        <v>59.13</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.59</v>
+        <v>11.61</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.54</v>
+        <v>53.82</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.91</v>
+        <v>13</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.220000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.64</v>
+        <v>18.43</v>
       </c>
       <c r="EB16" t="n">
         <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7514,130 +7514,130 @@
         <v>1.27</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.09</v>
+        <v>89.92</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>45.09</v>
+        <v>44.42</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.55</v>
+        <v>11.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.73</v>
+        <v>13.58</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48</v>
+        <v>46.83</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH17" t="n">
         <v>10.09</v>
       </c>
-      <c r="BB17" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.05</v>
-      </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO17" t="n">
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.77</v>
+        <v>4.91</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT17" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY17" t="n">
         <v>2.95</v>
@@ -7661,10 +7661,10 @@
         <v>3.69</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="CE17" t="n">
         <v>1.38</v>
@@ -7673,7 +7673,7 @@
         <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7682,7 +7682,7 @@
         <v>1.98</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
         <v>1.41</v>
@@ -7691,7 +7691,7 @@
         <v>1.77</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CN17" t="n">
         <v>2.12</v>
@@ -7703,7 +7703,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7724,13 +7724,13 @@
         <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="DA17" t="n">
         <v>2.14</v>
@@ -7745,79 +7745,79 @@
         <v>3.25</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="DH17" t="n">
-        <v>97</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.54</v>
+        <v>53.78</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.73</v>
+        <v>10.7</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.64</v>
+        <v>7.78</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.36</v>
+        <v>48.7</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.09</v>
+        <v>11.87</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.220000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.5</v>
+        <v>19.26</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>87.55</v>
+        <v>88.08</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.36</v>
+        <v>39.42</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.640000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.27</v>
+        <v>8.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43</v>
+        <v>43.83</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.09</v>
+        <v>8.92</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.18</v>
+        <v>16.92</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.5</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BL18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO18" t="n">
         <v>0.91</v>
       </c>
-      <c r="BM18" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0.82</v>
-      </c>
       <c r="BP18" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT18" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY18" t="n">
         <v>3.68</v>
@@ -8058,40 +8058,40 @@
         <v>4.06</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC18" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="CD18" t="n">
         <v>5.57</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>5.77</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK18" t="n">
         <v>1.47</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM18" t="n">
         <v>2.54</v>
@@ -8103,7 +8103,7 @@
         <v>1.32</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ18" t="n">
         <v>3.59</v>
@@ -8112,10 +8112,10 @@
         <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU18" t="n">
         <v>1.43</v>
@@ -8130,64 +8130,64 @@
         <v>1.59</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
         <v>2.08</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.64</v>
+        <v>88.87</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.36</v>
+        <v>42.26</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.779999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.91</v>
+        <v>10.82</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.720000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DS18" t="n">
         <v>0.09</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>43.28</v>
+        <v>43.7</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.77</v>
+        <v>9.65</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.14</v>
+        <v>17.48</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.18</v>
@@ -8320,52 +8320,52 @@
         <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" t="n">
-        <v>81.91</v>
+        <v>85.17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.36</v>
+        <v>39.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.64</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.91</v>
+        <v>9.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>48.91</v>
+        <v>50</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.359999999999999</v>
+        <v>10.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.27</v>
+        <v>3.92</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.18</v>
+        <v>19.08</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY19" t="n">
         <v>2.21</v>
@@ -8461,31 +8461,31 @@
         <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.69</v>
@@ -8497,19 +8497,19 @@
         <v>1.63</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8524,73 +8524,73 @@
         <v>1.46</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX19" t="n">
         <v>1.48</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DB19" t="n">
         <v>1.29</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="DE19" t="n">
         <v>0.13</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DH19" t="n">
-        <v>89.54000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.46</v>
+        <v>5.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.22</v>
+        <v>48.48</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.96</v>
+        <v>10.87</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.22</v>
+        <v>11.08</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.039999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.59</v>
+        <v>52.04</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.68</v>
+        <v>11</v>
       </c>
       <c r="DY19" t="n">
         <v>7.13</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.54</v>
+        <v>3.87</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.05</v>
+        <v>19.96</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>87.81999999999999</v>
+        <v>88.08</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="K20" t="n">
-        <v>5.91</v>
+        <v>5.67</v>
       </c>
       <c r="L20" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>44.36</v>
+        <v>43.67</v>
       </c>
       <c r="N20" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>11.27</v>
+        <v>11.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.55</v>
+        <v>11.92</v>
       </c>
       <c r="R20" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="S20" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="T20" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V20" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>43</v>
+        <v>43.33</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.55</v>
+        <v>10.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>19</v>
+        <v>19.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8804,70 +8804,70 @@
         <v>1.82</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BH20" t="n">
-        <v>11.73</v>
+        <v>11.48</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM20" t="n">
         <v>1.09</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.64</v>
+        <v>5.52</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV20" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX20" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CC20" t="n">
         <v>5.11</v>
@@ -8876,13 +8876,13 @@
         <v>6.8</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH20" t="n">
         <v>1.41</v>
@@ -8894,7 +8894,7 @@
         <v>1.65</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL20" t="n">
         <v>1.65</v>
@@ -8906,31 +8906,31 @@
         <v>2.07</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV20" t="n">
         <v>2.17</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX20" t="n">
         <v>1.49</v>
@@ -8942,91 +8942,91 @@
         <v>2.57</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DB20" t="n">
         <v>1.29</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.86</v>
+        <v>88</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.32</v>
+        <v>5.22</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.27</v>
+        <v>42</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.14</v>
+        <v>11.04</v>
       </c>
       <c r="DQ20" t="n">
-        <v>11.78</v>
+        <v>11.96</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.869999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.04</v>
+        <v>43.22</v>
       </c>
       <c r="DW20" t="n">
         <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>10.32</v>
+        <v>10.43</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.95</v>
+        <v>18.22</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0.18</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>91.27</v>
+        <v>87.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.64</v>
+        <v>38.92</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.36</v>
+        <v>10.83</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.18</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,82 +9183,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43.27</v>
+        <v>42.67</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.64</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BD21" t="n">
-        <v>16.27</v>
+        <v>16.92</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.550000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.73</v>
+        <v>4.57</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS21" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU21" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV21" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY21" t="n">
         <v>3.63</v>
@@ -9267,28 +9267,28 @@
         <v>3.88</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="CC21" t="n">
-        <v>7.49</v>
+        <v>7.56</v>
       </c>
       <c r="CD21" t="n">
-        <v>8.77</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG21" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI21" t="n">
         <v>1.91</v>
@@ -9306,22 +9306,22 @@
         <v>2.66</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO21" t="n">
         <v>1.27</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CR21" t="n">
         <v>1.42</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CT21" t="n">
         <v>2.98</v>
@@ -9330,16 +9330,16 @@
         <v>1.48</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.4</v>
@@ -9351,52 +9351,52 @@
         <v>1.33</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="DE21" t="n">
         <v>0.09</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.91</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.04</v>
+        <v>39.17</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.1</v>
+        <v>14.09</v>
       </c>
       <c r="DQ21" t="n">
-        <v>10.46</v>
+        <v>10.7</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS21" t="n">
         <v>0.09</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.36</v>
+        <v>44</v>
       </c>
       <c r="DW21" t="n">
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>8.960000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DY21" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.55</v>
+        <v>18.79</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.08</v>
+        <v>59</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.13</v>
+        <v>58.09</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>53.17</v>
+        <v>53.08</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.87</v>
+        <v>52.83</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>100.91</v>
+        <v>104.42</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>57</v>
+        <v>57.17</v>
       </c>
       <c r="N10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.36</v>
+        <v>13.33</v>
       </c>
       <c r="R10" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>46.45</v>
+        <v>47.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.36</v>
+        <v>12.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.55</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,70 +4774,70 @@
         <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO10" t="n">
         <v>1.09</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY10" t="n">
         <v>2.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC10" t="n">
         <v>4.07</v>
@@ -4846,10 +4846,10 @@
         <v>4.44</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG10" t="n">
         <v>2.83</v>
@@ -4858,7 +4858,7 @@
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.83</v>
@@ -4867,10 +4867,10 @@
         <v>1.45</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN10" t="n">
         <v>1.98</v>
@@ -4879,28 +4879,28 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX10" t="n">
         <v>1.56</v>
@@ -4915,55 +4915,55 @@
         <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD10" t="n">
         <v>3.28</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.54000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.54</v>
+        <v>49</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.41</v>
+        <v>10.35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.54</v>
+        <v>12.56</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="DS10" t="n">
         <v>0.04</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.68</v>
+        <v>43.35</v>
       </c>
       <c r="DW10" t="n">
         <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.77</v>
+        <v>10.74</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.64</v>
+        <v>7.61</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.91</v>
+        <v>19.17</v>
       </c>
       <c r="EB10" t="n">
         <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.27</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.81999999999999</v>
+        <v>82.42</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.64</v>
+        <v>7.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.64</v>
+        <v>45.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.45</v>
+        <v>10.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.91</v>
+        <v>7.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.45</v>
+        <v>16.92</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
         <v>1.09</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU12" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY12" t="n">
         <v>2.86</v>
@@ -5640,16 +5640,16 @@
         <v>3.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.35</v>
+        <v>5.16</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
@@ -5658,13 +5658,13 @@
         <v>2.83</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.81</v>
@@ -5673,7 +5673,7 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM12" t="n">
         <v>2.5</v>
@@ -5682,22 +5682,22 @@
         <v>1.95</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU12" t="n">
         <v>1.42</v>
@@ -5724,52 +5724,52 @@
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
         <v>3.23</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.28</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.46</v>
+        <v>43.26</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.960000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.72</v>
+        <v>12.61</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.68</v>
+        <v>7.52</v>
       </c>
       <c r="DS12" t="n">
         <v>0.13</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.64</v>
+        <v>45.48</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.81</v>
+        <v>12.87</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.59</v>
+        <v>17.79</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="13">
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>53.17</v>
+        <v>53.25</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.57</v>
+        <v>52.61</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.58</v>
+        <v>51.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0.08</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.82</v>
+        <v>53.87</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_England_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
-        <v>89.09</v>
+        <v>90.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.45</v>
+        <v>49.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.18</v>
+        <v>12.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.18</v>
+        <v>10.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.64</v>
+        <v>45.92</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.64</v>
+        <v>13.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.18</v>
+        <v>7.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.18</v>
+        <v>16.83</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT2" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
         <v>2.55</v>
@@ -1610,31 +1610,31 @@
         <v>2.72</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.19</v>
+        <v>4.03</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.49</v>
+        <v>4.32</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH2" t="n">
         <v>1.53</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1658,16 +1658,16 @@
         <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU2" t="n">
         <v>1.55</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="DG2" t="n">
         <v>3.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.08</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.52</v>
+        <v>49.92</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.31</v>
+        <v>12.42</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.44</v>
+        <v>10.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.74</v>
+        <v>7.79</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.05</v>
+        <v>49.04</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.57</v>
+        <v>13.38</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.26</v>
+        <v>19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.91</v>
+        <v>95.17</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.91</v>
+        <v>6.42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>57</v>
+        <v>56.58</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.55</v>
+        <v>10.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.09</v>
+        <v>56.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.45</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.91</v>
+        <v>5.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.18</v>
+        <v>16.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.91</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.39</v>
+        <v>4.54</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.52</v>
+        <v>4.67</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY3" t="n">
         <v>1.43</v>
@@ -2013,25 +2013,25 @@
         <v>1.44</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2043,25 +2043,25 @@
         <v>1.97</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
         <v>1.86</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO3" t="n">
         <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
@@ -2082,25 +2082,25 @@
         <v>2.03</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2109,73 +2109,73 @@
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.87</v>
+        <v>100.75</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.92</v>
+        <v>6.17</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.65</v>
+        <v>60.29</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.17</v>
+        <v>10.04</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.91</v>
+        <v>10.88</v>
       </c>
       <c r="DR3" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.09</v>
+        <v>57.75</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.91</v>
+        <v>14.88</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.92</v>
+        <v>5.04</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.78</v>
+        <v>17.04</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="H4" t="n">
-        <v>91.18000000000001</v>
+        <v>88.67</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>5.18</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>44.36</v>
+        <v>56.92</v>
       </c>
       <c r="N4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O4" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>10.36</v>
+        <v>10.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.18</v>
+        <v>16.92</v>
       </c>
       <c r="R4" t="n">
-        <v>7.27</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.55</v>
+        <v>54.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.45</v>
+        <v>13.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.55</v>
+        <v>14.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
         <v>0.08</v>
@@ -2356,70 +2356,70 @@
         <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.61</v>
+        <v>4.83</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2431,16 +2431,16 @@
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH4" t="n">
         <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.72</v>
@@ -2449,7 +2449,7 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
         <v>2.73</v>
@@ -2464,7 +2464,7 @@
         <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2473,7 +2473,7 @@
         <v>2.8</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
@@ -2482,7 +2482,7 @@
         <v>2.17</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
@@ -2497,55 +2497,55 @@
         <v>2.11</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC4" t="n">
         <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="DE4" t="n">
         <v>0.04</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.43000000000001</v>
+        <v>86.34</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.04</v>
+        <v>5.34</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.61</v>
+        <v>50.88</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.17</v>
+        <v>10.08</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.52</v>
+        <v>16.42</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.48</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>52.83</v>
+        <v>53.62</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.04</v>
+        <v>12.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.57</v>
+        <v>8.17</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.31</v>
+        <v>15.34</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.73</v>
+        <v>83.67</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.36</v>
+        <v>5.92</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.45</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.55</v>
+        <v>8.42</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.64</v>
+        <v>47.83</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.36</v>
+        <v>18.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.869999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>4.92</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.86</v>
@@ -2819,16 +2819,16 @@
         <v>2.99</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
@@ -2837,13 +2837,13 @@
         <v>2.71</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.73</v>
@@ -2855,10 +2855,10 @@
         <v>1.74</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
@@ -2867,22 +2867,22 @@
         <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW5" t="n">
         <v>1.77</v>
@@ -2909,79 +2909,79 @@
         <v>3.18</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DH5" t="n">
-        <v>92</v>
+        <v>90.25</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.13</v>
+        <v>4.96</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.87</v>
+        <v>45</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.52</v>
+        <v>10.42</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.56</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.74</v>
+        <v>7.21</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>47.48</v>
+        <v>46.66</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.48</v>
+        <v>10.29</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.13</v>
+        <v>19.08</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="H6" t="n">
-        <v>101.36</v>
+        <v>101.67</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="K6" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>59.73</v>
+        <v>58.42</v>
       </c>
       <c r="N6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.45</v>
+        <v>11.67</v>
       </c>
       <c r="R6" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="S6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.64</v>
+        <v>53.67</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.64</v>
+        <v>14.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.45</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CA6" t="n">
         <v>3.74</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC6" t="n">
         <v>3.7</v>
@@ -3240,13 +3240,13 @@
         <v>2.48</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.63</v>
@@ -3255,7 +3255,7 @@
         <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM6" t="n">
         <v>2.6</v>
@@ -3264,127 +3264,127 @@
         <v>1.98</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
         <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.56</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.41</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.13</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DK6" t="n">
         <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.09</v>
+        <v>53.67</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.78</v>
+        <v>11.84</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.56</v>
+        <v>10.71</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.78</v>
+        <v>7.84</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.48</v>
+        <v>52.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.35</v>
+        <v>13.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.35</v>
+        <v>16.08</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="H8" t="n">
-        <v>104.45</v>
+        <v>107.58</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="L8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>61.64</v>
+        <v>64.42</v>
       </c>
       <c r="N8" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.55</v>
+        <v>12.75</v>
       </c>
       <c r="R8" t="n">
-        <v>6.82</v>
+        <v>6.67</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.45</v>
+        <v>59.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.36</v>
+        <v>14.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.64</v>
+        <v>14.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.26</v>
+        <v>10.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CC8" t="n">
         <v>2.31</v>
@@ -4040,157 +4040,157 @@
         <v>2.48</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH8" t="n">
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK8" t="n">
         <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CR8" t="n">
         <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CT8" t="n">
         <v>3.26</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB8" t="n">
         <v>1.28</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DH8" t="n">
-        <v>100.04</v>
+        <v>101.79</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.74</v>
+        <v>5.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM8" t="n">
-        <v>53.91</v>
+        <v>55.62</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.05</v>
+        <v>13.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.96</v>
+        <v>6.88</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.17</v>
+        <v>57.75</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.39</v>
+        <v>13.42</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.08</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.27</v>
+        <v>79.42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>38.91</v>
+        <v>42.08</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.73</v>
+        <v>9.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.09</v>
+        <v>7.92</v>
       </c>
       <c r="AT9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.18</v>
       </c>
-      <c r="AU9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>42.27</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BF9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.43</v>
+        <v>4.58</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.62</v>
@@ -4431,16 +4431,16 @@
         <v>2.73</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CE9" t="n">
         <v>1.39</v>
@@ -4449,7 +4449,7 @@
         <v>2.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4461,10 +4461,10 @@
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM9" t="n">
         <v>2.53</v>
@@ -4473,127 +4473,127 @@
         <v>1.98</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA9" t="n">
         <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.43000000000001</v>
+        <v>83.34</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.26</v>
+        <v>44.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.04</v>
+        <v>44.04</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.52</v>
+        <v>11.62</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.61</v>
+        <v>7.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.95</v>
+        <v>16.92</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.08</v>
@@ -4693,52 +4693,52 @@
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.18000000000001</v>
+        <v>87.33</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.09</v>
+        <v>39.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.73</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.27</v>
+        <v>10.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38.91</v>
+        <v>39.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.18</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.64</v>
+        <v>6.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.27</v>
+        <v>18.58</v>
       </c>
       <c r="BE10" t="n">
         <v>1.05</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT10" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY10" t="n">
         <v>2.66</v>
@@ -4834,22 +4834,22 @@
         <v>2.77</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
         <v>3.56</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG10" t="n">
         <v>2.83</v>
@@ -4870,7 +4870,7 @@
         <v>1.85</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN10" t="n">
         <v>1.98</v>
@@ -4879,10 +4879,10 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.42</v>
@@ -4906,7 +4906,7 @@
         <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.42</v>
@@ -4915,25 +4915,25 @@
         <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG10" t="n">
         <v>2.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.7</v>
+        <v>95.88</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
@@ -4942,28 +4942,28 @@
         <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.87</v>
+        <v>7.92</v>
       </c>
       <c r="DS10" t="n">
         <v>0.04</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.35</v>
+        <v>43.46</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.61</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.17</v>
+        <v>19.29</v>
       </c>
       <c r="EB10" t="n">
         <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>88.18000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.82</v>
+        <v>4.08</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.27</v>
+        <v>43.25</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.91</v>
+        <v>11.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.45</v>
+        <v>10.92</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.73</v>
+        <v>50.42</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.55</v>
+        <v>10.83</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.73</v>
+        <v>19.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="BO11" t="n">
         <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
         <v>3.16</v>
@@ -5237,31 +5237,31 @@
         <v>3.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.77</v>
@@ -5273,22 +5273,22 @@
         <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CO11" t="n">
         <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
         <v>2.92</v>
@@ -5300,10 +5300,10 @@
         <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5321,85 +5321,85 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.26000000000001</v>
+        <v>87.12</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.87</v>
+        <v>47.62</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.04</v>
+        <v>10.96</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.87</v>
+        <v>10.62</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.26</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.26</v>
+        <v>51.54</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.79</v>
+        <v>11.88</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.130000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.17</v>
+        <v>20.16</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
-        <v>96.73</v>
+        <v>96.83</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K12" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="L12" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>41.91</v>
+        <v>41.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.27</v>
+        <v>12.75</v>
       </c>
       <c r="R12" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.64</v>
+        <v>46</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.18</v>
+        <v>14.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.45</v>
+        <v>9.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.73</v>
+        <v>19.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>1.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.390000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.87</v>
+        <v>4.04</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.43</v>
+        <v>4.58</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT12" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC12" t="n">
         <v>4.5</v>
@@ -5664,25 +5664,25 @@
         <v>1.41</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
         <v>1.92</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP12" t="n">
         <v>1.99</v>
@@ -5703,7 +5703,7 @@
         <v>1.42</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW12" t="n">
         <v>1.89</v>
@@ -5712,13 +5712,13 @@
         <v>1.6</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
@@ -5727,82 +5727,82 @@
         <v>2.09</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.26000000000001</v>
+        <v>89.62</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.26</v>
+        <v>42.88</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.61</v>
+        <v>12.38</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.52</v>
+        <v>7.46</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.48</v>
+        <v>45.66</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.87</v>
+        <v>12.46</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.74</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.79</v>
+        <v>18</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G13" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="H13" t="n">
-        <v>117.45</v>
+        <v>114.83</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K13" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>69.27</v>
+        <v>67.58</v>
       </c>
       <c r="N13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>8.91</v>
+        <v>9.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.82</v>
+        <v>10.75</v>
       </c>
       <c r="R13" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>62.55</v>
+        <v>61.83</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>18.27</v>
+        <v>18.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.09</v>
+        <v>12.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.45</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
         <v>2.01</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>10.17</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1.96</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.26</v>
+        <v>4.54</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.48</v>
+        <v>5.54</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="CC13" t="n">
         <v>2.29</v>
@@ -6058,46 +6058,46 @@
         <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG13" t="n">
         <v>3.53</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CN13" t="n">
         <v>2.2</v>
       </c>
-      <c r="CJ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>2.19</v>
-      </c>
       <c r="CO13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP13" t="n">
         <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CT13" t="n">
         <v>3.25</v>
@@ -6106,73 +6106,73 @@
         <v>1.63</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DB13" t="n">
         <v>1.27</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DH13" t="n">
-        <v>114.87</v>
+        <v>113.66</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.56</v>
+        <v>5.62</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM13" t="n">
-        <v>63.65</v>
+        <v>63.04</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.52</v>
+        <v>11.46</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.57</v>
+        <v>6.54</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.74</v>
+        <v>61.42</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.43</v>
+        <v>15.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.13</v>
+        <v>11.08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.22</v>
+        <v>20</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6305,139 +6305,139 @@
         <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>106</v>
+        <v>105.33</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.45</v>
+        <v>55.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.18</v>
+        <v>9.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.91</v>
+        <v>13.17</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.45</v>
+        <v>6.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>59.18</v>
+        <v>59.33</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.18</v>
+        <v>8.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BD14" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY14" t="n">
         <v>1.33</v>
@@ -6446,31 +6446,31 @@
         <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CE14" t="n">
         <v>1.21</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CH14" t="n">
         <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.61</v>
@@ -6485,16 +6485,16 @@
         <v>2.53</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CP14" t="n">
         <v>1.5</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
@@ -6512,7 +6512,7 @@
         <v>2.24</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
@@ -6521,7 +6521,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
         <v>2.06</v>
@@ -6536,46 +6536,46 @@
         <v>2.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DH14" t="n">
-        <v>108.09</v>
+        <v>107.66</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.69</v>
+        <v>59.62</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.869999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.09</v>
+        <v>13.21</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.69</v>
+        <v>5.58</v>
       </c>
       <c r="DS14" t="n">
         <v>0.08</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.44</v>
+        <v>59.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.05</v>
+        <v>14.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.13</v>
+        <v>17.96</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>102</v>
+        <v>99.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="K15" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="L15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="M15" t="n">
-        <v>55.73</v>
+        <v>55.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="P15" t="n">
-        <v>10.64</v>
+        <v>10.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.09</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
         <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.91</v>
+        <v>51.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.27</v>
+        <v>16.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.09</v>
+        <v>10.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.36</v>
+        <v>19.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="BJ15" t="n">
         <v>0.83</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="CA15" t="n">
         <v>3.96</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="CC15" t="n">
         <v>2.92</v>
@@ -6867,16 +6867,16 @@
         <v>2.36</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK15" t="n">
         <v>1.39</v>
@@ -6888,7 +6888,7 @@
         <v>2.76</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO15" t="n">
         <v>1.19</v>
@@ -6909,7 +6909,7 @@
         <v>3.28</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV15" t="n">
         <v>2.39</v>
@@ -6933,52 +6933,52 @@
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.22</v>
+        <v>100.88</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.26</v>
+        <v>49.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.44</v>
+        <v>10.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.35</v>
+        <v>12.29</v>
       </c>
       <c r="DR15" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.61</v>
+        <v>52.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.17</v>
+        <v>16.05</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.56</v>
+        <v>10.42</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.26</v>
+        <v>18.96</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.08</v>
@@ -7111,52 +7111,52 @@
         <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>110.36</v>
+        <v>107.08</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.45</v>
+        <v>5.92</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AN16" t="n">
-        <v>63.09</v>
+        <v>61.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.09</v>
+        <v>10.25</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.73</v>
+        <v>6.92</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>56.27</v>
+        <v>55.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.64</v>
+        <v>11.33</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.82</v>
+        <v>18.67</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.65</v>
+        <v>11.92</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.39</v>
+        <v>5.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.22</v>
+        <v>5.29</v>
       </c>
       <c r="BR16" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY16" t="n">
         <v>2.17</v>
@@ -7252,73 +7252,73 @@
         <v>2.21</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="CE16" t="n">
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.71</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CQ16" t="n">
         <v>2.88</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>2.9</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CT16" t="n">
         <v>3.22</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.48</v>
@@ -7330,19 +7330,19 @@
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DB16" t="n">
         <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
         <v>1.04</v>
@@ -7351,70 +7351,70 @@
         <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.82</v>
+        <v>103.42</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>59.13</v>
+        <v>58.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.87</v>
+        <v>53.54</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>13</v>
+        <v>12.79</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.43</v>
+        <v>18.38</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>101.91</v>
+        <v>98.42</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="K17" t="n">
-        <v>6.36</v>
+        <v>6.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M17" t="n">
-        <v>64</v>
+        <v>63.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="P17" t="n">
-        <v>9.91</v>
+        <v>9.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.27</v>
+        <v>11.33</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>7.42</v>
       </c>
       <c r="S17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.73</v>
+        <v>49.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.09</v>
+        <v>13.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.09</v>
+        <v>18.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08</v>
@@ -7595,49 +7595,49 @@
         <v>1.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.91</v>
+        <v>5.04</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CC17" t="n">
         <v>4.06</v>
@@ -7667,124 +7667,124 @@
         <v>4.28</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
         <v>1.98</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK17" t="n">
         <v>1.41</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM17" t="n">
         <v>2.75</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
         <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY17" t="n">
         <v>1.75</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
         <v>0.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.65000000000001</v>
+        <v>94.17</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM17" t="n">
-        <v>53.78</v>
+        <v>53.75</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.7</v>
+        <v>10.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.78</v>
+        <v>7.96</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.7</v>
+        <v>48.04</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.87</v>
+        <v>11.75</v>
       </c>
       <c r="DY17" t="n">
         <v>8.08</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.26</v>
+        <v>19.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H19" t="n">
-        <v>97.18000000000001</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>5.82</v>
+        <v>5.58</v>
       </c>
       <c r="L19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>58.09</v>
+        <v>57.67</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>11.27</v>
+        <v>11.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.45</v>
+        <v>11.67</v>
       </c>
       <c r="R19" t="n">
-        <v>6.18</v>
+        <v>6.67</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,22 +8296,22 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54.27</v>
+        <v>53</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
         <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.91</v>
+        <v>20.75</v>
       </c>
       <c r="AD19" t="n">
         <v>1.45</v>
@@ -8401,70 +8401,70 @@
         <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.22</v>
+        <v>10.08</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS19" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       